--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -20,6 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_記載密度の比較" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_調査の妥当性" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_追加の修正指示" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_受給率の内訳と推移" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_サービス別の給付動向" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,9 +30,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -137,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,6 +204,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -567,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1080,169 +1102,205 @@
       </c>
       <c r="D30" s="6" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>13_受給率の内訳と推移</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>受給率の在宅・施設居住系別の内訳と、全国との差の推移。要支援・要介護者1人あたり定員。</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>14_サービス別の給付動向</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>サービス種類別の第1号被保険者1人あたり給付月額の推移と、増減の要因。</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画（本編）</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>北海道の施策の柱・数値目標との整合確認</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>08シートの整合確認が概括にとどまる</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>国の記載事項への網羅性確認</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>07シートは部会資料の報道内容に基づく暫定評価</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画（本編）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
+          <t>北海道の施策の柱・数値目標との整合確認</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
+          <t>08シートの整合確認が概括にとどまる</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>国の記載事項への網羅性確認</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>07シートは部会資料の報道内容に基づく暫定評価</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>給付費・地域支援事業費の計画対実績</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の残高推移</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>04シートの剰余額は概算にとどまる</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>注1）本検証の期間中、厚生労働省（mhlw.go.jp）及び北海道（pref.hokkaido.lg.jp）のサイトは本作業環境のネットワークポリシーにより直接取得できなかった。07・08シートは検索結果として得られた報道・解説記事の記述に基づく暫定評価であり、告示及び計画本編の入手後に再確認を要する。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
@@ -1251,7 +1309,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3652,22 +3710,22 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>給付水準の高さの要因が、認定率ではなく受給率と受給者1人あたり給付月額にあることが見える化D49で確認できるが、素案の第2章に要因分解がなく、KPIも認定率系に偏っている。</t>
+          <t>給付水準の高さの要因が、認定率ではなく施設および居住系サービスの受給率にあるが、素案の第2章に要因分解がなく、KPIも認定率系に偏っている。</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節に地域差指数による要因分解（給付月額1.08／認定率1.02／受給率1.08／受給者単価1.06）を新設する。受給率・受給者単価をモニタリング指標に加える。ただしD49の受給率の分母定義を先に確定する。</t>
+          <t>第2章第2節に地域差指数（給付月額1.08／認定率1.02／受給率1.08／受給者単価1.06）と、受給率の内訳（在宅は全国比1.02、施設および居住系は同1.23）による要因分解を新設する。施設および居住系サービス受給率をモニタリング指標に加える。</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>見える化D49（令和5年・地域別）／見える化D42（介護サービス利用率）</t>
+          <t>見える化D49（令和5年）／D41（令和7年）／D41-a（月次時系列 H26.4〜R8.1）</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>要（定義を確認）</t>
+          <t>不要（数値確定済み）</t>
         </is>
       </c>
     </row>
@@ -4269,6 +4327,1573 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>受給率の内訳と全国・北海道との差の推移</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見える化D41（令和7年・地域別）、D41-a（平成26年4月〜令和8年1月の月次時系列。年度平均に集計）、D28・D29・D30（要支援・要介護者1人あたり定員）による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　受給率の内訳（令和7年・％。分母は第1号被保険者数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>全国比</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>受給率（在宅サービス）</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>在宅の受給率は全国とほぼ同水準。北海道は全国を下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>受給率（施設および居住系サービス）</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>大雪は全国を1.0ポイント（23％）上回る。給付水準の超過分はほぼ全てここに集中している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>見える化D49の地域差指数「受給率1.08」を再現する。これにより同指数の分母が第1号被保険者数であることが確定した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2　施設および居住系サービス受給率の推移（年度平均・％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>H28</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="L12" s="18" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>平成27年度6.10％をピークに0.85ポイント低下。定員の縮小と整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L13" s="18" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>4.4〜4.7％で横ばい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>平成28年度4.03％から令和7年度4.30％へ0.27ポイント上昇。大雪と逆方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>差（大雪－全国・ポイント）</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度1.98ポイントから令和7年度0.95ポイントへ半減した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>指数（全国＝1.00）</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>1.49から1.22へ低下。大雪の施設・居住系の相対的な手厚さは着実に失われている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3　要支援・要介護者1人あたり定員の推移（人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>H30→R7</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>－34.9％</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度に施設が開設され0.124人へ上昇した後、令和2年度に0.085人へ低下。定員234人→160人に対応する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="D21" s="25" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="F21" s="25" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>－4.7％</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>定員240人は不変。認定者増により1人あたりは緩やかに低下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>－3.0％</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>定員62人は平成30年度以降不変。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス計</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="D23" s="25" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="F23" s="25" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="26" t="inlineStr">
+        <is>
+          <t>－17.7％</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度をピークに17.7％減。認定者1人あたりでみた施設の受け皿は着実に縮小している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>－4.8％</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>定員156人は概ね不変。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>－17.7％</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>定員117人→99人の減少に対応する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>居住系サービス計</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="F26" s="25" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>－10.3％</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>令和4年度に段差がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>通所系サービス計</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F27" s="25" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>－2.7％</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>通所介護は0.013人→0.023人と増える一方、地域密着型通所介護は0.030人→0.025人に減少。区分間の移動を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>注1）受給率は受給者数を第1号被保険者数で除した値。介護サービス利用率（06シート）は受給者数を認定者数で除した値であり、分母が異なる別の比率である。注2）D41-aは月次データであり、本シートでは年度（4月〜翌年3月）で平均した。令和7年度は令和8年1月までの10か月平均である。注3）要支援・要介護者1人あたり定員は介護サービス情報公表システム及び月報による。定員そのものは変わらなくても認定者が増えれば低下するため、供給の実数の変化（06シート1）と併せて読む。注4）第9期計画・素案第9稿とも本シートの指標を掲載していない。第2章に新設することを推奨する（修正指示書A-11・A-13）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>サービス種類別　第1号被保険者1人あたり給付月額の推移</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見える化D13-a〜z（時系列）及びD13（令和7年・サービス種類別）による。令和7年度は令和8年1月サービス提供分までの暫定値。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>H30→R7</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>5094</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>3952</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>3943</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>4039</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>4105</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度から平成30年度にかけて1,142円減。以後は横ばい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>4562</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>4547</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>4672</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>4359</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>4440</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>定員240人が不変で、給付も横ばい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>674</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1662</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>1715</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>1712</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度の整備で水準が定着。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>1032</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>985</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>1128</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>1139</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>1188</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>定員156人が不変のなかで単価上昇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>2549</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>2947</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>2445</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>2461</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>-0.105</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>定員117人→99人の減少に対応して令和5年度に低下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>2317</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>2602</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>2706</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>3287</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>3976</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>全サービスで最大の増加額（＋1,374円）。在宅給付の最大項目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>314</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>328</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>463</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>451</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>555</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>0.6920000000000001</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>増加率が最大。医療ニーズの在宅化を反映している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>1619</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>694</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>697</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>669</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>675</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>平成28年度の地域密着型への移行で段差がある。以後は横ばい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>777</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>623</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>719</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>567</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>令和5年度以降に大きく低下。事業所の休廃止の有無を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>1378</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1328</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>1425</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>1676</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>通所介護が横ばいのなかで増加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>1549</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1731</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>1989</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>2155</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>在宅で3番目に大きい項目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>429</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>516</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>518</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>662</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>704</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>在宅生活の継続を支える基盤として増加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援・居宅介護支援</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>899</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1163</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>1229</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>受給者数の伸びを上回る増加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度0円、平成30年度4円、令和2年度33円、令和5年度0円、令和7年度15円と不安定で、実質的に未整備。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2　読み取れること</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>所見</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>第10期での対応</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>在宅給付の増加は訪問系が牽引している</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度→令和7年度で訪問介護＋52.8％（＋1,374円）、訪問看護＋69.2％（＋227円）。一方で通所介護－2.7％、地域密着型通所介護－27.0％と通所系は縮小している。</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>第2章の給付分析を「在宅・居住系・施設」の3区分にとどめず、在宅を訪問系・通所系・その他に分けて示す。第6章の見込量も同じ区分で説明する。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>重度在宅を支える24時間サービスが実質的に存在しない</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護は令和7年度で15円、夜間対応型訪問介護は0円、看護小規模多機能型居宅介護は0円（見える化D13・令和7年）。一方で要介護5の在宅・居住系割合は54.6％に達している。</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第6章第4節の整備方針で、重度在宅者を支える24時間対応サービスの必要性を検討する。整備しない判断をする場合も、その代替（訪問介護・訪問看護・小規模多機能の組合せ）を明記する。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の減少が給付に表れている</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>定員117人（令和3年度）→99人（令和4年度以降）に対応して、給付月額は2,947円（令和2年度）から2,445円（令和5年度）へ17.0％低下している。</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>第2章で定員減少とその要因（事業所の休廃止・ユニット縮小）を記述し、認知症高齢者の増加見込みとの整合を第6章で説明する。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護の低下要因を確認する必要がある</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>777円（平成30年度）→567円（令和7年度）で27.0％低下。第9期計画は4施設で据置きとしていた。</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>事業所数・定員・利用者数の推移を確認し、休廃止があれば第2章に記述する。美瑛町3施設・東川町1施設の状況を町に照会する。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>施設給付は既に平成30年度に一段下がっている</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設は5,094円（平成26年度）→3,952円（平成30年度）で22.4％低下し、以後は横ばい。定員194人→234人→160人の推移と対応している。</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画・素案とも施設給付の水準変化の経緯を記述していない。第2章に沿革を注記する。</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>注1）金額は第1号被保険者1人あたりの月額（円）。分母は見える化の第1号被保険者数。注2）令和6年度は令和7年2月、令和7年度は令和8年1月のサービス提供分までの暫定値であり確定値ではない。注3）地域密着型通所介護は平成27年度の値がないため、平成30年度からの比較としている。平成28年度の制度改正で通所介護（定員18人以下）が地域密着型へ移行したため、通所介護と地域密着型通所介護は合算して読む必要がある（平成30年度1,471円→令和7年度1,242円で15.6％減）。注4）令和7年のサービス種類別の合計は、在宅12,558円＋施設および居住系14,327円＝26,885円で、見える化C1の第1号被保険者1人あたり保険給付月額（令和7年度26,885円）と一致する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -4352,22 +5977,22 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>認定率を代表KPIに据えた設計が、給付水準の要因構造とずれている</t>
+          <t>給付水準の高さは施設・居住系サービスの受給率に集約される</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>見える化D49の地域差指数（令和5年）は、第1号1人あたり給付月額1.08・受給率1.08・受給者1人あたり給付月額1.06に対し、性年齢調整後の認定率は1.02で全国並み。北海道はそれぞれ0.94／0.97／0.92／1.07。</t>
+          <t>見える化D41（令和7年）の受給率は、在宅サービスが全国11.0％・北海道10.3％に対し大雪11.2％（全国比1.02）、施設および居住系サービスが全国4.3％・北海道4.5％に対し大雪5.3％（全国比1.23）。両者の合計16.5％は全国15.3％の1.078倍で、D49の地域差指数「受給率1.08」を再現する。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>代表KPI4項目のうち2項目（①認定率・②重度認定率）が認定率系。給付水準を押し上げている受給率・単価には指標がない。</t>
+          <t>代表KPI4項目のうち2項目（①認定率・②重度認定率）が認定率系。年齢調整後の認定率は1.02で全国並みであり、給付水準を押し上げている施設・居住系の受給率には指標がない。</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>H01は年齢調整済認定率へ改める方向で妥当。加えて受給率・受給者単価をモニタリング指標に加える。ただしD49の受給率の分母定義が出力ファイルから確認できないため、要因分解の前に定義を確定する。</t>
+          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。</t>
         </is>
       </c>
     </row>
@@ -4394,12 +6019,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は利用率を分析も指標化もしていない。認定者増を前提に給付費を見込んだため、実績が見込を下回る一因となった可能性がある。</t>
+          <t>第9期計画は利用率を分析も指標化もしていない。認定者増を前提に給付費を見込んだため、実績が見込を下回る一因となった可能性がある。なお利用率（受給者÷認定者）と受給率（受給者÷第1号被保険者）は別の比率であり、受給率が全国を上回ること（所見1）と利用率が低下することは両立する。</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>未利用の要因（供給制約・申請先行・軽度者の自立）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率の推移を新設する。</t>
+          <t>未利用の要因（供給制約・申請先行・軽度者の自立）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。</t>
         </is>
       </c>
     </row>
@@ -4421,7 +6046,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>見える化D38：在宅・居住系割合は73.3％（H26）→77.5％（R7）。要介護5は31.3％→54.6％、要介護4は43.9％→49.1％。一方D25・D26の定員は介護老人福祉施設が234人（H29）→160人（R2以降）、認知症GHが117人（R3）→99人（R4以降）。</t>
+          <t>見える化D38：在宅・居住系割合は73.3％（H26）→77.5％（R7）。要介護5は31.3％→54.6％、要介護4は43.9％→49.1％。一方、見える化D28の要支援・要介護者1人あたり定員（施設サービス計）は0.288人（H30）→0.237人（R7）で17.7％減、うち介護老人福祉施設は0.126人→0.082人で34.9％減。D29の居住系計は0.146人→0.131人で10.3％減。実数ではD25・D26のとおり介護老人福祉施設が234人（H29）→160人（R2以降）、認知症GHが117人（R3）→99人（R4以降）。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -4723,10 +6348,10 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく受給率・単価に由来し（所見1）、その受給率は低下傾向にあり（所見2）、同時に重度者の在宅化と供給縮小が進んでいる（所見3）。この3点が第10期の需給分析の中心論点になる。</t>
+          <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率に由来し（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
         </is>
       </c>
     </row>
@@ -7221,7 +8846,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>大雪は全国を8％上回る。ただし本指標の分母（第1号被保険者か認定者か）が出力ファイルから確認できず、見える化D42の介護サービス利用率（令和6年度74.3％・低下傾向）とは方向が一致しない。定義の確認を要する。</t>
+          <t>大雪は全国を8％上回る。分母はD41との突合により第1号被保険者数と確定した（大雪：在宅11.2％＋施設居住系5.3％＝16.5％、全国：11.0％＋4.3％＝15.3％、比1.078）。内訳は在宅が全国比1.02、施設および居住系が同1.23で、超過分はほぼ全て施設・居住系に由来する。</t>
         </is>
       </c>
     </row>
@@ -7254,7 +8879,7 @@
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>注1）3の受給率について、地域差指数は大雪が全国を8％上回るとする一方、見える化D42の介護サービス利用率（受給者数÷認定者数）は平成28年度82.2％から令和6年度74.3％へ低下している。両者は分母が異なる可能性が高く、第2章で要因分解を行う前に見える化のマニュアルで定義を確定する必要がある。定義を誤ると「利用が多いから給付費が高い」と「利用が少ないのに給付費が高い」という正反対の結論になり得る。注2）管内他保険者の施策内容については、各保険者の計画本編が未入手のため本検証では比較していない。保険料水準の高い上位4保険者はいずれも小規模町であり、施設整備の状況・被保険者数の規模による1人あたり負担の変動が要因として考えられるが、確認していない。</t>
+          <t>注1）3の受給率の分母は、D41（令和7年・地域別）の在宅11.2％と施設および居住系5.3％の合計16.5％が全国の15.3％の1.078倍となり、D49の1.08と一致することから第1号被保険者数と確定した。見える化D42の介護サービス利用率（受給者数÷認定者数）とは分母が異なる別の比率であり、受給率が全国を上回りながら利用率が低下することは矛盾しない。第2章では両者を併記し分母を明記する。注2）管内他保険者の施策内容については、各保険者の計画本編が未入手のため本検証では比較していない。保険料水準の高い上位4保険者はいずれも小規模町であり、施設整備の状況・被保険者数の規模による1人あたり負担の変動が要因として考えられるが、確認していない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -22,6 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_追加の修正指示" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_受給率の内訳と推移" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_サービス別の給付動向" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_第10期KPIの妥当性" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_仕様書との適合性" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +38,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +77,11 @@
       <name val="Carlito"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -141,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,6 +175,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -196,9 +206,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -215,6 +222,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -589,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1138,169 +1146,205 @@
       </c>
       <c r="D32" s="6" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>15_第10期KPIの妥当性</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>H01〜H16の16項目について、データ源の確保状況と基準値の算定可否を個別に評価。</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>16_仕様書との適合性</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>業務仕様書４（1）〜（12）及び業務スケジュールに対する対応状況と未対応事項。</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画（本編）</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>北海道の施策の柱・数値目標との整合確認</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>08シートの整合確認が概括にとどまる</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>国の記載事項への網羅性確認</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>07シートは部会資料の報道内容に基づく暫定評価</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画（本編）</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
+          <t>北海道の施策の柱・数値目標との整合確認</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
+          <t>08シートの整合確認が概括にとどまる</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>国の記載事項への網羅性確認</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>07シートは部会資料の報道内容に基づく暫定評価</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>給付費・地域支援事業費の計画対実績</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の残高推移</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>04シートの剰余額は概算にとどまる</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>注1）本検証の期間中、厚生労働省（mhlw.go.jp）及び北海道（pref.hokkaido.lg.jp）のサイトは本作業環境のネットワークポリシーにより直接取得できなかった。07・08シートは検索結果として得られた報道・解説記事の記述に基づく暫定評価であり、告示及び計画本編の入手後に再確認を要する。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
@@ -1309,8 +1353,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2094,34 +2138,34 @@
           <t>認知症</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>114</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>68</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="14" t="n">
         <v>10.38</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="14" t="n">
         <v>18.66</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="14" t="n">
         <v>32.98</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>21.94</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <v>10.41</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -2136,34 +2180,34 @@
           <t>住まい</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="14" t="n">
         <v>2.46</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <v>1.78</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <v>7.76</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>3.07</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <v>9.02</v>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -2178,34 +2222,34 @@
           <t>BCP・業務継続</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>0.88</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>5.55</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -2220,34 +2264,34 @@
           <t>家族介護</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <v>1.94</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>1.32</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="14" t="n">
         <v>3.82</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -2262,34 +2306,34 @@
           <t>権利擁護</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="14" t="n">
         <v>1.33</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="14" t="n">
         <v>7.76</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="14" t="n">
         <v>0.88</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="14" t="n">
         <v>2.77</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -2304,34 +2348,34 @@
           <t>介護人材</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="14" t="n">
         <v>2.28</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="14" t="n">
         <v>0.44</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="14" t="n">
         <v>1.45</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="14" t="n">
         <v>3.07</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="14" t="n">
         <v>3.47</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -2346,34 +2390,34 @@
           <t>人材確保</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>1.55</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="14" t="n">
         <v>0.89</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="14" t="n">
         <v>0.97</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="14" t="n">
         <v>1.32</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="14" t="n">
         <v>2.43</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -2388,34 +2432,34 @@
           <t>生産性向上</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="14" t="n">
         <v>1.32</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="14" t="n">
         <v>1.04</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -2430,34 +2474,34 @@
           <t>給付適正化</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>0.46</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="K13" s="14" t="n">
         <v>2.43</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -2472,34 +2516,34 @@
           <t>フレイル</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="14" t="n">
         <v>1.18</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="14" t="n">
         <v>11.99</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="14" t="n">
         <v>0.97</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="13" t="n">
+      <c r="K14" s="14" t="n">
         <v>2.77</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -2514,34 +2558,34 @@
           <t>通いの場</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>1.46</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="14" t="n">
         <v>0.44</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="14" t="n">
         <v>1.45</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="14" t="n">
         <v>0.88</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="K15" s="14" t="n">
         <v>1.73</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -2556,34 +2600,34 @@
           <t>総合事業</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="14" t="n">
         <v>2.64</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="14" t="n">
         <v>0.89</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="14" t="n">
         <v>1.45</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="14" t="n">
         <v>3.07</v>
       </c>
-      <c r="K16" s="13" t="n">
+      <c r="K16" s="14" t="n">
         <v>2.43</v>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -2598,34 +2642,34 @@
           <t>地域ケア会議</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>1.91</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="14" t="n">
         <v>1.33</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="14" t="n">
         <v>2.91</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="14" t="n">
         <v>4.39</v>
       </c>
-      <c r="K17" s="13" t="n">
+      <c r="K17" s="14" t="n">
         <v>2.08</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -2640,34 +2684,34 @@
           <t>重層的支援</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="14" t="n">
         <v>0.36</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="14" t="n">
         <v>0.89</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="14" t="n">
         <v>1.32</v>
       </c>
-      <c r="K18" s="13" t="n">
+      <c r="K18" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -2682,34 +2726,34 @@
           <t>日常生活圏域</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>1.09</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="13" t="n">
+      <c r="K19" s="14" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -2724,34 +2768,34 @@
           <t>身寄り</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="H20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="I20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="13" t="n">
+      <c r="J20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="13" t="n">
+      <c r="K20" s="14" t="n">
         <v>1.73</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -2766,34 +2810,34 @@
           <t>中山間</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="I21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="J21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="13" t="n">
+      <c r="K21" s="14" t="n">
         <v>1.39</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2808,34 +2852,34 @@
           <t>移動支援・移送・公共交通</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="14" t="n">
         <v>1.78</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="I22" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="13" t="n">
+      <c r="J22" s="14" t="n">
         <v>1.75</v>
       </c>
-      <c r="K22" s="13" t="n">
+      <c r="K22" s="14" t="n">
         <v>0.35</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2850,34 +2894,34 @@
           <t>数値目標・目標値</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="I23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="J23" s="14" t="n">
         <v>0.88</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="K23" s="14" t="n">
         <v>1.04</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2892,34 +2936,34 @@
           <t>処遇改善</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="H24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="I24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="13" t="n">
+      <c r="J24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="13" t="n">
+      <c r="K24" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2934,34 +2978,34 @@
           <t>人生会議・ACP</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="I25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="13" t="n">
+      <c r="J25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="13" t="n">
+      <c r="K25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2976,34 +3020,34 @@
           <t>ヤングケアラー</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="14" t="n">
         <v>0.27</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="I26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="J26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="K26" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -3115,10 +3159,10 @@
           <t>介護予防・日常生活圏域ニーズ調査</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>7239</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>4626</v>
       </c>
       <c r="E5" s="23" t="n">
@@ -3151,10 +3195,10 @@
           <t>在宅介護実態調査</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>79</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>37</v>
       </c>
       <c r="E6" s="23" t="n">
@@ -3187,10 +3231,10 @@
           <t>居所変更実態調査</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>21</v>
       </c>
       <c r="E7" s="23" t="n">
@@ -3223,10 +3267,10 @@
           <t>在宅生活改善調査</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E8" s="23" t="n">
@@ -3259,10 +3303,10 @@
           <t>介護人材実態調査</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>27</v>
       </c>
       <c r="E9" s="23" t="n">
@@ -3618,7 +3662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3641,7 +3685,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>修正指示書（第9稿→第10稿）に追加済みの項目。追加後の総数は45件（区分A 13件／区分B 18件／区分C 14件）。</t>
+          <t>修正指示書（第9稿→第10稿）に追加済みの項目21件。追加後の総数は51件（区分A 15件／区分B 20件／区分C 16件、うち要照会35件）。</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3885,12 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>第3章第4節の評価を「目標比」「推計比」「全国・北海道比」の3軸で併記する。①は目標未達だが推計を下回り上昇幅は全国の半分、②は目標・推計とも達成、③は目標未達だが基準値との差は有意でない、④は国目標を達成し自主目標に0.2ポイント未達、と整理する。</t>
+          <t>第3章第4節の評価を「目標比」「推計比」「全国・北海道比」「年齢層別」の4軸で併記する。①は目標未達だが推計を下回り上昇幅は全国の半分で、75歳以上では▲1.8ポイント・85歳以上では▲2.1ポイントと低下、②は目標・推計とも達成、③は目標未達だが基準値との差は有意でない、④は国目標8％を達成し自主目標に0.2ポイント未達、と整理する。</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>第9期計画 第1章第6節1／見える化P2／令和7年度 健康とくらしの調査</t>
+          <t>第9期計画 第1章第6節1／見える化P2・B4-a・B4-d・B4-e／令和7年度 健康とくらしの調査</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -4317,16 +4361,268 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>注1）本シートの15件は修正指示書に反映済みで、追加後の総数は45件（区分A 13件／区分B 18件／区分C 14件）、うち照会が必要なものは29件。注2）優先度「最優先」は第1回介護保険事業計画策定委員会の資料に反映すべき事項。注3）A-11〜A-13は相互に関連しており、第2章の需給分析の骨格を構成する。3件を一体で修正する。</t>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>第2章第2節／計画全体</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>仕様書４（４）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」と明示しているが、類似保険者との比較が未実施であり、受領した見える化データにも類似保険者の系列がない。</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>見える化の類似保険者比較機能で出力を取得し、第2章第2節に比較分析を新設する。比較対象の選定基準（人口規模、高齢化率、施設整備状況、財政力等）を明記する。</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>業務仕様書４（４）／第9期計画 第1章第6節1（1）</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>要（類似保険者の出力を依頼）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A-15</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>第2章／第1章第7節</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>仕様書４（４）は「構成町別及び日常生活圏域等の地域特性を踏まえた分析を実施すること」と明示しているが、圏域別の分析が未実施であり、圏域別のデータも未受領である。</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>圏域別の認定率・受給率・サービス利用状況を入手し、第2章に圏域別の分析を新設する。圏域設定の見直し（C-9）と併せて整理する。</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>業務仕様書４（４）／第9期計画 第1章第7節</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>要（圏域別データを依頼）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>B-19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>第4章第3節／資料編 資料1</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>H09・H10は3町の地域包括支援センターの業務記録をデータ源とするが、記録様式が統一されていない可能性が高く、令和9年度当初からの実測が困難である。</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>初年度は「共通様式の整備と試行」を管理指標とし、基準値の設定と実測を令和10年度からとする段階設定にする。H10の標準日数は3町で合意のうえ定義書に固定する。</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>素案 資料編 資料1（1）／3町 第9期高齢者福祉計画</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>要（3町の記録様式を確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>B-20</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第4章第3節／資料編 資料1</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>H16は実績指標であるため計画期間中に事象がなければ測定機会が生じない。データ源とされる事業所実態調査も仕様書の対象調査に含まれていない。</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>体制指標（BCP策定率、訓練実施率、相互応援協定の締結数）への組替えを検討する。BCPの策定は令和6年度から義務化されており、調査を経ずに測定できる。</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>素案 資料編 資料1（1）／業務仕様書４（３）</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>要（指標の組替えを決定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>C-15</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>資料編 資料1（2）</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>H03（75歳以上新規認定率）は見える化に新規認定者数の系列がなく、認定台帳からの抽出が必要である。抽出可否が未確認。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>認定台帳から年度別・年齢階級別の新規認定者数を抽出できるか確認する。抽出できない場合は指標から外すか、認定者数の純増での代替を検討する。</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>素案 資料編 資料1（2）／見える化B3-a〜e</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>要（台帳の抽出可否を確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>C-16</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>資料編 資料1／第10期の介護人材実態調査</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>H13は「必要常勤換算数」、H14は「採用後12か月時点の在職」を必要とするが、第9期の介護人材実態調査にこれらの設問は確認できない。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>第10期の調査票を確認する。ない場合はH13を求人継続期間又は採用退職の差分、H14を年間離職率での代替とする。仕様書は新たな調査の設計を業務範囲外としている。</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>素案 資料編 資料1（1）／第9期計画 第2章第5節／業務仕様書４（３）</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>要（調査票を確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートの21件は修正指示書に反映済みで、追加後の総数は51件（区分A 15件／区分B 20件／区分C 16件）、うち照会が必要なものは35件。注2）優先度「最優先」は第1回介護保険事業計画策定委員会の資料に反映すべき事項。注3）A-11〜A-13は相互に関連しており、第2章の需給分析の骨格を構成する。3件を一体で修正する。注4）A-14・A-15は業務仕様書４（４）が明示的に求めている分析（類似保険者との比較、日常生活圏域別の分析）が未実施であることを指摘するもので、いずれもデータの受領が前提となる。注5）B-19・B-20・C-15・C-16は15シート（第10期KPIの妥当性）の評価から生じた項目である。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -4340,7 +4636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4426,16 +4722,16 @@
           <t>受給率（在宅サービス）</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>10.3</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>11.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>1.02</v>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
@@ -4458,16 +4754,16 @@
           <t>受給率（施設および居住系サービス）</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>4.3</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>4.5</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>5.3</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>1.23</v>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
@@ -4490,16 +4786,16 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>15.3</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>14.8</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>16.5</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>1.078</v>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -4601,40 +4897,40 @@
           <t>大雪地区広域連合</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>6.02</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>6.1</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>5.92</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>5.72</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>5.66</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>5.72</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>5.72</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="19" t="n">
         <v>5.6</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="19" t="n">
         <v>5.28</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K12" s="19" t="n">
         <v>5.39</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="L12" s="19" t="n">
         <v>5.31</v>
       </c>
-      <c r="M12" s="18" t="n">
+      <c r="M12" s="19" t="n">
         <v>5.25</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
@@ -4649,40 +4945,40 @@
           <t>北海道</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>4.66</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>4.57</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>4.5</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>4.47</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>4.49</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>4.48</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>4.47</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="19" t="n">
         <v>4.44</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="19" t="n">
         <v>4.41</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K13" s="19" t="n">
         <v>4.44</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="L13" s="19" t="n">
         <v>4.46</v>
       </c>
-      <c r="M13" s="18" t="n">
+      <c r="M13" s="19" t="n">
         <v>4.49</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -4697,40 +4993,40 @@
           <t>全国</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>4.04</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>4.04</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>4.03</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>4.08</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>4.1</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>4.15</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>4.19</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="19" t="n">
         <v>4.18</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="19" t="n">
         <v>4.19</v>
       </c>
-      <c r="K14" s="18" t="n">
+      <c r="K14" s="19" t="n">
         <v>4.2</v>
       </c>
-      <c r="L14" s="18" t="n">
+      <c r="L14" s="19" t="n">
         <v>4.26</v>
       </c>
-      <c r="M14" s="18" t="n">
+      <c r="M14" s="19" t="n">
         <v>4.3</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
@@ -4745,37 +5041,37 @@
           <t>差（大雪－全国・ポイント）</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>1.98</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>2.06</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>1.89</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>1.64</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>1.56</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>1.57</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="19" t="n">
         <v>1.53</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>1.42</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>1.09</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="19" t="n">
         <v>1.19</v>
       </c>
-      <c r="L15" s="18" t="n">
+      <c r="L15" s="19" t="n">
         <v>1.05</v>
       </c>
       <c r="M15" s="24" t="n">
@@ -4793,40 +5089,40 @@
           <t>指数（全国＝1.00）</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>1.49</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1.51</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>1.47</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>1.4</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>1.38</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>1.38</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="19" t="n">
         <v>1.37</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="19" t="n">
         <v>1.34</v>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="19" t="n">
         <v>1.26</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="19" t="n">
         <v>1.28</v>
       </c>
-      <c r="L16" s="18" t="n">
+      <c r="L16" s="19" t="n">
         <v>1.25</v>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="19" t="n">
         <v>1.22</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
@@ -5205,17 +5501,814 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>4　要介護度別の受給率の推移（％。分母は第1号被保険者数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>（1）施設サービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>要介護度</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>H28</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M37" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>合計（施設サービス）</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度4.3％から令和7年度3.7％へ0.6ポイント低下。低下分のほぼ全てが要介護5に由来する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>（2）在宅サービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>要介護度</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>H28</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M48" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>合計（在宅サービス）</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度10.3％から令和7年度11.2％へ0.9ポイント上昇。要介護1・4・5の増加が牽引している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="56" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>注1）施設サービスの受給率の低下は要介護5に集中している（1.2％→0.7％で41.7％減）。要介護3・4は横ばいで、要介護1・2にも大きな変化はない。注2）在宅サービスの受給率は要介護5が0.3％→0.6％（2.0倍）、要介護4が0.5％→0.8％（1.6倍）と重度者で大きく上昇している。施設の要介護5の減少分と在宅の要介護4・5の増加分が対応しており、重度者が施設から在宅へ移行したことを直接示している。注3）要支援1・2の在宅受給率が平成29年度から平成30年度にかけて低下しているのは、介護予防訪問介護・介護予防通所介護が介護予防・日常生活支援総合事業へ移行したことによる。注4）在宅の合計受給率11.2％はD41の在宅サービス受給率と一致し、施設3.7％に居住系1.6％を加えた5.3％はD41の施設および居住系サービス受給率と一致する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>注1）受給率は受給者数を第1号被保険者数で除した値。介護サービス利用率（06シート）は受給者数を認定者数で除した値であり、分母が異なる別の比率である。注2）D41-aは月次データであり、本シートでは年度（4月〜翌年3月）で平均した。令和7年度は令和8年1月までの10か月平均である。注3）要支援・要介護者1人あたり定員は介護サービス情報公表システム及び月報による。定員そのものは変わらなくても認定者が増えれば低下するため、供給の実数の変化（06シート1）と併せて読む。注4）第9期計画・素案第9稿とも本シートの指標を掲載していない。第2章に新設することを推奨する（修正指示書A-11・A-13）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A29:N29"/>
+  <mergeCells count="4">
+    <mergeCell ref="A50:N50"/>
     <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A53:N53"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5303,22 +6396,22 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>5094</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>3952</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>3943</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>4039</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>4105</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="28" t="n">
         <v>0.039</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -5333,22 +6426,22 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>4562</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>4547</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>4672</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>4359</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>4440</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="28" t="n">
         <v>-0.024</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -5363,22 +6456,22 @@
           <t>地域密着型介護老人福祉施設</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>674</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>1662</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>1715</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>1712</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>1890</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="28" t="n">
         <v>0.137</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -5393,22 +6486,22 @@
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>1032</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>985</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>1128</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>1139</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>1188</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="28" t="n">
         <v>0.206</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -5423,22 +6516,22 @@
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>2549</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>2750</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>2947</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>2445</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>2461</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="29" t="n">
         <v>-0.105</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -5453,22 +6546,22 @@
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>2317</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>2602</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>2706</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>3287</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>3976</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="30" t="n">
         <v>0.528</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -5483,22 +6576,22 @@
           <t>訪問看護</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>314</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>463</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>451</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>555</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="30" t="n">
         <v>0.6920000000000001</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -5513,22 +6606,22 @@
           <t>通所介護</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>1619</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>694</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>697</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>669</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>675</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="28" t="n">
         <v>-0.027</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -5548,19 +6641,19 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>777</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>623</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>719</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>567</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="29" t="n">
         <v>-0.27</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -5575,22 +6668,22 @@
           <t>通所リハビリテーション</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>1378</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>1209</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>1328</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>1425</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="30" t="n">
         <v>0.386</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -5605,22 +6698,22 @@
           <t>小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>1549</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>1802</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>1731</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>1989</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>2155</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="28" t="n">
         <v>0.196</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -5635,22 +6728,22 @@
           <t>福祉用具貸与</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>429</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>516</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>518</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>662</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>704</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="30" t="n">
         <v>0.364</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -5665,22 +6758,22 @@
           <t>介護予防支援・居宅介護支援</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>1004</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>1023</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>1163</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>1229</v>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="28" t="n">
         <v>0.224</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -5695,19 +6788,19 @@
           <t>定期巡回・随時対応型訪問介護看護</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -5896,6 +6989,1610 @@
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>第10期の代表KPI16項目の妥当性</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>素案第9稿 資料編 資料1の定義に対し、データ源の確保状況、基準値の算定可否、本検証の結果との整合、実行可能性を評価した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>データ源</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>データ源の状況</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>基準値</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>本検証の結果との整合</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>評価と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>年齢調整済要介護認定率</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>年齢構成の影響を調整した認定率</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5-a／認定台帳</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>確保</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>要決定</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>本検証で75歳以上の認定率が平成30年3月末35.3％から令和8年3月末33.5％へ、85歳以上が令和2年3月末63.7％から61.6％へ低下していることを確認した。全体では＋1.0ポイント上昇しており、年齢調整の必要性が裏付けられた。</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。ただし見える化には2系列あり、【注目する地域のみ】18.4％は他地域と比較できない。【他地域と比較】16.7％の採用を推奨（修正指示書A-10）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>要介護3以上認定率</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>要介護3〜5の第1号認定者割合</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>見える化B4-a</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>確保</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>算定済</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>令和8年3月末6.3％。第9期の代表KPI②と定義が実質同一で接続できる。ただし要介護3〜5の実数は564人（令和6年3月末）→580人（令和8年3月末）と増加しており、率の改善は分母の動きにも依存する。</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。実数と率を併記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>75歳以上新規認定率</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>年度内に初回認定を受けた75歳以上の割合</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>認定台帳（新規認定者数）</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>未算定</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>見える化には新規認定者数の系列がなく、認定台帳からの抽出が必要。本検証で75歳以上の認定率（ストック）は低下していることを確認したが、新規認定率（フロー）は把握できていない。</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>H01の要因分析として有用。認定台帳から新規認定者数を年度別・年齢別に抽出できるか確認を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>フレイル該当割合</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>固定した判定ロジックによる該当割合</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>確保</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>算定済</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度19.1％。基準値18.5％（令和4年度）との差＋0.6ポイントは統計的に有意でない。</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。目標設定は第9期の2時点外挿を踏襲せず、信頼区間を併記して「有意な改善」又は「水準の維持」で設定する（修正指示書B-14）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上の社会参加率</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>本人単位で月1回以上参加する割合</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>確保</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>算定済</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>社会参加6区分の合成指標で令和7年度36.0％（東川38.2％・美瑛35.4％・東神楽34.8％）。通いの場単独では8.8％。第9期の代表KPI④は通いの場のみで、合成指標とは接続しない。</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。第9期との継続性を確保するため、通いの場単独系列も併記する（修正指示書C-4）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>在宅生活継続困難割合</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>現状の支援では在宅継続が難しい人の割合</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>確保（仕様書の対象調査）</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>第9期は12事業所・利用者91人。要介護度別に分割すると各群20〜30人となり比較に耐えない。本検証で要介護4・5の在宅受給率が上昇していることを確認しており、指標の重要性は高い。</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。第10期の集計を受領後に基準値を算定する。標本規模を踏まえ、要介護度別の比較は信頼区間を併記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>主介護者の高負担割合</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>高負担区分に該当する主介護者割合</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>未確保</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>算定不可</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査は仕様書４（３）の対象4調査（在宅生活改善・居所変更・介護人材・健康とくらし）に含まれておらず、新たな調査の企画・設計・配布・回収も業務範囲外とされている。</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>データ源の確保が前提。実施されない場合は、健康とくらしの調査の介護者関連設問又は在宅生活改善調査の家族等介護者の意向・負担の項目への振替を検討する（修正指示書A-9）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>介護離職懸念・就労継続困難割合</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>就労継続が難しい就労中主介護者の割合</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>未確保</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>算定不可</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>H07と同じ。第9期計画の在宅介護実態調査（回答37人）では離職者が1〜2人にとどまり、そもそも標本規模が指標化に耐えない。</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>補完KPIであるため、代替が難しい場合は指標から外す判断もあり得る。在宅生活改善調査の「家族等介護者の就労継続」項目での代替を検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>H09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>退院時支援調整実施率</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>調整を要する退院者への調整完了割合</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>3町の地域包括支援センターの業務記録</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>様式整備が必要</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>未算定</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>第9期に実績がなく、3町の記録様式も統一されていない可能性が高い。東川町は重層的支援推進室に地域包括支援センターを内包し、美瑛町・東神楽町とは体制が異なる。</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>指標の方向は妥当だが、令和9年度からの実測には共通様式の整備が前提。初年度は「様式整備と試行」を管理指標とし、基準値の設定は令和10年度からとすることを検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>認知症相談から支援接続までの適時率</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>標準日数内に初回支援へ接続した割合</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>3町の地域包括支援センターの業務記録</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>様式整備が必要</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>未算定</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>H09と同じ。「標準日数」の定義が3町で統一されていない。</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>H09と同様の扱い。標準日数の定義を3町で合意することが先決。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>供給不足を理由とする住替え割合</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>サービス・住まい不足を主因とする居所変更割合</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>居所変更実態調査</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>確保（仕様書の対象調査）</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>第9期は21施設が回答し「居所変更した理由」を把握している。本検証で要介護5の施設受給率が41.7％低下していることを確認しており、指標の重要性は高い。</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。第9期の「居所変更した理由」の選択肢に供給不足に相当する区分があるか、調査票で確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>必要サービス未充足率</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>必要と判断されたが提供できなかった割合</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>事業所実態調査</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>未確保</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>算定不可</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>事業所実態調査は仕様書の対象4調査に含まれない。一方、本検証で令和6年度の未利用認定者が504人（認定者の25.7％）に達し、介護サービス利用率が7.9ポイント低下していることを確認した。供給制約の検証は第10期の中心論点であり、代替手段の確保が不可欠。</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>代理指標の候補：①認定者のうち居宅サービス計画未作成の者の割合、②ケアプラン作成時にサービスを確保できなかった件数（居宅介護支援事業所への照会）、③特別養護老人ホームの入所申込者数。①は保険者の統計から算定できる（修正指示書A-7・A-12）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>職種別欠員率</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>必要常勤換算数に対する不足割合</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>介護人材実態調査</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>設問追加が必要</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>介護人材実態調査は仕様書の対象4調査に含まれるが、第9期の同調査は職員数・男女比・就業形態・年齢構成・在職年数・直前の職場・資格・採用退職・勤務時間を把握しており、「必要常勤換算数」の設問は確認できない。</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>第10期の調査票に必要数の設問があるか確認する。ない場合は「採用者数－退職者数」の差分や求人継続期間等での代替を検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>採用者1年定着率</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>採用後12か月時点で在職する割合</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>介護人材実態調査</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>設問追加が必要</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>第9期の同調査は年間の採用者数・退職者数を把握しているが、採用者の12か月後の在職を追跡する設問は確認できない。</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>H13と同じ。追跡ができない場合は「年間離職率」（退職者数÷期首在職者数）での代替を検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>給付費の計画乖離率</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>計画給付費に対する実績差</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>介護保険特別会計決算／見える化</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>確保</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>算定可</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>第9期については必要保険料月額ベースで算定できる（令和6年度－5.3％、令和7年度－0.8％。基準額6,400円との対比）。決算ベースの算定には令和6〜8年度の決算が必要。</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>採用は妥当。計画値の定義（標準給付費見込額か総給付費か）を確定する。第9期計画は標準給付費見込額（令和6年度3,127,780,210円）と総給付費（同2,924,324,000円）の両方を掲載しており、いずれを分母とするか明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>災害・感染症時の必須サービス継続率</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>必須業務を継続・代替できた割合</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>事業所実態調査</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>未確保</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>算定不可</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>H12と同じ。実績としての「災害・感染症時」の事象がなければ測定機会自体がない。</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>実績指標ではなく体制指標（BCP策定率、訓練実施率、相互応援協定の締結数）への組替えを検討する。BCP策定は令和6年度から義務化されており、指定権者である北海道・広域連合が策定状況を把握できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2　データ源の確保状況のまとめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>該当ID</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>確保済み（基準値も算定済み）</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>H02・H04・H05・H15</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>第1回委員会の資料に基準値を掲載できる。H01は系列の決定後に算定する。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>確保済み（第10期調査の受領待ち）</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>H06・H11・H13</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>仕様書の対象4調査に含まれる。集計データの受領後に基準値を算定する。H13は必要常勤換算数の設問の有無を確認する。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>系列の決定が必要</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>【他地域と比較】16.7％の採用を推奨（修正指示書A-10）。</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>データ源が未確保</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>H07・H08・H12・H16</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査（H07・H08）と事業所実態調査（H12・H16）が仕様書の対象外。業務範囲の決定又は代理指標への振替が必要（修正指示書A-7・A-9）。</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>業務記録の様式整備が必要</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>H09・H10</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>3町の地域包括支援センターの記録様式を統一する必要がある。初年度は様式整備を管理指標とし、基準値の設定を令和10年度からとする案を検討する。</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>設問の追加・代替が必要</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>採用者の12か月後の在職を追跡する設問がない。年間離職率での代替を検討する。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>認定台帳からの抽出が必要</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>新規認定者数の年度別・年齢別の抽出可否を確認する。</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>注1）16項目のうち、令和9年度当初から実測できる見通しが立っているのは8項目（H01・H02・H04・H05・H06・H11・H13・H15）である。残り8項目は、業務範囲の決定（4項目）、様式整備（2項目）、設問追加又は代替（1項目）、台帳抽出（1項目）を要する。注2）第9期は5基本目標19施策に対し代表KPIが4項目で評価範囲が不足していた。第10期の16項目は範囲としては妥当だが、半数について測定手段が未確定であり、このまま計画に掲載すると第9期と同じ「評価不能」の状態を招く。第1回委員会で測定手段まで含めて決定することを推奨する。注3）「基準値」欄の「算定済」は本検証で値を算定したもの、「算定可」は資料受領後に算定できるもの、「未受領」は調査データの受領待ち、「算定不可」はデータ源が確保できていないものを指す。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>業務仕様書の業務内容と成果物の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>仕様書４（１）〜（12）及び５（業務スケジュール）に対する現時点の対応状況。本業務は令和8年8月着手のため、多くは着手前であるが、要件の見落としがないかを確認した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の業務内容</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>求められている内容</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>対応済みの成果物</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>未対応・留意事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="88" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>制度改正等の整理</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>国及び北海道の制度改正、通知、各種指針等の動向を把握し、第10期計画へ反映すべき事項を整理。反映すべき制度改正事項及び留意事項について情報提供及び技術的助言。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>妥当性検証報告書 07シート（国の基本指針との整合）。第10期基本指針案の9つの方向への素案の対応状況を整理済み。</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針は告示前。北海道の制度改正・通知の把握が未着手。本作業環境から厚生労働省・北海道のサイトを取得できないため、発注者から資料をご提供いただくか、別環境での取得が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の評価・検証</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の各種施策、介護保険給付実績、地域支援事業、介護予防施策等の実施状況を整理し、成果及び課題を分析。第10期へ反映すべき事項を取りまとめ。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>妥当性検証報告書 全15シート。代表KPI4項目の評価、19施策の構造評価、給付費・保険料の検証、施策体系新旧対照表。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>令和6〜8年度の施策・事業実績、地域支援事業の実績が未受領のため、施策単位の評価ができていない。第3章の記述は資料受領後に確定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>実施済み調査結果の集計・分析</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>対象4調査（①在宅生活改善調査 ②居所変更実態調査 ③介護人材実態調査 ④健康とくらしの調査）について単純集計及び必要なクロス集計を行い、見える化・介護給付実績・人口推計等と組み合わせた分析を実施。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>④健康とくらしの調査は個票CSVを受領し、20指標の集計・年齢階級別・町別のクロス集計、社会参加の合成指標の算出（36.0％）、令和4年との有意差検定を完了（図表集08・09シート）。</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>①②③は未受領。受領後に集計・クロス集計・見える化との組合せ分析を行う。なお在宅介護実態調査は対象4調査に含まれておらず、H07・H08のデータ源がない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>現状分析及び地域課題の整理</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>人口、高齢者人口、認定者数、介護給付実績、サービス利用状況、地域支援事業の実施状況等を分析。見える化・JAGES・国道の統計を活用し、必要に応じ全国平均、北海道平均及び【類似保険者】との比較分析。【構成町別及び日常生活圏域等】の地域特性を踏まえた分析。2040年を見据えた提供体制、人材確保、地域包括ケア、給付適正化の課題を整理。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>図表集 全24シート112点。全国・北海道との比較は受給率・給付月額・利用日数回数・認定率で実施済み。2040年を見据えた分析は16・17シート（町別将来推計・担い手の推移）。</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>【要対応1】類似保険者との比較分析が未実施。見える化の類似保険者比較の出力が受領データにない。【要対応2】日常生活圏域別の分析が未実施。圏域別（美瑛町4圏域）のデータが未受領。圏域設定そのものの妥当性にも論点がある（12シートC-9）。【要対応3】町別分析は第9期計画の掲載値に依存しており、見える化の町別出力が未受領。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>将来推計</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画期間及び2040年を見据えた人口、高齢者人口、認定者数、サービス利用者数、見込量、給付費、保険料の推計。国の推計ツール及び見える化を活用。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>自然体推計の計算過程確認シートを受領し、素案の数値との一致を確認済み（保険料6,237.77円、総給付費R9 3,056.7百万円ほか）。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算が未着手。基金残高・収納率が未受領のため保険料の確定試算ができない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>計画書の作成</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>骨子案、計画素案、計画最終案及び概要版原稿を作成。【国の基本指針、北海道介護保険事業支援計画及び構成町が策定する高齢者保健福祉計画との整合】を図り、地域特性を踏まえた内容とする。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>素案第9稿の精査、修正指示書45件、施策体系新旧対照表、図表番号一覧（本文への差し込み位置）。</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>【要対応】北海道介護保険事業支援計画（本編）が未入手のため整合確認が概括にとどまる（08シート）。構成町の高齢者福祉計画との整合には重大な不整合がある（09シート）。概要版原稿は未着手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>計画策定支援</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>構成町との協議、計画内容の調整及び計画案の修正等の支援。指示に基づく計画原稿の修正、図表の更新その他技術的支援。</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>確認依頼書（第2版）、施策体系新旧対照表、図表集の更新体制（すべて生成スクリプトで再現可能）。</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>3町との協議は未着手。3町の第10期検討資料・策定工程・担当課が未受領。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>各種会議への技術的支援</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>運営協議会等で求めがあった場合の技術的助言。会議資料原案、図表、グラフ、分析資料及び説明用データの作成支援。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>図表集（加工可能なExcel形式・112点）、妥当性検証報告書、確認依頼書。</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>第1回委員会の日程・審議事項・資料提出期限が未確定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>(9)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>パブリックコメント支援</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>素案の修正案の作成、提出意見の分類・整理、意見に対する考え方の原案作成、計画への反映に関する技術的助言。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>令和9年1月の工程。パブリックコメント期間が未確定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>(10)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>成果品の作成</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>計画書（A4判表紙レザック本文1色 100頁程度）200部。計画書及び概要版の電子データ。分析資料、推計資料、図表、グラフ、クロス集計表等の電子データ。打合せ資料、会議資料原案。図表・グラフ・統計資料も発注者が加工可能な形式で納品。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>図表集は本文1色（白黒）を前提としたパターン塗り・線種・マーカーで作図しており、「本文1色」の仕様に適合。すべてExcel形式で加工可能。生成スクリプトも提供する。</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>本文100頁程度に対する章別ページ配分が未定（修正指示書B-4）。図表は本文掲載96点・資料編12点で、配分の決定が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>(11)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>成果品の帰属</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>著作権は引渡しをもって発注者に帰属。</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>生成スクリプト及び出力ファイルはすべて納品対象とする。</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>仕様書に定めのない事項又は疑義は協議のうえ決定。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>確認依頼書（第2版）で委員会決定事項6件・事務局確認事項15件を提示。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>特に事業所実態調査の取扱い（業務範囲の疑義）は早期の協議が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2　業務スケジュールとの対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の業務内容</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>現時点の状況</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>留意事項</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>業務着手、キックオフ会議、第9期計画の評価・検証開始、各種資料整理</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の評価・検証は先行して実施済み（妥当性検証報告書15シート）。資料整理も先行。</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議の日程が未確定。確認依頼書の6件の決定事項は同会議までに整理が必要。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>実施済み調査（4調査）の集計・分析、介護給付実績分析、人口推計、現状分析</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査は完了。介護給付実績分析は図表集24シート112点で先行。人口推計は見える化の出力を整理済み。</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>残り3調査のデータが未受領。9月の工程に間に合わせるには8月中の受領が必要。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>地域課題整理、将来推計、骨子案作成、構成町との協議・調整</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>地域課題は妥当性検証報告書で整理済み。骨子は素案第9稿が先行している。</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>3町との協議の窓口・日程が未確定。共通指標の合意（12シートC-10）は10月までに必要。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>令和8年11月</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>構成町意見反映、計画骨子の整理</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>令和8年12月</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>計画素案作成、見込量及び保険料推計、令和9年度予算作成支援</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>素案は第9稿まで作成済み。修正指示書45件で第10稿の方向を整理。</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>基金残高・収納率・所得段階別被保険者数が未受領のため保険料推計ができない。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>令和9年1〜3月</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>パブリックコメント支援、最終案作成、計画書・概要版完成、成果品納品</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>パブリックコメント期間、印刷スケジュールが未確定。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>注1）仕様書５は「受託者は各工程終了後、発注者が指定する期日までに成果物を提出し、発注者の確認を受けた上で次工程へ進む」と定めているが、工程表・成果物レビュー管理表にこのゲートが明示されていない（修正指示書B-9）。注2）仕様書は人口推計・現状分析を9月としているが、工程表のNo.15「人口・世帯の将来推計」は令和8年10月1日開始となっている。前倒しの可否を協議する。注3）本検証の時点で工程を先行できているのは、第9期計画の評価・検証、健康とくらしの調査の集計・分析、介護給付実績分析、人口推計の整理である。一方、類似保険者との比較分析と日常生活圏域別の分析は、仕様書４（４）が明示的に求めているにもかかわらず未着手であり、必要なデータの受領を要する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6164,27 +8861,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>代表KPI①の評価は「目標未達」と「推計を下回った」の二面がある</t>
+          <t>認定率は全体では上昇したが、年齢層をそろえると低下している</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の目標は令和5年度実績20.8％の維持。同計画の推計値は令和8年度22.0％。実績は令和8年3月末21.8％（北海道21.7％、全国20.2％）。平成30年3月末からの上昇幅は大雪＋1.0ポイントに対し北海道・全国はいずれも＋2.2ポイント。</t>
+          <t>見える化B4-a・B4-d・B4-eの合計認定率（各年3月末）は、全体が平成30年20.8％→令和8年21.8％で＋1.0ポイントである一方、75歳以上は35.3％→33.5％で▲1.8ポイント、85歳以上は令和2年63.7％→令和8年61.6％で▲2.1ポイント。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>目標（20.8％維持）に対しては1.0ポイント未達。一方、自らの推計（22.0％）は0.2ポイント下回り、上昇幅は全国・北海道の半分にとどまる。第3章の評価をどちらの基準で書くかで結論が変わる。</t>
+          <t>全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>第3章第4節に「目標比」と「推計比」「全国比」の3つの評価軸を併記する。第10期は年齢調整済の水準で評価する（H01）。</t>
+          <t>第3章第4節に「目標比」「推計比」「全国比」「年齢層別」の4つの評価軸を併記する。H01を年齢調整済認定率へ改める最大の根拠がここにある。第2章に75歳以上・85歳以上の認定率の推移を新設する。</t>
         </is>
       </c>
     </row>
@@ -6371,7 +9068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6804,17 +9501,256 @@
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>3　年齢層別にみた認定率（各年3月末・％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>増減</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>合計認定率（第1号被保険者）</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>＋1.0</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>第9期のKPI①はこの系列。目標（20.8％の維持）に対し1.0ポイント未達。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>合計認定率（75歳以上）</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>▲1.8</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>平成30年3月末から一貫して低下している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>合計認定率（85歳以上）</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>▲2.1</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>令和2年3月末から令和5年3月末に3.6ポイント低下し、その後1.5ポイント戻している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>認定率（北海道）</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>＋2.2</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>全体系列のみ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>認定率（全国）</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>＋2.2</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>全体系列のみ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>注）全体の認定率が上昇する一方で75歳以上・85歳以上の認定率が低下しているのは、第1号被保険者に占める75歳以上・85歳以上の構成比が高まったためである。同一年齢層でみれば認定率は改善しており、第9期の介護予防の取組の成果は未調整の認定率には表れない。これがH01を年齢調整済認定率へ改める最大の根拠となる。▲は低下（改善）を表す。85歳以上の増減は令和2年3月末との比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>注1）「目標値設定の考え方」は第9期介護保険事業計画 第1章第6節1（1）（2）からの引用。注2）①の実績は見える化P2の各年3月末基準。第9期計画の基準値20.8％は各年9月分基準であり、基準月が異なるため厳密には接続しない（修正指示書 確認事項）。注3）③④の実績は令和7年度 健康とくらしの調査（JAGES調査）。④の基準値7.3％は第9期計画 第2章第3節（2）の掲載値と一致。注4）②の要介護3〜5の実数は見える化P2による（令和6年3月末213＋206＋145＝564人、令和8年3月末212＋213＋155＝580人）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A20:H20"/>
+  <mergeCells count="4">
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6910,22 +9846,22 @@
           <t>広域計　第9期計画（住基・コーホート）</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>27752</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>27614</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>27448</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>26767</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>24717</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>22125</v>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
@@ -6936,22 +9872,22 @@
           <t>広域計　見える化（国勢調査・社人研）</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>27303</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>27102</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>26876</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>25969</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>23582</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>21058</v>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
@@ -6962,22 +9898,22 @@
           <t>広域計　乖離率（％）</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>1.9</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>2.1</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>3.1</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>4.8</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>5.1</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -6992,22 +9928,22 @@
           <t>東川町　第9期計画（住基・コーホート）</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>8631</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>8703</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>8747</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>8924</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>9016</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <v>8610</v>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
@@ -7018,22 +9954,22 @@
           <t>東川町　見える化（国勢調査・社人研）</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>8233</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>8213</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>8182</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>8059</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>7607</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>7088</v>
       </c>
       <c r="H10" s="6" t="inlineStr"/>
@@ -7044,22 +9980,22 @@
           <t>東川町　乖離率（％）</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>4.8</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>6.9</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <v>18.5</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <v>21.5</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -7074,22 +10010,22 @@
           <t>美瑛町　第9期計画（住基・コーホート）</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>9323</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>9171</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>9021</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>8419</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>7050</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>5807</v>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -7100,22 +10036,22 @@
           <t>美瑛町　見える化（国勢調査・社人研）</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>9048</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>8893</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>8746</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>8160</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>6851</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="12" t="n">
         <v>5681</v>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -7126,22 +10062,22 @@
           <t>美瑛町　乖離率（％）</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>3.1</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>3.1</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>3.2</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>2.9</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <v>2.2</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -7156,22 +10092,22 @@
           <t>東神楽町　第9期計画（住基・コーホート）</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>9798</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>9740</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>9680</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>9424</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>8651</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <v>7708</v>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -7182,22 +10118,22 @@
           <t>東神楽町　見える化（国勢調査・社人研）</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>10022</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>9996</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>9947</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>9750</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>9124</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <v>8289</v>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -7208,22 +10144,22 @@
           <t>東神楽町　乖離率（％）</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>-2.2</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="13" t="n">
         <v>-2.6</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="13" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <v>-7</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -7288,22 +10224,22 @@
           <t>65歳以上人口　第9期計画</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="14" t="n">
         <v>9243</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>9289</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>9296</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>9304</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>9621</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>9216</v>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -7315,22 +10251,22 @@
           <t>65歳以上人口　見える化</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B22" s="14" t="n">
         <v>9346</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <v>9323</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>9320</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>9310</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="14" t="n">
         <v>9633</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="14" t="n">
         <v>9239</v>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -7346,22 +10282,22 @@
           <t>高齢化率　第9期計画（％）</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="14" t="n">
         <v>33.3</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <v>33.6</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>33.9</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>34.8</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="14" t="n">
         <v>38.9</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>41.7</v>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
@@ -7373,22 +10309,22 @@
           <t>高齢化率　見える化（％）</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>34.2</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="14" t="n">
         <v>34.4</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>34.7</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>35.9</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="14" t="n">
         <v>40.8</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="14" t="n">
         <v>43.9</v>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -7442,13 +10378,13 @@
           <t>第9期計画の推計（合計）</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="14" t="n">
         <v>2020</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="14" t="n">
         <v>2056</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>2076</v>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -7467,10 +10403,10 @@
           <t>実績（見える化P2、年度末）</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="14" t="n">
         <v>1962</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="14" t="n">
         <v>1984</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -7494,10 +10430,10 @@
           <t>差（実績－計画）</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="B30" s="14" t="n">
         <v>-58</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="14" t="n">
         <v>-72</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -7521,13 +10457,13 @@
           <t>出現率　第9期計画の推計（％）</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="14" t="n">
         <v>21.5</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="14" t="n">
         <v>21.8</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <v>22</v>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -7546,13 +10482,13 @@
           <t>認定率　実績（％、見える化P2）</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B32" s="14" t="n">
         <v>21.2</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C32" s="14" t="n">
         <v>21.4</v>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="14" t="n">
         <v>21.8</v>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
@@ -7682,28 +10618,28 @@
           <t>必要保険料月額（見える化）</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>6051</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>5715</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>6306</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>6354</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>6143</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>6337</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="12" t="n">
         <v>6063</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <v>6352</v>
       </c>
       <c r="J6" s="6" t="inlineStr"/>
@@ -7714,28 +10650,28 @@
           <t>保険料基準額（条例）</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>6077</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>6077</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>6077</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>6300</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>6300</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>6300</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="12" t="n">
         <v>6400</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="12" t="n">
         <v>6400</v>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -7746,28 +10682,28 @@
           <t>差（基準額－必要額）</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>362</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>-229</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>157</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n">
         <v>-37</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="15" t="n">
         <v>337</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>48</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -7782,28 +10718,28 @@
           <t>必要額のうち在宅</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>2156</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>2126</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>2195</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>2351</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>2379</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <v>2490</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="12" t="n">
         <v>2346</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <v>2596</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -7818,28 +10754,28 @@
           <t>必要額のうち居住系</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>818</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>821</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>895</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>861</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>787</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="12" t="n">
         <v>687</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>754</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -7854,28 +10790,28 @@
           <t>必要額のうち施設</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>2272</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>2178</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>2323</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>2299</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>2175</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="12" t="n">
         <v>2273</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="12" t="n">
         <v>2231</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>2207</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -7890,28 +10826,28 @@
           <t>必要額のうちその他</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>805</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>590</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>893</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>843</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>809</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>787</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="12" t="n">
         <v>799</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="12" t="n">
         <v>795</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -8175,7 +11111,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -8183,7 +11119,7 @@
           <t>当麻町</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>6800</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
@@ -8191,7 +11127,7 @@
       <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -8199,7 +11135,7 @@
           <t>愛別町</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>6706</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -8207,7 +11143,7 @@
       <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -8215,7 +11151,7 @@
           <t>鷹栖町</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>6700</v>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
@@ -8223,7 +11159,7 @@
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -8231,7 +11167,7 @@
           <t>中川町</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>6550</v>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
@@ -8239,15 +11175,15 @@
       <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>大雪地区広域連合</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>6400</v>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
@@ -8255,7 +11191,7 @@
       <c r="F10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -8263,7 +11199,7 @@
           <t>比布町</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>6300</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -8271,7 +11207,7 @@
       <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -8279,7 +11215,7 @@
           <t>旭川市</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>6190</v>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
@@ -8287,7 +11223,7 @@
       <c r="F12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -8295,7 +11231,7 @@
           <t>富良野市</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>6000</v>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
@@ -8303,7 +11239,7 @@
       <c r="F13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -8311,7 +11247,7 @@
           <t>上川町</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>6000</v>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
@@ -8319,7 +11255,7 @@
       <c r="F14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -8327,7 +11263,7 @@
           <t>剣淵町</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>6000</v>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -8335,7 +11271,7 @@
       <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -8343,7 +11279,7 @@
           <t>下川町</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>6000</v>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -8351,7 +11287,7 @@
       <c r="F16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -8359,7 +11295,7 @@
           <t>和寒町</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>5950</v>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
@@ -8367,7 +11303,7 @@
       <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -8375,7 +11311,7 @@
           <t>美深町</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>5900</v>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -8383,7 +11319,7 @@
       <c r="F18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -8391,7 +11327,7 @@
           <t>中富良野町</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>5700</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -8399,7 +11335,7 @@
       <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -8407,7 +11343,7 @@
           <t>南富良野町</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="12" t="n">
         <v>5700</v>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -8415,7 +11351,7 @@
       <c r="F20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -8423,7 +11359,7 @@
           <t>名寄市</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>5400</v>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -8431,7 +11367,7 @@
       <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -8439,7 +11375,7 @@
           <t>上富良野町</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="12" t="n">
         <v>5400</v>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -8447,7 +11383,7 @@
       <c r="F22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -8455,7 +11391,7 @@
           <t>占冠村</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>5100</v>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -8463,7 +11399,7 @@
       <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -8471,7 +11407,7 @@
           <t>士別市</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="12" t="n">
         <v>5025</v>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -8479,7 +11415,7 @@
       <c r="F24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -8487,7 +11423,7 @@
           <t>幌加内町</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -8495,7 +11431,7 @@
       <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -8503,7 +11439,7 @@
           <t>音威子府村</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="12" t="n">
         <v>3600</v>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -8552,7 +11488,7 @@
           <t>保険者数</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>21保険者</t>
         </is>
@@ -8576,7 +11512,7 @@
           <t>単純平均</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>5,829.6円</t>
         </is>
@@ -8600,7 +11536,7 @@
           <t>中央値</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>6,000円</t>
         </is>
@@ -8624,7 +11560,7 @@
           <t>標準偏差</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>725.1円</t>
         </is>
@@ -8648,7 +11584,7 @@
           <t>大雪の順位</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>高い方から5番目</t>
         </is>
@@ -8672,7 +11608,7 @@
           <t>北海道平均との差</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>＋662円</t>
         </is>
@@ -8696,7 +11632,7 @@
           <t>全国平均との差</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>＋175円</t>
         </is>
@@ -8720,7 +11656,7 @@
           <t>旭川市との差</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>＋210円</t>
         </is>
@@ -8783,13 +11719,13 @@
           <t>第1号被保険者1人あたり給付月額（性・年齢調整後）</t>
         </is>
       </c>
-      <c r="C40" s="18" t="n">
+      <c r="C40" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="18" t="n">
+      <c r="D40" s="19" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E40" s="18" t="n">
+      <c r="E40" s="19" t="n">
         <v>1.08</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -8809,13 +11745,13 @@
           <t>要介護認定率（性・年齢調整後）</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n">
+      <c r="C41" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="19" t="n">
         <v>1.07</v>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="19" t="n">
         <v>1.02</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -8835,13 +11771,13 @@
           <t>受給率</t>
         </is>
       </c>
-      <c r="C42" s="18" t="n">
+      <c r="C42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="19" t="n">
         <v>0.97</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="19" t="n">
         <v>1.08</v>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -8861,13 +11797,13 @@
           <t>受給者1人あたり給付月額</t>
         </is>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="19" t="n">
         <v>0.92</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="19" t="n">
         <v>1.06</v>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -8993,28 +11929,28 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>234</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>234</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <v>160</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -9029,28 +11965,28 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="12" t="n">
         <v>240</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -9075,22 +12011,22 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <v>62</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -9105,28 +12041,28 @@
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <v>156</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -9141,28 +12077,28 @@
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>99</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -9177,28 +12113,28 @@
           <t>施設サービス計</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>434</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>474</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>536</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>462</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>462</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="12" t="n">
         <v>462</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="12" t="n">
         <v>462</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>462</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -9213,28 +12149,28 @@
           <t>居住系サービス計</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>271</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>271</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>271</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="12" t="n">
         <v>255</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -9308,28 +12244,28 @@
           <t>合計認定者数（人）</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>1835</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>1842</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>1859</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>1878</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="14" t="n">
         <v>1903</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="14" t="n">
         <v>1921</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="14" t="n">
         <v>1931</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="14" t="n">
         <v>1962</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -9344,28 +12280,28 @@
           <t>合計受給者数（人）</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>1411</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>1515</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>1414</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>1457</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="14" t="n">
         <v>1492</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>1458</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="14" t="n">
         <v>1455</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="14" t="n">
         <v>1458</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -9380,28 +12316,28 @@
           <t>介護サービス利用率（％）</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>82.2</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="14" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="14" t="n">
         <v>75.3</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="I18" s="20" t="n">
         <v>74.3</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -9480,31 +12416,31 @@
           <t>要介護1</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="11" t="n">
         <v>88.3</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="11" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="11" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="F22" s="20" t="n">
+      <c r="F22" s="11" t="n">
         <v>91.7</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="11" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="11" t="n">
         <v>88.8</v>
       </c>
-      <c r="I22" s="20" t="n">
+      <c r="I22" s="11" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="J22" s="20" t="n">
+      <c r="J22" s="11" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -9519,31 +12455,31 @@
           <t>要介護2</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="11" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="11" t="n">
         <v>76.3</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="11" t="n">
         <v>78.7</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="11" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="11" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="11" t="n">
         <v>81</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="11" t="n">
         <v>78.5</v>
       </c>
-      <c r="I23" s="20" t="n">
+      <c r="I23" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="J23" s="20" t="n">
+      <c r="J23" s="11" t="n">
         <v>78.2</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -9558,31 +12494,31 @@
           <t>要介護3</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="11" t="n">
         <v>58.3</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="11" t="n">
         <v>57.9</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="11" t="n">
         <v>61.6</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="11" t="n">
         <v>55.4</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="11" t="n">
         <v>52.8</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="11" t="n">
         <v>57.8</v>
       </c>
-      <c r="H24" s="20" t="n">
+      <c r="H24" s="11" t="n">
         <v>60.4</v>
       </c>
-      <c r="I24" s="20" t="n">
+      <c r="I24" s="11" t="n">
         <v>58.5</v>
       </c>
-      <c r="J24" s="20" t="n">
+      <c r="J24" s="11" t="n">
         <v>61.4</v>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -9597,31 +12533,31 @@
           <t>要介護4</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="11" t="n">
         <v>43.9</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="11" t="n">
         <v>43.8</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="11" t="n">
         <v>42.9</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="11" t="n">
         <v>43.1</v>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="11" t="n">
         <v>47.5</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="11" t="n">
         <v>47.6</v>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="11" t="n">
         <v>51.4</v>
       </c>
-      <c r="I25" s="20" t="n">
+      <c r="I25" s="11" t="n">
         <v>50.1</v>
       </c>
-      <c r="J25" s="20" t="n">
+      <c r="J25" s="11" t="n">
         <v>49.1</v>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -9636,28 +12572,28 @@
           <t>要介護5</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="11" t="n">
         <v>31.3</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="11" t="n">
         <v>32.4</v>
       </c>
-      <c r="D26" s="20" t="n">
+      <c r="D26" s="11" t="n">
         <v>35.8</v>
       </c>
-      <c r="E26" s="20" t="n">
+      <c r="E26" s="11" t="n">
         <v>44.6</v>
       </c>
-      <c r="F26" s="20" t="n">
+      <c r="F26" s="11" t="n">
         <v>46.5</v>
       </c>
-      <c r="G26" s="20" t="n">
+      <c r="G26" s="11" t="n">
         <v>49.2</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="11" t="n">
         <v>49.1</v>
       </c>
-      <c r="I26" s="20" t="n">
+      <c r="I26" s="11" t="n">
         <v>51.1</v>
       </c>
       <c r="J26" s="21" t="n">
@@ -9675,31 +12611,31 @@
           <t>全体</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="11" t="n">
         <v>73.3</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="11" t="n">
         <v>74.3</v>
       </c>
-      <c r="E27" s="20" t="n">
+      <c r="E27" s="11" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="F27" s="20" t="n">
+      <c r="F27" s="11" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="11" t="n">
         <v>76.8</v>
       </c>
-      <c r="H27" s="20" t="n">
+      <c r="H27" s="11" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="I27" s="20" t="n">
+      <c r="I27" s="11" t="n">
         <v>76</v>
       </c>
-      <c r="J27" s="20" t="n">
+      <c r="J27" s="11" t="n">
         <v>77.5</v>
       </c>
       <c r="K27" s="6" t="inlineStr">

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_サービス別の給付動向" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_第10期KPIの妥当性" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_仕様書との適合性" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_確認すべき指標への対応" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,11 +33,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -148,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,27 +211,33 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -597,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -772,12 +780,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第9期基本指針及び第10期基本指針案の記載事項に対する、第9期計画・第10期素案の対応状況を確認する。</t>
+          <t>第9期基本指針及び第10期基本指針案（部会資料の原典）の記載事項に対する、第9期計画・第10期素案の対応状況を確認する。新別表「確認すべき指標・状況」11事項への対応も確認する。</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>素案は概ね整合</t>
+          <t>一部未対応</t>
         </is>
       </c>
     </row>
@@ -794,12 +802,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画の施策の柱との整合を確認する。</t>
+          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画の基本テーマ・8基本目標・評価指標及び上川中部圏域の記載との整合を確認する。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>資料未入手</t>
+          <t>重大な不整合あり</t>
         </is>
       </c>
     </row>
@@ -1182,179 +1190,197 @@
       </c>
       <c r="D34" s="6" t="inlineStr"/>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>17_確認すべき指標への対応</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針に新設される別表「確認すべき指標・状況」11事項への対応状況。</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道高齢者保健福祉計画・介護保険事業支援計画（本編）</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>北海道の施策の柱・数値目標との整合確認</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>08シートの整合確認が概括にとどまる</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
+          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>国の記載事項への網羅性確認</t>
+          <t>施策単位での整合確認</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>07シートは部会資料の報道内容に基づく暫定評価</t>
+          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
+          <t>記載事項への網羅性の最終確認</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
+          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>給付費・地域支援事業費の計画対実績</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>介護給付費準備基金の残高推移</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>04シートの剰余額は概算にとどまる</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>注1）本検証の期間中、厚生労働省（mhlw.go.jp）及び北海道（pref.hokkaido.lg.jp）のサイトは本作業環境のネットワークポリシーにより直接取得できなかった。07・08シートは検索結果として得られた報道・解説記事の記述に基づく暫定評価であり、告示及び計画本編の入手後に再確認を要する。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>注1）第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1・第135回 資料2-1）及び第9期北海道高齢者保健福祉計画・介護保険事業支援計画の本編を受領し、07・08・17シートは原典に基づいて作成した。北海道の計画本編は本文が画像で構成されているため、第4章（計画の方向性）及び第7章第12節（上川中部圏域）の主要頁を目視により読み取っている。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2059,12 +2085,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>出現回数（回）</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>記載密度（回／1万字）</t>
         </is>
@@ -3165,7 +3191,7 @@
       <c r="D5" s="14" t="n">
         <v>4626</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="25" t="n">
         <v>0.639</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3201,7 +3227,7 @@
       <c r="D6" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.468</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3237,7 +3263,7 @@
       <c r="D7" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="25" t="n">
         <v>0.75</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -3273,7 +3299,7 @@
       <c r="D8" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="25" t="n">
         <v>0.8</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -3309,7 +3335,7 @@
       <c r="D9" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="25" t="n">
         <v>0.771</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -5074,7 +5100,7 @@
       <c r="L15" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="M15" s="24" t="n">
+      <c r="M15" s="26" t="n">
         <v>0.95</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -5193,19 +5219,19 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="27" t="n">
         <v>0.104</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="27" t="n">
         <v>0.126</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="27" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="27" t="n">
         <v>0.083</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="27" t="n">
         <v>0.082</v>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
@@ -5232,19 +5258,19 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="27" t="n">
         <v>0.128</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="27" t="n">
         <v>0.129</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="27" t="n">
         <v>0.128</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="27" t="n">
         <v>0.124</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="27" t="n">
         <v>0.123</v>
       </c>
       <c r="G21" s="6" t="inlineStr"/>
@@ -5276,16 +5302,16 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="27" t="n">
         <v>0.033</v>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="27" t="n">
         <v>0.033</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="27" t="n">
         <v>0.032</v>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="27" t="n">
         <v>0.032</v>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -5312,19 +5338,19 @@
           <t>施設サービス計</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="27" t="n">
         <v>0.232</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="27" t="n">
         <v>0.288</v>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="27" t="n">
         <v>0.246</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="27" t="n">
         <v>0.239</v>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="27" t="n">
         <v>0.237</v>
       </c>
       <c r="G23" s="6" t="inlineStr"/>
@@ -5334,7 +5360,7 @@
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="26" t="inlineStr">
+      <c r="N23" s="28" t="inlineStr">
         <is>
           <t>－17.7％</t>
         </is>
@@ -5351,19 +5377,19 @@
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="27" t="n">
         <v>0.083</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="27" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="D24" s="25" t="n">
+      <c r="D24" s="27" t="n">
         <v>0.083</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="27" t="n">
         <v>0.081</v>
       </c>
-      <c r="F24" s="25" t="n">
+      <c r="F24" s="27" t="n">
         <v>0.08</v>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -5390,19 +5416,19 @@
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="27" t="n">
         <v>0.051</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="27" t="n">
         <v>0.062</v>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="27" t="n">
         <v>0.061</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="27" t="n">
         <v>0.051</v>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="27" t="n">
         <v>0.051</v>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -5429,19 +5455,19 @@
           <t>居住系サービス計</t>
         </is>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="27" t="n">
         <v>0.135</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="27" t="n">
         <v>0.146</v>
       </c>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="27" t="n">
         <v>0.144</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="27" t="n">
         <v>0.132</v>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="27" t="n">
         <v>0.131</v>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -5468,19 +5494,19 @@
           <t>通所系サービス計</t>
         </is>
       </c>
-      <c r="B27" s="25" t="n">
+      <c r="B27" s="27" t="n">
         <v>0.14</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="27" t="n">
         <v>0.148</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="27" t="n">
         <v>0.141</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="27" t="n">
         <v>0.15</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="27" t="n">
         <v>0.144</v>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
@@ -5509,7 +5535,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>（1）施設サービス</t>
         </is>
@@ -5856,7 +5882,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>（2）在宅サービス</t>
         </is>
@@ -6411,7 +6437,7 @@
       <c r="F5" s="12" t="n">
         <v>4105</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="30" t="n">
         <v>0.039</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -6441,7 +6467,7 @@
       <c r="F6" s="12" t="n">
         <v>4440</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="30" t="n">
         <v>-0.024</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -6471,7 +6497,7 @@
       <c r="F7" s="12" t="n">
         <v>1890</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="30" t="n">
         <v>0.137</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -6501,7 +6527,7 @@
       <c r="F8" s="12" t="n">
         <v>1188</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="30" t="n">
         <v>0.206</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -6531,7 +6557,7 @@
       <c r="F9" s="12" t="n">
         <v>2461</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="31" t="n">
         <v>-0.105</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -6561,7 +6587,7 @@
       <c r="F10" s="12" t="n">
         <v>3976</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="32" t="n">
         <v>0.528</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -6591,7 +6617,7 @@
       <c r="F11" s="12" t="n">
         <v>555</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="32" t="n">
         <v>0.6920000000000001</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -6621,7 +6647,7 @@
       <c r="F12" s="12" t="n">
         <v>675</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="30" t="n">
         <v>-0.027</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -6653,7 +6679,7 @@
       <c r="F13" s="12" t="n">
         <v>567</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G13" s="31" t="n">
         <v>-0.27</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -6683,7 +6709,7 @@
       <c r="F14" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="32" t="n">
         <v>0.386</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -6713,7 +6739,7 @@
       <c r="F15" s="12" t="n">
         <v>2155</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="30" t="n">
         <v>0.196</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -6743,7 +6769,7 @@
       <c r="F16" s="12" t="n">
         <v>704</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="32" t="n">
         <v>0.364</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -6773,7 +6799,7 @@
       <c r="F17" s="12" t="n">
         <v>1229</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="30" t="n">
         <v>0.224</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -8598,13 +8624,630 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>第10期基本指針の新別表「確認すべき指標・状況」11事項への対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>第135回社会保障審議会介護保険部会 資料2-1（令和8年6月29日）。現行の基本指針には計画策定に当たって確認すべき指標が掲げられていないが、第10期から新たな別表として一覧が示される案となっている。下線・（新）は令和8年度以降に見える化システムの改修等で新たに把握が可能となる指標。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>確認すべき指標・状況</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>内容（指針案）</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>確認の観点</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>対応状況</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>把握方法（指針案）</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>評価と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="88" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>地勢と交通</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>地域特性、交通機関の状況、地理的状況、生活圏 等</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>特に訪問・通所困難地域がある場合は、当該地域へのアクセスや社会資源の状況等を確認</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>各自治体で独自に把握</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>3町のうち東川町・美瑛町が移動支援を施策化しているが（09シート）、広域計画に訪問・通所困難地域の記載がない。美瑛町の4圏域（旭・北西、美馬牛、朗根内）は訪問・通所困難地域に該当する可能性が高く、圏域設定の見直し（修正指示書C-9）と一体で整理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>人口構造</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>年齢三区分人口、高齢化率、世帯数（単身高齢・高齢夫婦のみ）等</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>中長期の需要の傾向を把握するため、過年度及び中長期の推移等を確認</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム／（新）人口メッシュ</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>図表集01〜03・14・16シートで対応済み。人口メッシュは新規のため再出力を依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>人口動態</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>出生数、死亡数、健康寿命 等</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>認定率の推計や医療介護連携に資するため、死亡場所別の死亡数等について過年度の推移等を確認</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム、人口動態統計</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>死亡場所別の死亡数（自宅・施設・医療機関別）は在宅看取りの実態を示す指標で、第10期のH09（退院時支援調整実施率）や医療介護連携の議論の基礎となる。受領データに含まれていないため入手を依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の状況</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>要介護認定者数、要介護認定率 等</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の認定者数、年齢調整後の要介護認定率等について、過年度の推移及び計画と実績の乖離等を確認</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>図表集04〜06シート、検証報告書02・03シートで対応済み。「計画と実績の乖離」は03シートで算定済み（令和6年度－2.9％、令和7年度－3.5％）。年齢調整後の認定率はH01で採用予定だが系列の決定が必要（修正指示書A-10）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス等の利用状況</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>受給者数、受給率、自市町村内の事業所によるサービス提供割合、1人あたり費用額・算定回数、介護サービスの提供状況の地域差を示す指標（介護SCR）等</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>サービス別の受給率、1人あたり費用額、介護SCR等について、過年度の推移や直近の状況等を確認</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム／（新）自市町村内の事業所によるサービス提供割合／（新）介護SCR</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>受給率・1人あたり費用額・算定回数は図表集15・18・19・21・22シートで対応済み。自市町村内の事業所によるサービス提供割合（介護サービス自給率）と介護SCR（性・年齢調整済みレセプト出現比）は新規指標で受領データにない。自給率は3町の住民が旭川市の事業所を利用している度合いを示すため、圏域論の基礎資料となる。再出力を依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス見込量</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス見込量、地域支援事業見込量、家族の就業の状況・意向 等</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>サービス別の見込量について、家族等の就労継続や負担軽減の必要性等も踏まえ、過年度の推移及び計画と実績の乖離等を確認</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>重大な課題</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム、在宅介護実態調査</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>国が把握方法として「在宅介護実態調査」を明示している。同調査は業務仕様書４（３）の対象4調査に含まれておらず、H07・H08のデータ源もない（修正指示書A-9）。基本指針が求める「家族の就業の状況・意向」の把握手段を確保する必要がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>七</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>介護保険施設・事業所の状況</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>介護保険施設・事業所数、利用者数、入所率、稼働率、従事者数 等</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>サービス提供体制の現状や過不足を把握するため、1人あたり施設・事業所数や事業所別の入所率等を確認</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム／（新）入所率、職員数推移</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>定員と要支援・要介護者1人あたり定員は図表集21シートで対応済み。入所率・稼働率は新規指標で受領データにない。入所率は「認定者504人が未利用」（修正指示書A-12）の要因分析に直結するため、H12（必要サービス未充足率）の代理指標として最も有力。再出力を依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>八</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>高齢者向け住まいの状況</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の施設数・戸数、入居者数、定員、要介護者等である入居者の状況 等</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の設置状況及び入居者の状況（65歳以上高齢者数、認定者数、介護サービス受給者数等）を確認</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>適正化システムの改修（新）</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画は住宅型有料老人ホーム4施設・軽費老人ホーム1施設・サービス付き高齢者向け住宅0施設が居所変更実態調査の対象であったことのみ記載し、定員・入居者数は掲載していない。第10期は基本的記載事項に「要介護者等の入居状況」が追加されるため、資料の入手が必須となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>九</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業（日常生活支援・総合事業等）の状況</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>多様なサービス・活動の数・参加者数、通いの場の数・参加者数、地域包括支援センターにおける相談体制の状況、インセンティブ交付金における評価等</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>過年度及び直近の状況を確認</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>重大な課題</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業の実施状況に関する調査、地域包括支援センター運営状況調査</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>国が示す把握方法は総合事業調査であり、大雪の第9期KPI④が用いた日常生活圏域ニーズ調査ではない。北海道の第9期KPI（通いの場への参加率3.94％→5.37％以上）も総合事業調査ベースであり、大雪の7.3％・8.8％とは定義が異なる（08シート・修正指示書A-16）。また地域包括支援センター運営状況調査は北海道のKPIのデータ源でもあり、H09・H10の代替候補となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>十</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>医療介護連携の状況</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>医療介護連携に関する加算の算定状況 等</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>管内事業所の医療介護連携に関する各種加算の算定実績について、過年度及び直近の状況等を確認</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム／（新）レーダーチャート</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>加算の算定実績は保険者が給付実績から直接把握できる。第10期のH09（退院時支援調整実施率）を業務記録で測る前に、加算の算定実績で代替できる可能性がある（退院時共同指導加算、入退院支援加算等）。見える化の新機能で再出力を依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>十一</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>認知症の人の数及び関連施策の状況</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>自治体内の認知症の人の数や推計値、認知症疾患医療センター、認知症サポート医等の機能や利用者数、ピアサポート活動や就労等の社会参加の機会、場の数・利用者数 等</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>地域の医療資源の機能や利用者等を確認。認知症カフェ、本人ミーティング、ピアサポート活動、就労といった社会参加の機会・場について、地域にどのようなものがあり、どれくらい活用されているかを確認</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>各自治体で把握</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画は認知症の語を114回用いているが、認知症の人の数の推計値を掲載していない。北海道は令和22年に道内で約35.5〜42.1万人と推計している（北海道計画 図表3-1）。大雪の推計値の算出と、3町の認知症カフェ・チームオレンジ等の実数の把握が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2　対応状況のまとめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>該当事項</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>二 人口構造、四 認定者数の状況</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>図表集及び本報告書で対応済み。人口メッシュのみ再出力を依頼する。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>五 介護サービス等の利用状況、七 介護保険施設・事業所の状況</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>既存指標は対応済み。新規指標（自給率、介護SCR、入所率、稼働率、職員数推移）の再出力を依頼する。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>重大な課題</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>六 介護サービス見込量、九 地域支援事業の状況</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>六は在宅介護実態調査が業務範囲外（A-9）、九は通いの場の定義不一致（A-16）。いずれも基本指針が求める把握手段が確保できていない。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>一 地勢と交通、三 人口動態、八 高齢者向け住まい、十 医療介護連携、十一 認知症</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>いずれもデータの入手が前提。八と十一は第10期の基本的記載事項・任意記載事項に直結する。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>注1）本別表は第10期基本指針に新設される案であり、告示前である。告示後に最終確認を要する。注2）11事項のうち、現時点で確認できているのは2事項にとどまる。うち5事項（五の一部、七の一部、三、十、二の人口メッシュ）は見える化システムの再出力で対応でき、3事項（一、八、十一）は発注者・3町からの資料提供で対応できる。残る2事項（六、九）は業務範囲又は指標定義の決定を要する。注3）特に「七 入所率・稼働率」と「五 自市町村内の事業所によるサービス提供割合（介護サービス自給率）」は、本検証で明らかになった未利用認定者504人（A-12）と重度在宅化（A-13）の要因分析に直結する。見える化システムの再出力を最優先で依頼することを推奨する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8618,7 +9261,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証の総括　主要所見12件</t>
+          <t>検証の総括　主要所見14件</t>
         </is>
       </c>
     </row>
@@ -9021,32 +9664,96 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>通いの場参加率の目標と実績が別の統計に基づいている</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画は「国が掲げている目標値8％（令和7年度）を参考に」目標10.0％を設定したが、国の8％及び北海道のKPI（3.94％→5.37％以上）は介護予防・日常生活支援総合事業の実施状況に関する調査に基づく。一方、大雪の実績（令和4年度7.3％・令和7年度8.8％）は日常生活圏域ニーズ調査における自己申告割合である。</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>分母・分子の定義が異なる指標を比較して目標を設定していた。第10期基本指針の新別表も、通いの場の把握方法として総合事業調査を挙げている。したがって「国目標8％を達成」という評価も、厳密には成立しない。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>第10期は総合事業調査ベースの参加率とニーズ調査ベースの参加率を区別し、目標を設定する系列を明示する。北海道との比較には総合事業調査ベースを用いる。H05の合成指標36.0％はニーズ調査ベースであり、北海道・全国とは比較できない点を注記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>北海道の評価指標のうち3項目は大雪でも直ちに使える</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期KPIのうち、①地域包括支援センター運営状況調査の評価結果（71.6％→全国平均値以上）、②介護従事者の採用率と離職率の差（1.0％→全国平均以上）、③介護給付適正化の主要3事業の実施（100％）は、いずれも既存の全国調査又は既存データで算定できる。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画はこれらの調査に一切言及していない。代表KPI4項目のうち3項目が独自定義であったため、北海道・全国との比較ができなかった。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>①はH09・H10（業務記録の様式整備が必要）の代替又は補完として使える。②はH13・H14（設問がない）の代替として使え、第9期の介護人材実態調査の採用者数・退職者数から算定できる。③は給付適正化の管理指標として使える。第10期のKPI体系に組み込むことを推奨する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>日常生活圏域の設定に人口規模の著しい偏りがある</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>第9期計画 第7節の6圏域のうち、美瑛町の朗根内地区は人口233人・高齢者82人。最大の美瑛町市街地・周辺地区は7,869人で、33.8倍の開き。</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>介護保険法第117条第2項第1号は地理的条件・人口等の社会的条件を勘案して圏域を設定することを求めるが、233人の圏域に独立したサービス基盤を割り当てることは現実的でない。</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>第10期の圏域設定を委員会の決定事項とする。統計・分析単位としての圏域と、基盤整備単位としての圏域を分けて整理する案を提示する。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率に由来し（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
         </is>
@@ -9054,9 +9761,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12667,7 +13374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12688,7 +13395,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第9期基本指針への第9期計画の対応と、第10期基本指針案（令和8年6月29日 社会保障審議会介護保険部会 第135回）への素案第9稿の対応状況。</t>
+          <t>第9期基本指針への第9期計画の対応と、第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1 令和8年3月9日、第135回 資料2-1 令和8年6月29日）への素案第9稿の対応状況。両資料を受領し原典で確認した。</t>
         </is>
       </c>
     </row>
@@ -13218,10 +13925,145 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>注1）第10期基本指針は令和8年7月時点で告示前であり、本シートは令和8年6月29日の社会保障審議会介護保険部会（第135回）資料に関する報道・解説記事の記述に基づく暫定評価である。本作業環境のネットワークポリシーにより厚生労働省サイト（mhlw.go.jp）から資料本体を取得できなかったため、告示後に本シートを更新する必要がある。注2）「対応」は素案に該当する記述又は施策があるもの、「一部対応」は言及はあるが施策・指標に接続していないもの、「未対応」は該当記述がないものを指す。注3）出現回数は全角半角と空白を正規化したうえでの単純計数であり、記述の質を評価するものではない。分量比は10シートの記載密度による。</t>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>3　第10期基本指針の構成の見直し（市町村計画に関する部分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>第9期（現行）</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>第10期（改正案）</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>変更</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>素案第9稿への影響</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>作成に関する基本的事項</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>1 基本理念等／2 実態の把握等／3 体制の整備／4 中長期的な推計及び第9期の目標／5 目標の達成状況の点検等／6 日常生活圏域の設定／7 他の計画との関係／8 その他</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>1 基本理念等／2 実態の把握等／3 体制の整備／4 都道府県との連携／5 第10期の目標／6 目標の達成状況の点検等／7 他の計画との関係／8 その他</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>「4 都道府県との連携」が新設され、「6 日常生活圏域の設定」は基本的記載事項の「1 日常生活圏域」へ統合</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>素案の策定体制に北海道との協議の位置付けがない（修正指示書B-18）。圏域の記載は基本的記載事項へ移るため、第1章第7節の扱いを整理する。</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>第1章第5節に北海道との協議を追加。圏域は第1章第7節を維持しつつ基本的記載事項として扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="100" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>基本的記載事項</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>1 日常生活圏域／2 サービス種類ごとの量の見込み／3 地域支援事業の量の見込み／4 自立支援・重度化防止・給付適正化への取組及び目標設定</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>1 日常生活圏域／2 サービス種類ごとの量の見込み及び2040年度を含む中長期的な推計／3 地域支援事業の量の見込み及び2040年度を含む中長期的な推計／4 2040年を見据えた中長期的なサービス提供体制の確保に関して取り組むべき事項／5 自立支援・重度化防止・給付適正化への取組及び目標設定</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>「4 2040年を見据えた中長期的なサービス提供体制の確保に関して取り組むべき事項」が新設。2・3に「2040年度を含む中長期的な推計」が明記</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>素案は第2章第7節・第4章第2節で2040年を扱っており方向は妥当。ただし新設項目は「中山間・人口減少地域対応、医療・介護連携、高齢者向け住まい、人材確保・生産性向上・経営改善支援等」を内容とし、独立した節として立てることが求められる。</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>第6章に「2040年を見据えた中長期的なサービス提供体制の確保」を独立した節として新設する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="100" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>任意記載事項</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>1〜11（在宅医療・介護連携、保健事業と介護予防の一体的実施、生活支援・介護予防の基盤整備、地域ケア会議、介護予防の推進、高齢者の居住安定 ほか）</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>1〜11（同左。ただし「（五）介護予防の推進」を削除し「1 自立支援、介護予防・重度化防止の推進」へ統合。7に「要介護者等の入居状況」を追加）</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム・サービス付き高齢者向け住宅について、入居定員総数に加え「要介護者等の入居状況」の記載が求められる</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>素案に高齢者向け住まいの実数の把握がない。資料が未受領。</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>資料の入手を依頼済み。第2章に高齢者向け住まいの状況を新設する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>注1）第10期基本指針は令和8年7月時点で告示前である。本シートは社会保障審議会介護保険部会（第134回 資料1-1・第135回 資料2-1）の原典に基づく評価であり、告示後に最終確認を要する。指針案は7月頃に全国課長会議へ示し年内に告示する予定とされている。注2）「対応」は素案に該当する記述又は施策があるもの、「一部対応」は言及はあるが施策・指標に接続していないもの、「未対応」は該当記述がないものを指す。注3）出現回数は全角半角と空白を正規化したうえでの単純計数であり、記述の質を評価するものではない。分量比は10シートの記載密度による。</t>
         </is>
       </c>
     </row>
@@ -13229,7 +14071,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13241,15 +14083,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -13262,278 +14105,1041 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>北海道の計画本編が本作業環境のネットワークポリシーにより取得できなかったため、公表情報から確認できた施策の柱との対応にとどまる。計画本編の入手後に再検証を要する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+          <t>北海道の計画本編（第4章 計画の方向性、第7章 高齢者保健福祉圏域ごとの整備目標）を受領し、基本テーマ・8基本目標・評価指標（KPI）及び上川中部圏域の記載と突合した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　北海道の基本テーマ・基本目標と大雪の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>北海道の施策の柱（確認できた範囲）</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>大雪の対応</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>第9期計画・素案の該当</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>評価と確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>北海道の基本目標（第9期）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>北海道の評価指標（KPI）と目標</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>大雪の対応する施策</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>基本テーマ「道民みんなで支え合う、明るく活力に満ちた高齢社会づくり」</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の基本理念</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>大雪の第9期計画に北海道の基本テーマへの言及はない。第10期は第1章第8節で関係を明示する。</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>地域包括ケアシステムの深化・推進</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>高齢者が可能な限り住み慣れた地域で日常生活を営むことができるよう、地域包括ケアシステムの深化・推進に取り組む。</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>地域包括ケアシステム構築のための地域づくりと地域ケア会議の推進</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター運営状況調査の各項目における評価結果　71.6％（R3）→ 全国平均値以上（R8）</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>基本目標1・2（地域ケア会議の推進、包括的な支援体制の整備）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標1・2。素案 基本目標1案・2案。</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>整合。ただし東川町の計画は「地域ケアシステム」の語を5回用いており（「地域包括ケアシステム」は3回）、国・北海道・広域連合の用語と一致しない。09シート参照。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>北海道のKPIは国の共通評価指標（計59問）による。大雪・3町の評価結果を入手すれば、第10期のH09・H10の代替又は補完指標として直ちに使える。第9期計画は同調査に言及していない。</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>介護サービス基盤の整備</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>地域の実情に応じたサービス基盤の計画的整備。全道域及び高齢者保健福祉圏域で必要な調整を行う。</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>生活支援体制整備の推進</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>①生活支援コーディネーターの活動の進捗を定期的に確認し改善・見直しを行っている市町村数 127（R5）→142以上（R8）②多様な主体による生活支援・通いの場を実施する市町村数 85（R4）→98以上（R8）</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2（介護予防・日常生活支援総合事業の推進）</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標4・第6章第4節。素案 基本目標3案。</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>整合。ただし第9期計画は全サービスで定員据置きとしており、「調整」の内容が記載されていない。上川中部高齢者保健福祉圏域における調整の枠組みを第10期に明記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>②は総合事業の訪問型サービスA・B・D、通所型サービスA・Bのいずれかに取り組む市町村数。大雪の総合事業の類型別実施状況を第2章で示す必要がある。</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>自立支援、介護予防・重度化防止の推進</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>通いの場への参加率（月1回以上）　3.94％（R3）→ 5.37％以上（R8）　※全国はR3 5.53％、国目標8％（2025年まで）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>基本目標3・代表KPI④（通いの場参加率）</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>重大な不整合</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>北海道・全国・国目標はいずれも「介護予防・日常生活支援総合事業の実施状況に関する調査」に基づく参加率。一方、大雪の第9期KPI④の実績（R4 7.3％・R7 8.8％）は日常生活圏域ニーズ調査における自己申告割合であり、分母・分子の定義が異なる。第9期計画は国目標8％を参考に目標10.0％を設定しており、定義の異なる指標を比較して目標を立てている。（修正指示書A-16）</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>医療・介護連携の充実</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>在宅での看取りや入退院時等に活用できる医療・介護関係者の情報共有ツールを作成している市町村数 134（R5）→158以上（R8）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>基本目標1（在宅療養者支援に向けた医療機関との連携体制の構築）</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>情報共有ツール（情報共有シート、連絡帳、地域連携クリティカルパス、認知症ケアパス等）の作成状況が第9期計画に記載されていない。第10期のH09の前提として3町の状況を確認する。</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策の推進</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>①専門医療機関との連携により早期診断・早期対応につなげる体制を構築している市町村数 149（R5）→全市町村（R8）②認知症サポーターの活動等による支援体制や社会参加の推進を図る取組を行っている市町村数 63（R5）→全市町村（R8）</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2-3（認知症施策推進大綱を踏まえた施策の推進）</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>②はR5時点で63市町村（全179市町村の35.2％）にとどまり、R8に全市町村が目標。大雪3町が該当するかを確認し、該当しない場合は第10期の重点施策とする。</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>介護人材の養成・確保</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>介護サービスの担い手となる人材を育て、確保し、働き続けられる環境を整える。</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>①介護従事者の採用率と離職率の差 1.0％（R3）→ 全国平均以上（R8）②介護従事者の数 100,523人（R4）→ 113,701人以上（R8）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>基本目標4-4（人材確保・育成の推進）</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標4-4「人材確保・育成の推進」。素案 基本目標4案。</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>整合。東川町は町内の旭川福祉専門学校との協定・地域おこし協力隊・日本語学校との連携を計画に明記しており先行している。美瑛町は外国人介護福祉人材育成支援事業を設けている。3町の取組を広域計画に集約して掲載する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>介護現場の生産性の向上</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>生産性向上に資する支援・施策の総合的推進。</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>一部対応</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標4-1「介護サービスの生産性向上」。素案の記述は第9期より薄い。</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>北海道が設置する生産性向上の支援体制（ワンストップ窓口等）への参画状況を確認し、第10期に明記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>認知症施策の推進</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>認知症になっても安心して暮らせる地域づくりと認知症の予防。</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>①は（公財）介護労働安定センター「介護労働実態調査」による。第9期の介護人材実態調査は採用者数・退職者数を把握しており、同じ定義で算定できる。H13・H14の設問がない問題（修正指示書C-16）の代替として、この指標の採用を推奨する。②の推計は「各市町村のサービスの利用量を基に厚生労働省が作成したワークシート」によるため、大雪の必要人材数も同じ方法で推計できる。</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>安全・安心な暮らしの確保</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>①成年後見制度の活用や高齢者虐待防止に関する体制の整備、消費者被害防止の取組をすべて行っている市町村数 129（R3）→158以上（R8）②道所管介護保険施設の避難確保計画策定数（風水害・土砂災害）290施設（R5）→312施設（R8）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>基本目標1-4（高齢者の虐待防止の推進）・基本目標5（災害や感染症対策）</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標2-3。3町とも独立した目標又は施策として設定。</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>整合。認知症基本法（令和5年6月公布・令和6年1月施行）を3町とも計画に反映済み。第10期は認知症施策推進基本計画（国）及び北海道の推進計画との関係を第1章第8節に追記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>権利擁護・虐待防止、災害時等の安全確保</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>高齢者の権利を守り、虐待を防止し、災害時などの安全を確保する。</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>②は道所管施設が対象。大雪圏域の施設の策定状況を北海道に照会すれば、第10期のH16（災害・感染症時の必須サービス継続率）の体制指標への組替え（修正指示書B-20）に使える。</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>介護保険制度の適切な運営</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>介護給付適正化事業の目標値　主要3事業「要介護認定の適正化」「ケアプラン等の点検」「医療情報との突合・縦覧点検」の全市町村での実施（100％）</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>基本目標4-3（介護給付費の適正化【主要3事業】）</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標1-4・基本目標5。3町とも施策あり。</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>整合。東神楽町は権利擁護の記述が16回と手厚い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>介護保険制度の適正・公平な運営</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>介護保険サービスが質高く、効率的かつ公平に提供されるよう制度を運営する。</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>対応</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画 基本目標4-2・4-3（給付適正化）。素案 基本目標5案。</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>整合。給付適正化計画の期数が素案で未記載（修正指示書B-1）。北海道の給付適正化計画の期別に照らして確定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>注1）本シートの「北海道の施策の柱」は、北海道保健福祉部福祉局高齢者保健福祉課の公表ページ及び関連する解説記事から確認できた範囲であり、計画本編の施策体系そのものではない。北海道の数値目標（介護職員数の確保目標等）は確認できていない。注2）第9期計画 第1章第8節は、国の基本指針－北海道の支援計画－広域連合の事業計画－3町の高齢者福祉計画の関係を図で示しているが、北海道の支援計画の具体的な目標との対応関係は記載していない。第10期では、北海道の目標のうち保険者に関係するものを特定し、対応関係を表で示すことを推奨する。注3）本検証で必要となる北海道の資料：①第9期北海道高齢者保健福祉計画・介護保険事業支援計画（本編）、②上川中部高齢者保健福祉圏域に関する記載、③北海道の介護人材確保の数値目標、④北海道の介護給付適正化計画の期別と目標。第1回委員会までの入手を依頼する。</t>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>北海道の記載は「これまで主要5事業とされていたが、次期計画から主要3事業に再編される」。第9期計画の「第6期給付適正化計画」の期数（修正指示書B-1）と併せて確認する。道内実施率（R3）は要介護認定の適正化86.5％、ケアプランの点検78.8％、医療情報との突合・縦覧点検94.2％。</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2　上川中部圏域における大雪地区広域連合の位置（北海道計画 第7章第12節）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>総人口</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>高齢者人口</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上割合</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>平均年齢</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>旭川市</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>325162</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>112411</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>58032</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>50.89</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>鷹栖町</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>6567</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>2272</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1182</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>50.83</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>10112</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>2929</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1544</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>47.77</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>当麻町</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>6319</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>2659</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1532</v>
+      </c>
+      <c r="F21" s="22" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>54.79</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>比布町</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>3520</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>848</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>54.85</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>愛別町</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>2605</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>703</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>上川町</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>1550</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>880</v>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>55.81</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>8313</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>2759</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>9668</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>3749</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>2133</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>53.49</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>幌加内町</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>559</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>344</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>54.44</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>圏域計</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>377136</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>131555</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>68688</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>52.9</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>注1）令和2年国勢調査。構成3町の計は28,093人（圏域の7.4％）、高齢者9,437人、高齢化率33.6％。圏域の86.2％は旭川市が占める。注2）平均年齢は東神楽町47.77歳が圏域で最も若く、美瑛町53.49歳は圏域平均52.90歳を上回る。3町の間で人口構造が大きく異なることが、圏域の平均値では見えない。注3）圏域の令和22年の推計は総人口307,281人・高齢者128,332人・高齢化率41.76％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>3　上川中部圏域内の保険者比較（北海道計画 第7章第12節・見える化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>旭川市</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>その他の町</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>調整済み重度認定率（要介護3〜5）</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>5.7％</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>約5.6％（R3図）／5.8％（R6）</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>約5.7％</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>鷹栖約6.9％・愛別約6.3％</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>大雪は北海道とほぼ同水準。圏域内では中位。</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>調整済み軽度認定率（要支援1〜要介護2）</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>14.8％</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>約13.5％（R3図）／14.2％（R6）</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>約15.7％</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>鷹栖約11.5％・愛別約9.8％</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>大雪は北海道をやや下回る。旭川市が圏域で最も高い。</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>調整済み第1号1人あたり給付月額（在宅）</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>8,918円</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>9,164円（R5）</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>約12,000円</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>愛別約11,200円・当麻約9,000円</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>大雪は北海道を2.8％上回る程度。旭川市は北海道を約35％上回り圏域で最も高い。</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>調整済み第1号1人あたり給付月額（施設及び居住系）</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>10,504円</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>13,097円（R5）</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>約9,700円</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>当麻約13,600円・愛別約13,500円</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>大雪は北海道を24.7％上回る。旭川市は北海道を下回り、大雪と旭川市で構造が逆転している。</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>注1）北海道計画 第7章第12節の分布図から読み取った概数（「約」を付した値）と、受領した見える化データの実数（B6は令和6年、D8は令和5年）を併記した。注2）この分布図は業務仕様書４（４）が求める「類似保険者との比較分析」の材料として直接使える（修正指示書A-14の一部が解決）。ただし北海道計画の図は第9期策定時点（令和3年前後）の値であり、最新値は見える化の類似保険者比較機能で再出力する必要がある。注3）大雪と旭川市の構造の違い（大雪は施設・居住系が高く在宅が低い、旭川市はその逆）は、住民の生活圏が重なるだけに住民説明で問われやすい。第2章に要因とともに記載することを推奨する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>4　上川中部圏域のサービス見込量にみる大雪の位置（北海道計画 第7章第12節4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>圏域R4実績</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>圏域R8見込</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>圏域R22見込</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>大雪の状況</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護（人/月）</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>68</v>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>84</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>第1号1人あたり給付月額は令和7年度15円で実質未整備</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>圏域の定期巡回はほぼ旭川市に集中していると考えられる。大雪の重度在宅者を支える手段が欠けている。</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護（人/月）</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="23" t="n">
+        <v>101</v>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>給付月額0円で事業所なし</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>圏域はR4の1.0人からR8に101.0人へ大幅に増やす計画。大雪は計画にも実績にもない。</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護（人/月）</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>58</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>給付月額0円で事業所なし</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>圏域では一定量が見込まれている。</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護（人/月）</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="n">
+        <v>242.3</v>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>238</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>242</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>定員62人（見える化）／63人（第9期計画）</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>圏域の約26％が大雪の定員。圏域全体でも増やす計画はない。</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護（人/月）</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="n">
+        <v>1407.8</v>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>1431</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>定員99人（R4以降）</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>圏域は微増の計画。大雪は令和4年度に117人から99人へ18人減少しており、圏域の方向と逆。</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="56" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>注1）圏域の見込量は北海道計画 第7章第12節4「老人福祉サービスの目標（介護サービス）」による。注2）重度在宅者を支える24時間対応サービス（定期巡回、夜間対応、看多機）について、圏域では一定量が見込まれているのに対し大雪は実質ゼロである。要介護5の在宅・居住系割合が54.6％に達している大雪の状況（06シート）と併せると、第6章の整備方針の中心論点になる（修正指示書A-13）。注3）本シートで用いた北海道計画の受領範囲は、第1章（計画の基本的事項）、第2章（本道の高齢者を取りまく状況）、第3章（本道の高齢者福祉の現状）、第4章（計画の方向性）、第5章（計画の具体的な展開）、第6章（サービス量の見込みと整備目標）、第7章（高齢者保健福祉圏域ごとの整備目標）、第8章（資料編）である。本文が画像で構成されているため、第4章及び第7章の主要頁を目視により読み取った。第5章（計画の具体的な展開・52頁）の施策の詳細は未確認であり、施策単位の整合確認は今後の作業となる。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A49:G49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_第10期KPIの妥当性" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_仕様書との適合性" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_確認すべき指標への対応" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_ロジックモデルの構成" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1208,169 +1209,187 @@
       </c>
       <c r="D35" s="6" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>18_ロジックモデルの構成</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>北海道第9期計画 第5章の記述構成（インプット・アウトプット・アウトカム）と、第10期基本指針が求めるロジックモデルへの対応。</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>施策単位での整合確認</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
+          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>記載事項への網羅性の最終確認</t>
+          <t>施策単位での整合確認</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
+          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
+          <t>記載事項への網羅性の最終確認</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
+          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>給付費・地域支援事業費の計画対実績</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>介護給付費準備基金の残高推移</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>04シートの剰余額は概算にとどまる</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>注1）第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1・第135回 資料2-1）及び第9期北海道高齢者保健福祉計画・介護保険事業支援計画の本編を受領し、07・08・17シートは原典に基づいて作成した。北海道の計画本編は本文が画像で構成されているため、第4章（計画の方向性）及び第7章第12節（上川中部圏域）の主要頁を目視により読み取っている。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
@@ -1378,8 +1397,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9241,13 +9260,554 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>北海道第9期計画の施策の構成と、第10期基本指針が求めるロジックモデル</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>北海道第9期計画 第5章「計画の具体的な展開」は8節すべてを同じ5層構成で記述しており、インプット・アウトプット・アウトカムが節ごとに完結している。第10期基本指針案は「介護保険事業（支援）計画におけるロジックモデルの活用やPDCAサイクルに沿った計画策定の推進」を記載充実事項に挙げている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　北海道第9期計画 第5章の記述構成（全8節に共通）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>層</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>北海道の例（第6節 介護人材の養成・確保）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>大雪 第9期計画の対応</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>第10期での対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>（1）現状と課題</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>定量的な現状認識と、そこから導かれる課題を箇条書きで示す</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>令和8年までに約114千人の介護人材が必要。道内の離職率11.9％（R3）は全国14.3％を下回るが、採用率も12.9％と全国15.2％を下回る。介護職の有効求人倍率はR4で3.08倍（全職種1.09倍）</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>第5章の各施策は「主な取組」「管理指標」「主体」の3列の表のみで、現状と課題の記述がない</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>素案の第5章に各基本目標の冒頭で現状と課題を記述する。第2章の分析結果を根拠として引用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>（2）関連データ</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>課題を裏付ける図表を掲載する</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>有効求人倍率推移（北海道）のグラフ</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>図表集の該当図表を第5章にも再掲するか、第2章の図表番号で参照する（図表番号一覧を活用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>（3）施策の方向性</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>取り組む方向を、事業名を添えて示す</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>「北海道介護人材確保対策推進協議会」を設置し関係機関のネットワークを活用［介護従事者定着支援事業］</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>「主な取組」列が該当するが、事業名との結び付きがない</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>取組ごとに実施事業名を明示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>（4）主な事業　＜インプット＞</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>事業名と内容（何をするか）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>介護支援専門員等資質向上事業、介護職員等研修事業、キャリアパス支援等研修事業、介護未経験者に対する研修支援事業</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>第5章に事業名がない。第9期計画の地域支援事業の記述は第3章にあるが施策と接続していない</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>各施策に実施事業を紐づける。3町の事業は資料2の役割分担表と対応させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>（4）主な事業　＜目標（アウトプット）＞</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>事業の実施量の目標（どれだけやるか）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>初任介護支援専門員OJT研修 受講者数25人／年、キャリアパス支援研修 12,000人／年、受講料減免を受けて初任者研修等を受講した人数 230人／年 ほか6項目</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>アウトプット指標は「通いの場参加率」の1項目のみ。第9期計画自身が「アウトプットの達成→アウトカムの達成のロジックの妥当性」を指標設定の考慮点に挙げているが未実装</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>素案の第3層「施策管理指標」をアウトプット指標として定義し、各施策に配置する</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>（5）達成目標（アウトカム）</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>施策の成果（どう変わるか）。節ごとに1〜2項目</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>介護支援専門員従事者数　R4 9,718人 → R8 10,331人</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>代表KPI4項目が該当するが、5基本目標19施策に対し4項目で、施策との対応が付いていない</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>H01〜H16を基本目標に割り付け、各節の末尾に達成目標として掲げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　北海道の達成目標（アウトカム）の例と大雪への示唆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>北海道の達成目標（アウトカム）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>基準年→目標年</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>大雪で同種の指標を置く場合</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>第3節 自立支援、介護予防・重度化防止の推進</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>介護予防に資する住民主体の通いの場がある市町村数</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>R4 159市町村 → R8 全市町村（179市町村）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>市町村単位の指標のため大雪（1保険者）には直接適用できないが、「通いの場がある日常生活圏域数」又は「通いの場の数・参加者数」に置き換えられる。総合事業の実施状況に関する調査から算定できる。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>第6節 介護人材の養成・確保</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>介護支援専門員従事者数</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>R4 9,718人 → R8 10,331人</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>大雪圏域の介護支援専門員数は指定台帳から把握できる。H13（職種別欠員率）の測定が難しい場合の代替として、職種別の従事者数の推移が使える。</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>第4章第3節 評価指標</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>介護従事者の採用率と離職率の差</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>R3 1.0％ → R8 全国平均以上</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>採用（離職）率＝各年の採用（離職）者数÷各年9月30日の在籍者数×100。第9期の介護人材実態調査は採用者数・退職者数を把握しており、同じ定義で算定できる（修正指示書B-21）。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>第4章第3節 評価指標</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター運営状況調査の各項目における評価結果</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>R3 71.6％ → R8 全国平均値以上</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>国が全国統一して用いる59問（組織運営19、総合相談6、権利擁護4、包括的継続的ケアマネジメント6、地域ケア会議13、介護予防ケアマネジメント6、事業間連携5）による。3町の評価結果を入手すれば、H09・H10の補完指標として直ちに使える。</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>3　国の第10期基本指針案との関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>指針案の記載充実事項</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>北海道の状況</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>大雪の状況</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ロジックモデルの活用</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>「介護保険事業（支援）計画におけるロジックモデルの活用やPDCAサイクルに沿った計画策定の推進」（第一 二 4 介護保険制度の立案及び運用に関するPDCAサイクルの推進）</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>第9期で既に実装済み。第5章の全8節がインプット・アウトプット・アウトカムの3層で記述されている</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画は「アウトカム指標3・アウトプット指標1」と分類はしているが、施策ごとのインプット・アウトプットがなく、ロジックが接続していない</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第5章の構成をそのまま踏襲することで、国の指針案の要請と北海道との整合を同時に満たせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>計画策定の前提となる地域の現状等の把握・分析</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>「別表1に掲げる指標を参考とすることについて記載」（第二 一 1）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第5章の各節に「（2）関連データ」を置き、課題の裏付けを図表で示している</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>素案の第5章は表形式で、根拠となるデータの参照がない</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>17シートの11事項の分析結果を第2章に整理し、第5章から図表番号で参照する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>施策の達成状況の評価</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>「基本理念、達成しようとする目的及び地域の実情に応じた特色の明確化、施策の達成状況の評価等」（第二 一 1）</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>節ごとに達成目標（アウトカム）を掲げ、第4章第3節に8基本目標の評価指標を集約している</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>代表KPI4項目が5基本目標19施策に対して不足していた。素案は16項目に拡張したが半数の測定手段が未確定</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>16項目を基本目標に割り付け、各節の末尾に達成目標として掲げる。測定手段が未確定の項目は初年度を体制整備の管理指標とする（修正指示書B-19・B-20）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>注1）北海道第9期計画 第5章は8節・52頁で構成され、8節は第4章第2節の8基本目標と1対1で対応している。本シートは第3節（自立支援、介護予防・重度化防止の推進）、第6節（介護人材の養成・確保）、第8節（介護保険制度の適切な運営）の頁を目視で確認したうえで、全節に共通する構成として整理した。注2）大雪の素案第9稿は「本文12項目＋補完4項目＋施策管理指標」の3層構造を掲げており方向は妥当である。本シートの提案は、その3層を北海道と同じ「インプット→アウトプット→アウトカム」の記述構成に落とし込むことで、施策と指標の対応を計画本文の上で見えるようにするものである。注3）北海道の指標には市町村数を単位とするものが多く、1保険者である大雪にはそのまま適用できない。日常生活圏域数又は実数・率への置き換えが必要であり、その際の圏域の扱いは修正指示書C-9と連動する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9261,7 +9821,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証の総括　主要所見14件</t>
+          <t>検証の総括　主要所見15件</t>
         </is>
       </c>
     </row>
@@ -9728,32 +10288,64 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>北海道は施策の記述をロジックモデルで構成しており、これを踏襲できる</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>北海道第9期計画 第5章は全8節を「（1）現状と課題／（2）関連データ／（3）施策の方向性／（4）主な事業＜インプット／目標（アウトプット）＞／（5）達成目標（アウトカム）」の5層で記述している。例えば第6節は事業4件・アウトプット目標6項目・アウトカム1項目（介護支援専門員従事者数 R4 9,718人→R8 10,331人）。</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>大雪の第9期計画は第5章が「主な取組・管理指標・主体」の3列の表のみで、現状と課題、根拠データ、実施事業、アウトプット目標がいずれもない。計画自身が「アウトプットの達成→アウトカムの達成のロジックの妥当性」を指標設定の考慮点に挙げているが、実装されていない。</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針案は「ロジックモデルの活用やPDCAサイクルに沿った計画策定の推進」を記載充実事項に挙げている。北海道の第5章の構成を踏襲すれば、国の要請と北海道との整合を同時に満たせる。素案の3層構造（本文12・補完4・施策管理指標）をこの記述構成に落とし込む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>日常生活圏域の設定に人口規模の著しい偏りがある</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>第9期計画 第7節の6圏域のうち、美瑛町の朗根内地区は人口233人・高齢者82人。最大の美瑛町市街地・周辺地区は7,869人で、33.8倍の開き。</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>介護保険法第117条第2項第1号は地理的条件・人口等の社会的条件を勘案して圏域を設定することを求めるが、233人の圏域に独立したサービス基盤を割り当てることは現実的でない。</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>第10期の圏域設定を委員会の決定事項とする。統計・分析単位としての圏域と、基盤整備単位としての圏域を分けて整理する案を提示する。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率に由来し（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
         </is>
@@ -9761,8 +10353,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -26,6 +26,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_仕様書との適合性" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_確認すべき指標への対応" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_ロジックモデルの構成" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_見える化の再出力依頼" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1227,169 +1228,187 @@
       </c>
       <c r="D36" s="6" t="inlineStr"/>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>19_見える化の再出力依頼</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>見える化の指標リスト906件との突合。再出力を依頼する指標の指標IDと用途、及び自給率を見える化以外で把握する場合の代替。</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>施策単位での整合確認</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
+          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>記載事項への網羅性の最終確認</t>
+          <t>施策単位での整合確認</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
+          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
+          <t>記載事項への網羅性の最終確認</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
+          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>給付費・地域支援事業費の計画対実績</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>介護給付費準備基金の残高推移</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>04シートの剰余額は概算にとどまる</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>注1）第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1・第135回 資料2-1）及び第9期北海道高齢者保健福祉計画・介護保険事業支援計画の本編を受領し、07・08・17シートは原典に基づいて作成した。北海道の計画本編は本文が画像で構成されているため、第4章（計画の方向性）及び第7章第12節（上川中部圏域）の主要頁を目視により読み取っている。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
@@ -1398,8 +1417,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10361,6 +10380,1002 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの再出力依頼リスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>受領した「指標リスト（目的別）」により、見える化の指標は全906件で、受領済みはA・B・C・D・P系列の182件（20.1％）であることを確認した。未受領のδ・F・H・J・K・L・M・N・O・W系列に、第10期基本指針の新別表11事項の大半と、測定手段が未確定だったKPIの代替指標が含まれている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　最優先で依頼する指標</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>指標ID</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>指標名</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>見える化のメニュー位置</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>定義・内容</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>大雪で何が分かるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>δ2／δ2-a〜e</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス自給率（時系列）　全体・訪問系・通所系・短期入所系・多機能系・施設居住系</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>地域分析＞介護サービス自給率＞時系列</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>毎年9月サービス提供分の介護レセプトに基づき、市区町村内に所在する事業所における給付月額を、各市区町村内における給付月額で除した割合（受領ファイルの注記による定義）。100％未満は域外の事業所の利用（流出）、100％超は域外からの受入れ（流入）を意味する。</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>3町がどれだけ旭川市の事業所を利用しているかが数値になる。定期巡回が給付月額15円でほぼゼロなのに圏域では59.1人/月ある理由（旭川市の事業所を使えているのか、そもそも届いていないのか）が判別できる。自給率が低ければ町内整備は不要、高ければ域外に頼れない。第6章の整備方針が逆になる（修正指示書A-13・B-22）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>δ3／δ3-a〜e</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス自給率（地域比較）　同6区分</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>地域分析＞介護サービス自給率＞地域比較</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>同上を他地域と比較する形式。</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>旭川市・上川中部圏域内の他保険者との自給率の比較ができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>F4／F5／F6</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上の通いの場の参加率／参加者数／箇所数</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業＞介護予防・日常生活支援総合事業＞通いの場</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業の実施状況に関する調査に基づく通いの場の参加率。国の目標8％（令和7年度）及び北海道のKPI（3.94％→5.37％以上）と同じ系列。</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>第9期の代表KPI④は国の目標8％を参考にしながら、実績はニーズ調査の自己申告割合（R4 7.3％・R7 8.8％）で測っており統計が一致していなかった（修正指示書A-16）。F4を出力すれば、この不一致は見える化の再出力だけで解消できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>F1／F2／F3</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>週1回以上の通いの場の参加率／参加者数／箇所数</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>国の第9期以前の目標は週1回以上が基準であった。</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上と週1回以上の双方を押さえ、第10期の目標をどちらで設定するかの判断材料とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>H1／H2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>介護人材の必要数／需要見込みに対する供給見込みの割合</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>介護人材の状況を確認する＞介護人材の必要数</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>各市町村のサービス利用量を基に厚生労働省が作成したワークシートにより推計した必要人材数と、供給見込みとの比較。</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>北海道はこの方法で「令和8年までに約114千人、令和22年までに約129千人が必要」としている。大雪の必要人材数が同じ方法で得られれば、H13（職種別欠員率）の代替となる。事業所実態調査が業務範囲外である問題（修正指示書A-7）の実務的な回避策になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>K1-a〜e／K2-a〜c／K3-a〜s</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>サービス提供事業所数（全27サービス種別）</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>介護保険施設・事業所数</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>34件</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス5種、居住系3種、在宅サービス19種の事業所数。</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針の新別表 七「介護保険施設・事業所数」に対応。定員（D25〜D30・受領済）と組み合わせると、1事業所あたり定員や事業所数の推移が把握できる。地域密着型通所介護の給付月額が27.0％低下した要因（休廃止の有無）の確認に直結する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　新別表11事項への対応のために依頼する指標</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>別表の事項</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>指標ID</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>指標名</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>定義・内容</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>三 人口動態</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>L27-a／b／c</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>在宅死亡者数（介護老人保健施設／老人ホーム／自宅）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>別表三は「死亡場所別の死亡数等について過年度の推移等を確認すること」としている。見える化のL27系列がこれに対応する。</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>在宅看取りの実態が把握でき、医療介護連携の議論と第6章の整備方針の基礎になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>三 人口動態</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>L28-a／b</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>看取り数（死亡診断書のみの場合も含む）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>算定回数とレセプト件数の2系列。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>七 施設・事業所</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>M2-a〜m</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>従事者数（サービス別）［認定者1万対］</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>13件</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設、老健、療養型、医療院、訪問介護、通所介護、通所リハ3種、訪問看護、地域密着型介護老人福祉施設、居宅介護支援、地域密着型通所介護の13サービス。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>別表七の「従事者数」に対応。認定者1万対で標準化されているため全国・北海道と比較できる。H13（職種別欠員率）の代替の一部となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>九 地域支援事業</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>F15〜F25</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センターの設置数・人員体制（3職種別）・地域ケア会議開催回数</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>11件</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>設置数、ブランチ・サブセンターを含む設置数、3職種の人員体制（保健師・社会福祉士・主任介護支援専門員別）、地域ケア会議開催回数。いずれも65歳以上人口1万対の標準化値がある。</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>別表九の「地域包括支援センターにおける相談体制の状況」に対応。3町の体制差（東川町は重層的支援推進室に内包）を定量的に示せる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>九 地域支援事業</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>F28〜F40</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>訪問型サービスA〜D・通所型サービスA〜C・見守り・配食・介護予防ケアマネジメントの実施延べ件数</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>13件</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>いずれも65歳以上人口1万対。</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>北海道のKPI「多様な主体による生活支援、通いの場を実施する市町村（訪問型サービスA・B・D、通所型サービスA・Bのいずれかに取り組む市町村）数」に対応。大雪の総合事業の類型別実施状況が分かる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>九 地域支援事業</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>W系列</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金・介護保険保険者努力支援交付金に係る評価指標</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>139件</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>市町村評価指標（令和4・5年度66件、令和6年度12件）、都道府県評価指標43件、アウトプット指標10件、アウトカム指標8件。</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>別表九の「インセンティブ交付金における評価」に対応。交付金の評価指標は保険者の取組状況を国の共通様式で点数化したものであり、第10期のKPIの補完指標としてそのまま使える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>十 医療介護連携</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>L20〜L26／O1〜O13</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>医療介護連携に関する加算等の算定状況</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>約20件</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>診療報酬側：介護支援連携指導、退院時共同指導、在宅ターミナルケア。介護報酬側：退院退所加算、入院時情報連携加算、退院・退所時連携加算、緊急時等居宅カンファレンス加算、ターミナルケアマネジメント加算、緊急時訪問看護・訪問介護加算、看取り介護加算 ほか。</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>別表十の「医療介護連携に関する加算の算定状況」に対応。H09（退院時支援調整実施率）を3町の業務記録で測る前に、L21（退院時共同指導）・L25（退院退所加算）・L26（入院時情報連携加算）・O5（退院・退所時連携加算）で代替できる可能性がある（修正指示書B-19の解決策）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>十 医療介護連携</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>δ1-a／b／c</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>レーダーチャート（地域の概況（需要）／サービス提供体制（供給）／医療介護連携）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>地域分析のレーダーチャート。</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針案が別表十の把握方法に「見える化システム（新）レーダーチャート」を挙げており、既存のδ1-cがこれに相当すると考えられる。3つの視点を1枚で示せるため委員会資料に適する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>十一 認知症</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>J16／J17／J18</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>認知症初期集中支援チームの訪問実績／認知症地域支援推進員の配置人数／認知症カフェの設置主体別箇所数</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>いずれも実施状況の実数。</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>別表十一の「ピアサポート活動や就労等の社会参加の機会、場の数・利用者数」の一部に対応。3町の認知症施策の実施状況を定量的に比較できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>十一 認知症</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>J1〜J15</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>認知症関連研修の修了者数（サポート医、かかりつけ医、病院勤務者、歯科医師、薬剤師、看護職員、介護実践者等）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>15件</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>研修種別ごとの修了者数。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>北海道のKPI「専門医療機関との連携により早期診断・早期対応につなげる体制を構築している市町村数」の裏付けとなる。第5章の認知症施策のアウトプット指標に使える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>3　指標リストに存在しない指標（令和8年度以降の改修待ち）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>別表の事項</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>指針案の記載</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>現状</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>代替</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="76" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>入所率・稼働率</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>七 介護保険施設・事業所の状況</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>把握方法に「見える化システム（新）入所率、職員数推移」と記載（下線＝令和8年度以降に新たに把握が可能となる指標）</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>指標リストに該当なし。改修待ち。</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>N8-a／N8-b（通所リハビリテーション定員あたり利用延人員数）が稼働率に近い。入所率は定員（D25〜D27・受領済）と受給者数（D1・受領済）から概算できるが、受給者は域外施設の利用者を含むため厳密な入所率にはならない。事業所別の入所率は自治体の指定台帳又は施設への照会が必要。</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>介護SCR（性・年齢調整済みレセプト出現比）</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>五 介護サービス等の利用状況</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>「介護サービスの提供状況の地域差を示す指標（介護SCR）」を新たに提示</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>指標リストに該当なし。改修待ち。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>D49（地域差指数）が受領済みで、調整済み給付月額1.08・調整済み認定率1.02・受給率1.08・受給者単価1.06の4指標が得られている。サービス種類別の調整済み値は改修後に取得する。</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="76" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>類似保険者比較</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>―（業務仕様書４（４）が要求）</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>指針案の別表には記載なし。仕様書が「類似保険者との比較分析」を明示。</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>指標リストに「類似」の語なし。δ3系列の「地域比較」で比較対象を選択する機能と考えられるが、選定条件は受領資料から確認できない。</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>出力時に比較対象の選定条件（人口規模、高齢化率、都市規模等）を併せて記録していただく。北海道計画 第7章第12節の上川中部圏域の分布図は圏域内比較であり、旭川市（325,162人）を含むため人口規模が近い保険者との比較にはならない。</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>人口メッシュ</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>二 人口構造</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>把握方法に「見える化システム（新）人口メッシュ」と記載</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>指標リストに該当なし。改修待ち。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の特定（別表一）に有用。改修後に取得する。当面は美瑛町の4圏域（旭・北西、美馬牛、朗根内、市街地・周辺）の区分で代替する。</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>4　介護サービス自給率を見える化以外で把握する場合の代替</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>資料</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>自給率の算定可否</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="68" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告（月報・年報）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>算定できない</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>様式が保険者単位の集計であり、サービスを提供した事業所の所在地の情報を持たない。大雪の被保険者が旭川市の事業所を利用した給付も、大雪の給付として計上される。したがって自給率の分子（自市町村内の事業所による給付月額）が取り出せない。</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>受給者数・給付費の総額（分母に相当）は取得できる。</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="68" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費等実態統計（旧・介護給付費実態調査）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>算定できない</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>保険者所在地別と事業所所在地別の集計はあるが、公表は都道府県単位が基本であり、市町村レベルで両者を突合した表は公表されていない。</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="68" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>国保連合会から保険者に提供される給付実績情報</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>算定できる（推奨）</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費明細書（レセプト）の内容が事業所番号付きで提供される。事業所番号と指定事業所台帳（所在地）を突合すれば、自市町村内か域外かを判定できる。見える化のδ2と同じデータソースであるため、値も一致するはず。</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>毎月提供されているため時系列も作成できる。見える化の定義に合わせるには「毎年9月サービス提供分」で集計する。</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="68" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>保険者の介護保険基幹システムの給付実績照会</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>算定できる</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>多くのシステムで事業所別の給付費・受給者数を集計できる。</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>システムの仕様により出力可否が異なる。</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="68" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型サービスの指定台帳</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型サービスは保険者が指定するため、原則として自市町村の被保険者のみが利用する。したがって地域密着型の自給率はほぼ100％と見なせる。</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>市町村間の同意による他保険者被保険者の利用がある場合は例外となる。</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="70" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートは受領した「指標リスト（目的別）」（見える化システムの指標一覧・994行）に基づく。指標IDが付されているものは906件で、うち受領済みはA系列13件・B系列27件・C系列4件・D系列199件・P系列ほかを含む182件（20.1％）である。注2）1の最優先6項目（計54件）は、いずれも本検証で明らかになった論点に直接対応する。特にF4は修正指示書A-16（通いの場の統計の不一致）を、H1・H2は同C-16（H13・H14の設問がない）を、δ2・δ3は同A-13・B-22（重度在宅化と24時間対応サービスの空白）を解決する。注3）2の依頼により、新別表11事項のうち三・七・九・十・十一の5事項が対応可能となる。残る一（地勢と交通）・八（高齢者向け住まい）は自治体からの資料提供、五の一部（介護SCR）・七の一部（入所率・稼働率）・二の一部（人口メッシュ）は改修待ちとなる。注4）依頼にあたっては、①出力年度（可能な限り時系列）、②比較対象（全国・北海道・類似保険者・圏域内保険者）、③類似保険者を選ぶ場合はその選定条件、の3点を併せてご指定いただきたい。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_確認すべき指標への対応" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_ロジックモデルの構成" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_見える化の再出力依頼" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_通いの場の統計の比較" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -152,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,6 +242,15 @@
     </xf>
     <xf numFmtId="168" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -607,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1246,169 +1256,187 @@
       </c>
       <c r="D37" s="6" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>20_通いの場の統計の比較</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>総合事業調査ベースとニーズ調査ベースの違い、総合事業ベースでみた大雪の水準と3箇所の内訳。</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>施策単位での整合確認</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
+          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>記載事項への網羅性の最終確認</t>
+          <t>施策単位での整合確認</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
+          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
+          <t>記載事項への網羅性の最終確認</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
+          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>給付費・地域支援事業費の計画対実績</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>介護給付費準備基金の残高推移</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>04シートの剰余額は概算にとどまる</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>注1）第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1・第135回 資料2-1）及び第9期北海道高齢者保健福祉計画・介護保険事業支援計画の本編を受領し、07・08・17シートは原典に基づいて作成した。北海道の計画本編は本文が画像で構成されているため、第4章（計画の方向性）及び第7章第12節（上川中部圏域）の主要頁を目視により読み取っている。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
@@ -1417,8 +1445,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9048,9 +9076,9 @@
           <t>過年度及び直近の状況を確認</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>重大な課題</t>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -9060,7 +9088,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>国が示す把握方法は総合事業調査であり、大雪の第9期KPI④が用いた日常生活圏域ニーズ調査ではない。北海道の第9期KPI（通いの場への参加率3.94％→5.37％以上）も総合事業調査ベースであり、大雪の7.3％・8.8％とは定義が異なる（08シート・修正指示書A-16）。また地域包括支援センター運営状況調査は北海道のKPIのデータ源でもあり、H09・H10の代替候補となる。</t>
+          <t>通いの場は見える化F1〜F9を受領し対応済み（20シート）。総合事業ベースの参加率は令和2年度で月1回以上1.6％（北海道3.9％・全国5.2％）、週1回以上0.7％（同1.6％・2.1％）、箇所数3箇所であることを確認した。第9期KPI④が用いたニーズ調査ベース（R4 7.3％）とは統計が異なる（修正指示書A-16）。多様なサービス・活動の数（F28〜F40）、地域包括支援センターの相談体制（F15〜F25）、インセンティブ交付金における評価（W系列）は未受領で、再出力を要する。</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9840,7 +9868,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証の総括　主要所見15件</t>
+          <t>検証の総括　主要所見16件</t>
         </is>
       </c>
     </row>
@@ -10248,22 +10276,22 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>通いの場参加率の目標と実績が別の統計に基づいている</t>
+          <t>総合事業ベースでみると通いの場の水準は全国の3分の1で、低下傾向にある</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は「国が掲げている目標値8％（令和7年度）を参考に」目標10.0％を設定したが、国の8％及び北海道のKPI（3.94％→5.37％以上）は介護予防・日常生活支援総合事業の実施状況に関する調査に基づく。一方、大雪の実績（令和4年度7.3％・令和7年度8.8％）は日常生活圏域ニーズ調査における自己申告割合である。</t>
+          <t>見える化F4（総合事業の実施状況に関する調査）の月1回以上の通いの場の参加率は、大雪が平成29年度3.1％をピークに令和2年度1.6％へ低下（参加者277人→151人で45％減）。同年の北海道は3.9％、全国は5.2％で、大雪は北海道の41％・全国の31％の水準。週1回以上でも大雪0.7％に対し北海道1.6％・全国2.1％。週1回以上の通いの場の箇所数は令和2年度で3箇所にとどまり、65歳以上1万人あたり3.24箇所は全国13.12箇所の25％、北海道10.48箇所の31％。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>分母・分子の定義が異なる指標を比較して目標を設定していた。第10期基本指針の新別表も、通いの場の把握方法として総合事業調査を挙げている。したがって「国目標8％を達成」という評価も、厳密には成立しない。</t>
+          <t>第9期計画は「国が掲げている目標値8％（令和7年度）を参考に」目標10.0％を設定したが、国の8％も北海道のKPI（3.94％→5.37％以上）も総合事業調査に基づく。一方、大雪の実績（令和4年度7.3％・令和7年度8.8％）は日常生活圏域ニーズ調査の自己申告割合で、統計が異なる（同一年で総合事業ベースの4.6倍）。統計を揃えると、大雪の水準は北海道・全国を大きく下回り、北海道の第9期目標5.37％にも2.34ポイント届かない。</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>第10期は総合事業調査ベースの参加率とニーズ調査ベースの参加率を区別し、目標を設定する系列を明示する。北海道との比較には総合事業調査ベースを用いる。H05の合成指標36.0％はニーズ調査ベースであり、北海道・全国とは比較できない点を注記する。</t>
+          <t>第3章第4節の第9期評価から「国目標8％を達成」の記述を外す。第10期は総合事業調査ベースを主系列とし、ニーズ調査ベースは補完として併記する。介護予防・社会参加は第10期の重点施策として位置づけを引き上げる必要がある（修正指示書A-16）。</t>
         </is>
       </c>
     </row>
@@ -10280,22 +10308,22 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標のうち3項目は大雪でも直ちに使える</t>
+          <t>通いの場の担い手と内容に圏域固有の特徴がある</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>北海道の第9期KPIのうち、①地域包括支援センター運営状況調査の評価結果（71.6％→全国平均値以上）、②介護従事者の採用率と離職率の差（1.0％→全国平均以上）、③介護給付適正化の主要3事業の実施（100％）は、いずれも既存の全国調査又は既存データで算定できる。</t>
+          <t>令和2年度の週1回以上の通いの場3箇所の内訳は、運営主体が住民団体2・社会福祉協議会1、活動場所が公民館等1・その他2、活動内容が体操（運動）1・認知症予防1・農作業1。農作業を主な活動内容とする通いの場は全国59箇所（0.1％）・北海道1箇所（0.1％）と稀で、大雪は3箇所中1箇所（33.3％）を占める。一方、住民個人が運営する通いの場は全国19.2％・北海道28.8％あるのに対し大雪は0箇所。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>第9期計画はこれらの調査に一切言及していない。代表KPI4項目のうち3項目が独自定義であったため、北海道・全国との比較ができなかった。</t>
+          <t>第9期計画は通いの場を参加率のみで扱い、箇所数・運営主体・活動内容の分析がない。3箇所という規模では、参加率の変動が1〜2箇所の増減で大きく振れる。</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>①はH09・H10（業務記録の様式整備が必要）の代替又は補完として使える。②はH13・H14（設問がない）の代替として使え、第9期の介護人材実態調査の採用者数・退職者数から算定できる。③は給付適正化の管理指標として使える。第10期のKPI体系に組み込むことを推奨する。</t>
+          <t>農作業型の通いの場は圏域の地域特性を反映しており、第10期の介護予防・社会参加の施策で展開の核にできる可能性がある。住民個人が運営する小規模な通いの場の立ち上げ支援も全国との差が大きい領域である。第2章に箇所数・運営主体・活動内容の分析を新設する。</t>
         </is>
       </c>
     </row>
@@ -10312,22 +10340,22 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>北海道は施策の記述をロジックモデルで構成しており、これを踏襲できる</t>
+          <t>北海道の評価指標のうち3項目は大雪でも直ちに使える</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>北海道第9期計画 第5章は全8節を「（1）現状と課題／（2）関連データ／（3）施策の方向性／（4）主な事業＜インプット／目標（アウトプット）＞／（5）達成目標（アウトカム）」の5層で記述している。例えば第6節は事業4件・アウトプット目標6項目・アウトカム1項目（介護支援専門員従事者数 R4 9,718人→R8 10,331人）。</t>
+          <t>北海道の第9期KPIのうち、①地域包括支援センター運営状況調査の評価結果（71.6％→全国平均値以上）、②介護従事者の採用率と離職率の差（1.0％→全国平均以上）、③介護給付適正化の主要3事業の実施（100％）は、いずれも既存の全国調査又は既存データで算定できる。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>大雪の第9期計画は第5章が「主な取組・管理指標・主体」の3列の表のみで、現状と課題、根拠データ、実施事業、アウトプット目標がいずれもない。計画自身が「アウトプットの達成→アウトカムの達成のロジックの妥当性」を指標設定の考慮点に挙げているが、実装されていない。</t>
+          <t>第9期計画はこれらの調査に一切言及していない。代表KPI4項目のうち3項目が独自定義であったため、北海道・全国との比較ができなかった。</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>第10期基本指針案は「ロジックモデルの活用やPDCAサイクルに沿った計画策定の推進」を記載充実事項に挙げている。北海道の第5章の構成を踏襲すれば、国の要請と北海道との整合を同時に満たせる。素案の3層構造（本文12・補完4・施策管理指標）をこの記述構成に落とし込む。</t>
+          <t>①はH09・H10（業務記録の様式整備が必要）の代替又は補完として使える。②はH13・H14（設問がない）の代替として使え、第9期の介護人材実態調査の採用者数・退職者数から算定できる。③は給付適正化の管理指標として使える。第10期のKPI体系に組み込むことを推奨する。</t>
         </is>
       </c>
     </row>
@@ -10339,32 +10367,64 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>北海道は施策の記述をロジックモデルで構成しており、これを踏襲できる</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>北海道第9期計画 第5章は全8節を「（1）現状と課題／（2）関連データ／（3）施策の方向性／（4）主な事業＜インプット／目標（アウトプット）＞／（5）達成目標（アウトカム）」の5層で記述している。例えば第6節は事業4件・アウトプット目標6項目・アウトカム1項目（介護支援専門員従事者数 R4 9,718人→R8 10,331人）。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>大雪の第9期計画は第5章が「主な取組・管理指標・主体」の3列の表のみで、現状と課題、根拠データ、実施事業、アウトプット目標がいずれもない。計画自身が「アウトプットの達成→アウトカムの達成のロジックの妥当性」を指標設定の考慮点に挙げているが、実装されていない。</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針案は「ロジックモデルの活用やPDCAサイクルに沿った計画策定の推進」を記載充実事項に挙げている。北海道の第5章の構成を踏襲すれば、国の要請と北海道との整合を同時に満たせる。素案の3層構造（本文12・補完4・施策管理指標）をこの記述構成に落とし込む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>日常生活圏域の設定に人口規模の著しい偏りがある</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>第9期計画 第7節の6圏域のうち、美瑛町の朗根内地区は人口233人・高齢者82人。最大の美瑛町市街地・周辺地区は7,869人で、33.8倍の開き。</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>介護保険法第117条第2項第1号は地理的条件・人口等の社会的条件を勘案して圏域を設定することを求めるが、233人の圏域に独立したサービス基盤を割り当てることは現実的でない。</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>第10期の圏域設定を委員会の決定事項とする。統計・分析単位としての圏域と、基盤整備単位としての圏域を分けて整理する案を提示する。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率に由来し（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
         </is>
@@ -10373,7 +10433,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10386,7 +10446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10617,7 +10677,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>介護人材の必要数／需要見込みに対する供給見込みの割合</t>
+          <t>介護人材の必要数／需要見込みに対する供給見込みの割合　【提供不可】</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -10632,12 +10692,12 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>各市町村のサービス利用量を基に厚生労働省が作成したワークシートにより推計した必要人材数と、供給見込みとの比較。</t>
+          <t>指標リストには掲載されているが、大雪地区広域連合についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>北海道はこの方法で「令和8年までに約114千人、令和22年までに約129千人が必要」としている。大雪の必要人材数が同じ方法で得られれば、H13（職種別欠員率）の代替となる。事業所実態調査が業務範囲外である問題（修正指示書A-7）の実務的な回避策になる。</t>
+          <t>H13（職種別欠員率）の代替として最有力であったが使用できない。代替は、①北海道と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）を第9期の介護人材実態調査の採用者数・退職者数から算定する、②M2-a〜m（従事者数・サービス別・認定者1万対）で従事者数の推移を代替とする、の2案となる（修正指示書C-16）。</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10790,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>在宅死亡者数（介護老人保健施設／老人ホーム／自宅）</t>
+          <t>在宅死亡者数（介護老人保健施設／老人ホーム／自宅）　【提供不可】</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -10740,12 +10800,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>別表三は「死亡場所別の死亡数等について過年度の推移等を確認すること」としている。見える化のL27系列がこれに対応する。</t>
+          <t>別表三は「死亡場所別の死亡数等について過年度の推移等を確認すること」としている。見える化のL27系列がこれに対応するが、大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>在宅看取りの実態が把握でき、医療介護連携の議論と第6章の整備方針の基礎になる。</t>
+          <t>代替として、①人口動態統計の市区町村別集計（死亡数・死亡場所別）を北海道又は上川保健所経由で入手する、②3町の死亡診断書・死体検案書の集計を用いる、③O11（看取り介護加算算定者数）・O12（ターミナルケア加算）・O13（ターミナルケアマネジメント加算）で介護側の看取りの実施状況を代替する、の3案が考えられる。③は介護報酬側のため出力できる見込み。</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10822,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>看取り数（死亡診断書のみの場合も含む）</t>
+          <t>看取り数（死亡診断書のみの場合も含む）　【提供不可】</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -10772,7 +10832,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>算定回数とレセプト件数の2系列。</t>
+          <t>算定回数とレセプト件数の2系列。診療報酬側のためL系列に属する。</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -10917,27 +10977,27 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>L20〜L26／O1〜O13</t>
+          <t>O1〜O13</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>医療介護連携に関する加算等の算定状況</t>
+          <t>医療介護連携に関する加算等の算定状況（介護報酬側）　【出力可・令和5年度まで】</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>約20件</t>
+          <t>13件</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>診療報酬側：介護支援連携指導、退院時共同指導、在宅ターミナルケア。介護報酬側：退院退所加算、入院時情報連携加算、退院・退所時連携加算、緊急時等居宅カンファレンス加算、ターミナルケアマネジメント加算、緊急時訪問看護・訪問介護加算、看取り介護加算 ほか。</t>
+          <t>退院・退所時連携加算（O5）、緊急時等居宅カンファレンス加算（O4）、緊急時訪問看護加算（O2）・緊急時訪問介護加算（O3）、看護体制強化加算（O1）、特定事業所加算（O6）、医療連携強化加算（O7）・医療連携体制加算（O8）、看護・介護職員連携強化加算（O9）、配置医師緊急時対応加算（O10）、看取り介護加算（O11）、ターミナルケア加算（O12）、ターミナルケアマネジメント加算（O13）。いずれも認定者1万対。</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>別表十の「医療介護連携に関する加算の算定状況」に対応。H09（退院時支援調整実施率）を3町の業務記録で測る前に、L21（退院時共同指導）・L25（退院退所加算）・L26（入院時情報連携加算）・O5（退院・退所時連携加算）で代替できる可能性がある（修正指示書B-19の解決策）。</t>
+          <t>別表十に対応。O4・O5は受領済み（20シート参照）。H09（退院時支援調整実施率）を3町の業務記録で測る前に、O5で代替できる可能性がある（修正指示書B-19）。ただし出力は令和5年度までで、第10期の基準値としては令和5年度が最新となる。</t>
         </is>
       </c>
     </row>
@@ -10949,44 +11009,44 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>δ1-a／b／c</t>
+          <t>L20〜L26</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>レーダーチャート（地域の概況（需要）／サービス提供体制（供給）／医療介護連携）</t>
+          <t>医療介護連携に関する加算等の算定状況（診療報酬側）　【提供不可】</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>地域分析のレーダーチャート。</t>
+          <t>介護支援連携指導（L20）、退院時共同指導（L21）、在宅ターミナルケア（L24）、退院退所加算（L25）、入院時情報連携加算（L26）ほか。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>第10期基本指針案が別表十の把握方法に「見える化システム（新）レーダーチャート」を挙げており、既存のδ1-cがこれに相当すると考えられる。3つの視点を1枚で示せるため委員会資料に適する。</t>
+          <t>大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。医療側からの連携の実施状況は、上川中部圏域の医療機関への照会又は北海道の医療計画・地域医療構想の資料で補う必要がある。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>十一 認知症</t>
+          <t>十 医療介護連携</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>J16／J17／J18</t>
+          <t>δ1-a／b／c</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援チームの訪問実績／認知症地域支援推進員の配置人数／認知症カフェの設置主体別箇所数</t>
+          <t>レーダーチャート（地域の概況（需要）／サービス提供体制（供給）／医療介護連携）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -10996,12 +11056,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>いずれも実施状況の実数。</t>
+          <t>地域分析のレーダーチャート。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>別表十一の「ピアサポート活動や就労等の社会参加の機会、場の数・利用者数」の一部に対応。3町の認知症施策の実施状況を定量的に比較できる。</t>
+          <t>第10期基本指針案が別表十の把握方法に「見える化システム（新）レーダーチャート」を挙げており、既存のδ1-cがこれに相当すると考えられる。3つの視点を1枚で示せるため委員会資料に適する。</t>
         </is>
       </c>
     </row>
@@ -11013,364 +11073,2301 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>J16／J17／J18</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>認知症初期集中支援チームの訪問実績／認知症地域支援推進員の配置人数／認知症カフェの設置主体別箇所数</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>いずれも実施状況の実数。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>別表十一の「ピアサポート活動や就労等の社会参加の機会、場の数・利用者数」の一部に対応。3町の認知症施策の実施状況を定量的に比較できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>十一 認知症</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
           <t>J1〜J15</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>認知症関連研修の修了者数（サポート医、かかりつけ医、病院勤務者、歯科医師、薬剤師、看護職員、介護実践者等）</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>15件</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>研修種別ごとの修了者数。</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>北海道のKPI「専門医療機関との連携により早期診断・早期対応につなげる体制を構築している市町村数」の裏付けとなる。第5章の認知症施策のアウトプット指標に使える。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>3　指標リストに存在しない指標（令和8年度以降の改修待ち）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>3　発注者に確認した提供可否（令和8年7月29日時点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>系列</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>提供可否</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>収録年度</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>通いの場（F1〜F9）</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>受領済み</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>平成25年度〜令和2年度</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>F1・F2・F3（週1回以上の参加率・参加者数・箇所数）、F4・F5（月1回以上の参加率・参加者数）、F7・F8・F9（週1回以上の箇所数の運営主体別・活動場所別・活動内容別）を受領。20シートで分析。令和3年度以降の収録の有無は要確認。</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>医療介護連携に関する加算（介護報酬側）</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>出力可</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>令和5年度まで</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>O4（緊急時等居宅カンファレンス加算）・O5（退院・退所時連携加算）を受領。残るO1・O2・O3・O6〜O13も出力できる見込み。第10期の基準値は令和5年度が最新となる。</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>介護人材の必要数（H1・H2）</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>提供不可</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>指標リストには掲載されているが大雪についてはデータ登録がない。H13（職種別欠員率）の代替として最有力であったが使用できない。</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>医療機関・看取り・診療報酬側の連携指標（L1〜L28）</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>提供不可</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>大雪についてはデータ登録がない。別表三（死亡場所別の死亡数）と別表十の診療報酬側の指標が取得できない。</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>δ</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス自給率（δ2・δ3）</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>出力可否の確認を依頼中。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>サービス提供事業所数（K1〜K3）</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>従事者数（M2-a〜m）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>H1・H2が提供不可となったため、H13の代替としての重要度が上がっている。</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>認知症施策（J1〜J18）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価指標</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>注）提供不可となったH系列・L系列に依存していた代替案は組み替えを要する。H13（職種別欠員率）はH1・H2が使えないため、北海道と同じ「採用率と離職率の差」（第9期の介護人材実態調査の採用者数・退職者数から算定）又はM2系列（従事者数）での代替となる。別表三（死亡場所別の死亡数）はL27が使えないため、人口動態統計の市区町村別集計、3町の死亡診断書の集計、又はO11〜O13（看取り介護加算・ターミナルケア加算）での代替となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>4　指標リストに存在しない指標（令和8年度以降の改修待ち）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>別表の事項</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>指針案の記載</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>現状</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>代替</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="76" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>入所率・稼働率</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>七 介護保険施設・事業所の状況</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>把握方法に「見える化システム（新）入所率、職員数推移」と記載（下線＝令和8年度以降に新たに把握が可能となる指標）</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>指標リストに該当なし。改修待ち。</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>N8-a／N8-b（通所リハビリテーション定員あたり利用延人員数）が稼働率に近い。入所率は定員（D25〜D27・受領済）と受給者数（D1・受領済）から概算できるが、受給者は域外施設の利用者を含むため厳密な入所率にはならない。事業所別の入所率は自治体の指定台帳又は施設への照会が必要。</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="76" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="76" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>介護SCR（性・年齢調整済みレセプト出現比）</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>五 介護サービス等の利用状況</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>「介護サービスの提供状況の地域差を示す指標（介護SCR）」を新たに提示</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>指標リストに該当なし。改修待ち。</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>D49（地域差指数）が受領済みで、調整済み給付月額1.08・調整済み認定率1.02・受給率1.08・受給者単価1.06の4指標が得られている。サービス種類別の調整済み値は改修後に取得する。</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="76" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="76" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>類似保険者比較</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>―（業務仕様書４（４）が要求）</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>指針案の別表には記載なし。仕様書が「類似保険者との比較分析」を明示。</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>指標リストに「類似」の語なし。δ3系列の「地域比較」で比較対象を選択する機能と考えられるが、選定条件は受領資料から確認できない。</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>出力時に比較対象の選定条件（人口規模、高齢化率、都市規模等）を併せて記録していただく。北海道計画 第7章第12節の上川中部圏域の分布図は圏域内比較であり、旭川市（325,162人）を含むため人口規模が近い保険者との比較にはならない。</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="76" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="76" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>人口メッシュ</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>二 人口構造</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>把握方法に「見える化システム（新）人口メッシュ」と記載</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>指標リストに該当なし。改修待ち。</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の特定（別表一）に有用。改修後に取得する。当面は美瑛町の4圏域（旭・北西、美馬牛、朗根内、市街地・周辺）の区分で代替する。</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>4　介護サービス自給率を見える化以外で把握する場合の代替</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>5　介護サービス自給率を見える化以外で把握する場合の代替</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>自給率の算定可否</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="68" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="68" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>介護保険事業状況報告（月報・年報）</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>算定できない</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>様式が保険者単位の集計であり、サービスを提供した事業所の所在地の情報を持たない。大雪の被保険者が旭川市の事業所を利用した給付も、大雪の給付として計上される。したがって自給率の分子（自市町村内の事業所による給付月額）が取り出せない。</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>受給者数・給付費の総額（分母に相当）は取得できる。</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="68" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="68" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>介護給付費等実態統計（旧・介護給付費実態調査）</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>算定できない</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>保険者所在地別と事業所所在地別の集計はあるが、公表は都道府県単位が基本であり、市町村レベルで両者を突合した表は公表されていない。</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="68" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="68" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>国保連合会から保険者に提供される給付実績情報</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>算定できる（推奨）</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>介護給付費明細書（レセプト）の内容が事業所番号付きで提供される。事業所番号と指定事業所台帳（所在地）を突合すれば、自市町村内か域外かを判定できる。見える化のδ2と同じデータソースであるため、値も一致するはず。</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>毎月提供されているため時系列も作成できる。見える化の定義に合わせるには「毎年9月サービス提供分」で集計する。</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="68" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="68" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>保険者の介護保険基幹システムの給付実績照会</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>算定できる</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>多くのシステムで事業所別の給付費・受給者数を集計できる。</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>システムの仕様により出力可否が異なる。</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="68" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="68" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>地域密着型サービスの指定台帳</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>地域密着型サービスは保険者が指定するため、原則として自市町村の被保険者のみが利用する。したがって地域密着型の自給率はほぼ100％と見なせる。</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>市町村間の同意による他保険者被保険者の利用がある場合は例外となる。</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="70" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>注1）本シートは受領した「指標リスト（目的別）」（見える化システムの指標一覧・994行）に基づく。指標IDが付されているものは906件で、うち受領済みはA系列13件・B系列27件・C系列4件・D系列199件・P系列ほかを含む182件（20.1％）である。注2）1の最優先6項目（計54件）は、いずれも本検証で明らかになった論点に直接対応する。特にF4は修正指示書A-16（通いの場の統計の不一致）を、H1・H2は同C-16（H13・H14の設問がない）を、δ2・δ3は同A-13・B-22（重度在宅化と24時間対応サービスの空白）を解決する。注3）2の依頼により、新別表11事項のうち三・七・九・十・十一の5事項が対応可能となる。残る一（地勢と交通）・八（高齢者向け住まい）は自治体からの資料提供、五の一部（介護SCR）・七の一部（入所率・稼働率）・二の一部（人口メッシュ）は改修待ちとなる。注4）依頼にあたっては、①出力年度（可能な限り時系列）、②比較対象（全国・北海道・類似保険者・圏域内保険者）、③類似保険者を選ぶ場合はその選定条件、の3点を併せてご指定いただきたい。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A41:G41"/>
+  <mergeCells count="4">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A56:G56"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>通いの場参加率の2つの統計と、総合事業ベースでみた大雪の水準</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見える化F1〜F9（厚生労働省「介護予防事業及び介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」）を受領し、第9期計画の代表KPI④が用いた日常生活圏域ニーズ調査と突合した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　2つの統計の違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>日常生活圏域ニーズ調査</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>調査主体・方法</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>保険者が事業実績を国へ報告（悉皆）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>住民への標本調査（自己申告）</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>前者は事業として把握している通いの場の実績、後者は住民が「参加している」と答えた割合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>通いの場の参加者実人数</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>「通いの場に月1回以上参加している」と回答した人</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>後者は総合事業に位置づけられていない自主的な活動への参加も含まれる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>分母</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>65歳以上人口</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>調査の有効回答者数</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>大雪の値</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>令和2年度 1.6％（月1回以上）</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>令和4年度 7.3％／令和7年度 8.8％</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>同時期で比較すると後者は前者の約4.6倍。同じ「通いの場参加率」という名称でも別の統計である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>国の目標8％（令和7年度まで）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>この統計による</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画は国の8％を参考にニーズ調査ベースの目標10.0％を設定しており、統計が一致していない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>3.94％（R3）→5.37％以上（R8）</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>北海道も総合事業調査ベース。大雪の実績と直接比較するにはこの系列が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針の新別表 九</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>把握方法として明示されている</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>国は総合事業調査を通いの場の把握方法としている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2　総合事業ベースの推移（％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>H25</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>H28</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上　大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度3.1％をピークに令和2年度1.6％へ48％低下。参加者は277人→151人で45％減。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上　北海道</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>令和元年度4.8％をピークに令和2年度3.9％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上　全国</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>令和元年度6.7％をピークに令和2年度5.2％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>月1回以上　大雪／全国</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度に0.63まで縮まったが、令和2年度は0.31へ拡大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>週1回以上　大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>平成25年度は大雪1.0％が北海道・全国0.7％を上回っていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>週1回以上　北海道</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>週1回以上　全国</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>平成25年度0.7％から令和元年度2.6％へ3.7倍。大雪は同期間で1.0％→0.6％と0.6倍に低下し逆転された。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>3　週1回以上の通いの場の箇所数（箇所）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>H25</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>H28</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度7箇所をピークに令和2年度3箇所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>490</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>598</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>920</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>924</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1273</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>1720</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>1766</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>一貫して増加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>11712</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>15477</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>20336</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>25266</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>33461</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>41509</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>51032</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>47181</v>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>令和元年度をピークに令和2年度は減少。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>令和2年度</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>箇所数</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上人口</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>1万人あたり箇所数</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>全国比</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>9251</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>全国の25％、北海道の31％の密度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="n">
+        <v>1766</v>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>1685744</v>
+      </c>
+      <c r="D32" s="33" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="E32" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>全国の80％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="n">
+        <v>47181</v>
+      </c>
+      <c r="C33" s="33" t="n">
+        <v>35974231</v>
+      </c>
+      <c r="D33" s="33" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>注）65歳以上人口は、大雪は見える化F4の掲載値、北海道・全国は参加者数と参加率から逆算した推計値。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>4　大雪の週1回以上の通いの場3箇所の内訳（令和2年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>大雪（箇所）</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>大雪（％）</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>北海道（％）</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>全国（％）</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>【運営主体】住民団体</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>全国・北海道と同様に主流。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>【運営主体】社会福祉協議会</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>全国2.1％に対し大雪は3箇所中1箇所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>【運営主体】住民個人</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="35" t="inlineStr">
+        <is>
+          <t>全国19.2％・北海道28.8％あるのに大雪は0箇所。小規模な住民主体の立ち上げ支援が課題。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>【活動場所】公民館・自治会館・集会所</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>全国80.3％・北海道87.2％が公民館等。大雪は1箇所のみ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>【活動場所】その他</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>全国5.4％に対し大雪は3箇所中2箇所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>【活動内容】体操（運動）</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>全国79.8％が体操。大雪は1箇所のみ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>【活動内容】認知症予防</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>全国1.4％に対し大雪は3箇所中1箇所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>【活動内容】農作業</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>全国59箇所（0.1％）・北海道1箇所（0.1％）と稀な類型。大雪は3箇所中1箇所を占める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>5　第9期の評価と第10期への反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="68" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>第9期の代表KPI④の評価</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>「国が掲げている目標値8％（令和7年度）を参考に」目標10.0％を設定し、実績8.8％（令和7年度）で自主目標に0.2ポイント未達、国目標8％は達成という評価であった。しかし国の8％は総合事業調査ベースであり、実績はニーズ調査ベースであるため、「国目標を達成」という評価は成立しない。</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>第3章第4節から当該記述を外し、ニーズ調査ベースの系列であることを明記する。総合事業ベースでは令和2年度1.6％で、北海道の第9期目標5.37％を2.34ポイント下回る。</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="68" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>第10期の主系列の決定</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>総合事業調査ベースは北海道・全国・国目標と比較でき、事業実績に基づく悉皆データである。ニーズ調査ベースは自主的な活動への参加も含み、H05の社会参加6区分の合成指標（36.0％）と連続する。</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>総合事業調査ベースを主系列とし、ニーズ調査ベースを補完として併記する。H05の合成指標は他地域と比較できない旨を資料編 資料1に注記する。</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="68" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>施策上の位置づけ</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>総合事業ベースで全国の31％、箇所数の密度で全国の25％という水準は、第9期計画が代表KPIに掲げた領域としては低い。しかも平成29年度をピークに低下している。</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・社会参加を第10期の重点施策として位置づけを引き上げる。北海道の第9期評価指標「介護予防に資する住民主体の通いの場がある市町村数 R4 159→R8 全179市町村」との関係でも、大雪は箇所数の確保そのものが課題である。</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="68" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>圏域特性の活用</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>農作業を主な活動内容とする通いの場は全国0.1％・北海道0.1％と稀だが、大雪は3箇所中1箇所を占める。</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>農作業型の通いの場を第10期の介護予防・社会参加の施策の核の一つとして位置づけることを検討する。JAグループ・農業関係団体との連携が考えられる。</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="68" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>小規模な立ち上げ支援</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>住民個人が運営する通いの場は全国19.2％・北海道28.8％あるのに対し、大雪は0箇所である。</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>小規模・低コストで立ち上げられる住民個人主体の通いの場の支援策を第5章に位置づける。生活支援コーディネーターの活動（北海道の評価指標②）と接続させる。</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="68" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>データの更新</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>見える化F1〜F9のデータは令和2年度までで、令和3年度以降が収録されていない。</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査は継続しているため、令和3〜6年度の値の有無を確認する。収録されていない場合は、保険者が国へ報告した調査票の写しの提供を依頼する。</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>6　参考：医療介護連携に関する加算の算定状況（見える化O4・O5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>O5 退院・退所時連携加算　大雪［認定者1万対］</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="28" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>令和5年度は北海道4.15の93％、全国6.65の58％。実数は年0〜1人で推移しており、1万対の値は1人の有無で大きく振れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>O5 退院・退所時連携加算　北海道</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="G59" s="19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>4.0前後で安定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>O5 退院・退所時連携加算　全国</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>緩やかに上昇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>O4 緊急時等居宅カンファレンス加算　大雪</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>実数はいずれの年度も0人と記録されている。1万対の値との関係は定義の確認を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>O4 緊急時等居宅カンファレンス加算　北海道</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>全国を下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>O4 緊急時等居宅カンファレンス加算　全国</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G63" s="19" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>0.2前後で安定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="56" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>注1）O4・O5は平成27年度（O4）・平成30年度（O5）から令和5年度までの収録で、令和6年度以降はない。第10期の基準値としては令和5年度が最新となる。注2）O5（退院・退所時連携加算）は特定施設入居者生活介護・地域密着型特定施設入居者生活介護に係る加算で、居宅介護支援における退院時の連携全体を表すものではない。居宅介護支援側の退院退所加算（L25）・入院時情報連携加算（L26）は診療報酬側のL系列に属し、大雪についてはデータ登録がなく出力できない。注3）大雪の実数は年0〜1人であり、指標として単独では安定しない。H09（退院時支援調整実施率）の代替とする場合は、O1〜O13の複数の加算を合成するか、3町の業務記録との併用が必要である。注4）1万対の値と実数の関係が読み取れないため、分母と集計期間の定義の確認を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートは見える化F1（週1回以上の参加率）・F2（同参加者数）・F3（同箇所数）・F4（月1回以上の参加率）・F5（同参加者数）・F7（週1回以上の箇所数　主な運営主体別）・F8（同　主な活動場所別）・F9（同　主な活動内容別）による。注2）令和2年度は全国・北海道とも参加率が前年度から低下しており、新型コロナウイルス感染症の影響を含むと考えられる。大雪の低下幅（月1回以上で1.1ポイント）は全国（1.5ポイント）・北海道（0.9ポイント）と同程度だが、水準そのものが低いため相対的な影響は大きい。注3）大雪の箇所数は3箇所であり、1箇所の増減が参加率を大きく動かす。率のみでの評価は避け、箇所数・参加者数と併せて評価する必要がある。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A64:J64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -28,6 +28,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_ロジックモデルの構成" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_見える化の再出力依頼" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_通いの場の統計の比較" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_事業所数と供給構造" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_従事者数の状況" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_交付金評価の分析" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -251,6 +254,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -617,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -927,7 +939,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>検証で確認した主要所見12件。重要度と第10期での対応方針。</t>
+          <t>検証で確認した主要所見20件。重要度と第10期での対応方針。</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1274,169 +1286,223 @@
       </c>
       <c r="D38" s="6" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>21_事業所数と供給構造</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>全28サービス種別の事業所数（H24〜R6）。域内に事業所が存在しない11種別の特定と、定員・給付との突合。</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>22_従事者数の状況</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>13サービスの従事者数（H29〜R6）と職種別内訳。H13（職種別欠員率）の代替としての評価。</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>23_交付金評価の分析</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価得点（令和5年調査）。総合得点・目標別・指標群別・0点項目と、H01のデータ源の確定。</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>3　本検証で用いなかった資料（未入手）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>施策単位での整合確認</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>記載事項への網羅性の最終確認</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>給付費・地域支援事業費の計画対実績</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>04シートは見える化の必要保険料月額による間接評価</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高推移</t>
+          <t>第9期北海道計画 第5章「計画の具体的な展開」（52頁）の本文</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+          <t>施策単位での整合確認</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>04シートの剰余額は概算にとどまる</t>
+          <t>08シートは基本目標・評価指標・圏域の記載にとどまる。本文が画像で構成されているため、施策の詳細は目視での読み取りを継続する</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>保険料収納率の実績</t>
+          <t>第10期介護保険事業（支援）計画 基本指針（告示）</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提確認</t>
+          <t>記載事項への網羅性の最終確認</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+          <t>07・17シートは部会資料（第134回・第135回）の原典に基づく評価。告示は年内の予定であり、告示後に最終確認を要する</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>令和6〜8年度の介護保険特別会計決算・事業実績</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>給付費・地域支援事業費の計画対実績</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>04シートは見える化の必要保険料月額による間接評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の残高推移</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>第9期の剰余の帰趨と第10期の取崩余力</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>04シートの剰余額は概算にとどまる</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納率の実績</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提確認</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>第10期の予定収納率99.0%の妥当性が検証できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>3町の第10期高齢者福祉計画の検討資料</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>第10期の施策体系の整合</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>09シートは第9期どうしの対照にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>注1）第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1・第135回 資料2-1）及び第9期北海道高齢者保健福祉計画・介護保険事業支援計画の本編を受領し、07・08・17シートは原典に基づいて作成した。北海道の計画本編は本文が画像で構成されているため、第4章（計画の方向性）及び第7章第12節（上川中部圏域）の主要頁を目視により読み取っている。注2）判定の「概ね妥当」は第10期で方針を変えなくてよい事項、「一部課題」は前提の見直しが必要な事項、「重大な論点あり」は委員会での決定を要する事項を指す。</t>
         </is>
@@ -1445,8 +1511,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A51:D51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7092,7 +7158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7179,7 +7245,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>見える化B5-a／認定台帳</t>
+          <t>見える化W144（交付金評価指標Ⅳ-5）</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -7189,17 +7255,17 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>要決定</t>
+          <t>算定済</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>本検証で75歳以上の認定率が平成30年3月末35.3％から令和8年3月末33.5％へ、85歳以上が令和2年3月末63.7％から61.6％へ低下していることを確認した。全体では＋1.0ポイント上昇しており、年齢調整の必要性が裏付けられた。</t>
+          <t>本検証で75歳以上の認定率が平成30年3月末35.3％から令和8年3月末33.5％へ、85歳以上が令和2年3月末63.7％から61.6％へ低下していることを確認した。全体では＋1.0ポイント上昇しており、年齢調整の必要性が裏付けられた。さらにW144により、性・年齢調整済み要介護2以上の認定率が令和5年調査で9.25％、全国8.99％・北海道8.59％を上回ることを確認した。W145の変化率は大雪＋1.76に対し全国▲0.37・北海道▲1.71で、大雪のみ上昇している。</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>採用は妥当。ただし見える化には2系列あり、【注目する地域のみ】18.4％は他地域と比較できない。【他地域と比較】16.7％の採用を推奨（修正指示書A-10）。</t>
+          <t>採用は妥当。データ源はW144（保険者機能強化推進交付金 評価指標Ⅳ-5「健康寿命延伸の状況（性・年齢調整済み要介護2以上の認定率）」）とすることを推奨する。国が全保険者を共通の方法で毎年算定しており、全国・北海道と直接比較できるため、見える化B5-aの2系列（【注目する地域のみ】18.4％／【他地域と比較】16.7％）の選択問題も解消する（修正指示書A-10）。基準値9.25％、目標は「全国平均以下」とする。現に全国を上回りかつ上昇しているため、「維持」ではなく「低下」を目標とすべきである。</t>
         </is>
       </c>
     </row>
@@ -7683,27 +7749,27 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査</t>
+          <t>見える化M2-a〜m／介護人材実態調査</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>設問追加が必要</t>
+          <t>確保（定義の変更を要する）</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>未受領</t>
+          <t>算定済</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査は仕様書の対象4調査に含まれるが、第9期の同調査は職員数・男女比・就業形態・年齢構成・在職年数・直前の職場・資格・採用退職・勤務時間を把握しており、「必要常勤換算数」の設問は確認できない。</t>
+          <t>介護人材実態調査は仕様書の対象4調査に含まれるが、第9期の同調査は職員数・男女比・就業形態・年齢構成・在職年数・直前の職場・資格・採用退職・勤務時間を把握しており、「必要常勤換算数」の設問は確認できない。見える化の介護人材の必要数（H1・H2）はデータ登録がなく提供不可であることが確定した。一方、M2-a〜m（13サービスの職種別従事者数、平成29年度〜令和6年度）を受領し、介護老人福祉施設で准看護師7→3人、生活相談員5→3人、機能訓練指導員2→1人といった特定職種の減少を確認した。</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>第10期の調査票に必要数の設問があるか確認する。ない場合は「採用者数－退職者数」の差分や求人継続期間等での代替を検討する。</t>
+          <t>「職種別欠員率」から「職種別従事者数（認定者1万対）の推移」へ定義を改めることを推奨する（22シート4）。欠員率は必要数が得られない以上算定できないが、従事者数の推移は全国・北海道と比較可能な形で毎年得られる。あわせて介護人材実態調査の採用者数・退職者数から北海道と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）を算定し、北海道の第9期評価指標⑥と接続する（修正指示書C-16）。</t>
         </is>
       </c>
     </row>
@@ -7873,16 +7939,16 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>H02・H04・H05・H15</t>
+          <t>H01・H02・H04・H05・H13・H15</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会の資料に基準値を掲載できる。H01は系列の決定後に算定する。</t>
+          <t>第1回委員会の資料に基準値を掲載できる。H01は見える化W144の受領により9.25％（令和5年調査）と確定した。H13は定義をM2系列の従事者数の推移へ改める前提で算定済み。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -7897,16 +7963,16 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>H06・H11・H13</t>
+          <t>H06・H11</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>仕様書の対象4調査に含まれる。集計データの受領後に基準値を算定する。H13は必要常勤換算数の設問の有無を確認する。</t>
+          <t>仕様書の対象4調査に含まれる。集計データの受領後に基準値を算定する。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
@@ -7917,20 +7983,20 @@
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>系列の決定が必要</t>
+          <t>データ源が未確保</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>H07・H08・H12・H16</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>【他地域と比較】16.7％の採用を推奨（修正指示書A-10）。</t>
+          <t>在宅介護実態調査（H07・H08）と事業所実態調査（H12・H16）が仕様書の対象外。業務範囲の決定又は代理指標への振替が必要（修正指示書A-7・A-9）。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
@@ -7941,20 +8007,20 @@
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>データ源が未確保</t>
+          <t>業務記録の様式整備が必要</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16</t>
+          <t>H09・H10</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>在宅介護実態調査（H07・H08）と事業所実態調査（H12・H16）が仕様書の対象外。業務範囲の決定又は代理指標への振替が必要（修正指示書A-7・A-9）。</t>
+          <t>3町の地域包括支援センターの記録様式を統一する必要がある。初年度は様式整備を管理指標とし、基準値の設定を令和10年度からとする案を検討する。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
@@ -7965,20 +8031,20 @@
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>業務記録の様式整備が必要</t>
+          <t>設問の追加・代替が必要</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>H09・H10</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>3町の地域包括支援センターの記録様式を統一する必要がある。初年度は様式整備を管理指標とし、基準値の設定を令和10年度からとする案を検討する。</t>
+          <t>採用者の12か月後の在職を追跡する設問がない。年間離職率での代替を検討する。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -7989,7 +8055,7 @@
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>設問の追加・代替が必要</t>
+          <t>認定台帳からの抽出が必要</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -7997,12 +8063,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>採用者の12か月後の在職を追跡する設問がない。年間離職率での代替を検討する。</t>
+          <t>新規認定者数の年度別・年齢別の抽出可否を確認する。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -8010,40 +8076,16 @@
       <c r="G29" s="6" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr"/>
     </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>認定台帳からの抽出が必要</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>新規認定者数の年度別・年齢別の抽出可否を確認する。</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="56" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>注1）16項目のうち、令和9年度当初から実測できる見通しが立っているのは8項目（H01・H02・H04・H05・H06・H11・H13・H15）である。残り8項目は、業務範囲の決定（4項目）、様式整備（2項目）、設問追加又は代替（1項目）、台帳抽出（1項目）を要する。注2）第9期は5基本目標19施策に対し代表KPIが4項目で評価範囲が不足していた。第10期の16項目は範囲としては妥当だが、半数について測定手段が未確定であり、このまま計画に掲載すると第9期と同じ「評価不能」の状態を招く。第1回委員会で測定手段まで含めて決定することを推奨する。注3）「基準値」欄の「算定済」は本検証で値を算定したもの、「算定可」は資料受領後に算定できるもの、「未受領」は調査データの受領待ち、「算定不可」はデータ源が確保できていないものを指す。</t>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>注1）16項目のうち、令和9年度当初から実測できる見通しが立っているのは8項目（H01・H02・H04・H05・H06・H11・H13・H15）である。うちH01とH13は令和8年7月29日の見える化の追加受領（W144・M2系列）により確定した。残り8項目は、業務範囲の決定（4項目）、様式整備（2項目）、設問追加又は代替（1項目）、台帳抽出（1項目）を要する。注2）第9期は5基本目標19施策に対し代表KPIが4項目で評価範囲が不足していた。第10期の16項目は範囲としては妥当だが、半数について測定手段が未確定であり、このまま計画に掲載すると第9期と同じ「評価不能」の状態を招く。第1回委員会で測定手段まで含めて決定することを推奨する。注3）「基準値」欄の「算定済」は本検証で値を算定したもの、「算定可」は資料受領後に算定できるもの、「未受領」は調査データの受領待ち、「算定不可」はデータ源が確保できていないものを指す。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -8940,7 +8982,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>受給率・1人あたり費用額・算定回数は図表集15・18・19・21・22シートで対応済み。自市町村内の事業所によるサービス提供割合（介護サービス自給率）と介護SCR（性・年齢調整済みレセプト出現比）は新規指標で受領データにない。自給率は3町の住民が旭川市の事業所を利用している度合いを示すため、圏域論の基礎資料となる。再出力を依頼する。</t>
+          <t>受給率・1人あたり費用額・算定回数は図表集15・18・19・21・22シートで対応済み。自市町村内の事業所によるサービス提供割合（介護サービス自給率＝δ2・δ3）は大雪についてデータ登録がなく提供不可であることが確定した（令和8年7月29日）。国保連の給付実績情報から算定する（19シート5）。ただしK系列の受領により、域内事業所がゼロの11種別については自給率0％と特定できた（21シート）。介護SCR（性・年齢調整済みレセプト出現比）は見える化の改修待ちで、当面はD49の地域差指数（給付月額1.08・認定率1.02・受給率1.08・受給者単価1.06）で代替する。</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9056,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>定員と要支援・要介護者1人あたり定員は図表集21シートで対応済み。入所率・稼働率は新規指標で受領データにない。入所率は「認定者504人が未利用」（修正指示書A-12）の要因分析に直結するため、H12（必要サービス未充足率）の代理指標として最も有力。再出力を依頼する。</t>
+          <t>事業所数（K1-a〜e／K2-a〜c／K3-a〜t、全28種別）と従事者数（M2-a〜m、13サービス）を受領し、検証報告書21・22シートで対応済み。定員と1人あたり定員は図表集21シートで対応済み。28種別中11種別で域内事業所がゼロであること、定期巡回・夜間対応・看多機は制度創設以来13年間ゼロであることを確定した。残る入所率・稼働率は新規指標で見える化の改修待ち。入所率は「認定者504人が未利用」（修正指示書A-12）の要因分析に直結するため、H12（必要サービス未充足率）の代理指標として最も有力。3町の指定台帳又は施設への照会で補う。</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9130,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>通いの場は見える化F1〜F9を受領し対応済み（20シート）。総合事業ベースの参加率は令和2年度で月1回以上1.6％（北海道3.9％・全国5.2％）、週1回以上0.7％（同1.6％・2.1％）、箇所数3箇所であることを確認した。第9期KPI④が用いたニーズ調査ベース（R4 7.3％）とは統計が異なる（修正指示書A-16）。多様なサービス・活動の数（F28〜F40）、地域包括支援センターの相談体制（F15〜F25）、インセンティブ交付金における評価（W系列）は未受領で、再出力を要する。</t>
+          <t>通いの場は見える化F1〜F9を受領し対応済み（20シート）。総合事業ベースの参加率は令和2年度で月1回以上1.6％（北海道3.9％・全国5.2％）、週1回以上0.7％（同1.6％・2.1％）、箇所数3箇所であることを確認した。第9期KPI④が用いたニーズ調査ベース（R4 7.3％）とは統計が異なる（修正指示書A-16）。インセンティブ交付金における評価（W126〜W145）を受領し、23シートで対応済み。総合得点332.0点は全国422.4点の78.6％で、活動指標群は全国の23.2％にとどまる一方、成果指標群は123.5％という構造を特定した。残る多様なサービス・活動の数（F28〜F40）、地域包括支援センターの相談体制（F15〜F25）は未受領。</t>
         </is>
       </c>
     </row>
@@ -9113,9 +9155,9 @@
           <t>管内事業所の医療介護連携に関する各種加算の算定実績について、過年度及び直近の状況等を確認</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>未対応</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -9125,7 +9167,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>加算の算定実績は保険者が給付実績から直接把握できる。第10期のH09（退院時支援調整実施率）を業務記録で測る前に、加算の算定実績で代替できる可能性がある（退院時共同指導加算、入退院支援加算等）。見える化の新機能で再出力を依頼する。</t>
+          <t>介護報酬側のO4（緊急時等居宅カンファレンス加算）・O5（退院・退所時連携加算）を受領し、20シートで対応済み。O5は令和5年度で認定者1万対3.88（全国6.65の58％）だが実数は年0〜1人。残るO1〜O3・O6〜O13も出力できる見込み（令和5年度まで）。診療報酬側のL20〜L26は大雪についてデータ登録がなく提供不可であることが確定した。交付金評価では支援Ⅲ（在宅医療・在宅介護連携）が全国の38.2％で全8目標中最低、入退院支援・人生の最終段階における支援はいずれも0点である（23シート）。</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9204,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は認知症の語を114回用いているが、認知症の人の数の推計値を掲載していない。北海道は令和22年に道内で約35.5〜42.1万人と推計している（北海道計画 図表3-1）。大雪の推計値の算出と、3町の認知症カフェ・チームオレンジ等の実数の把握が必要。</t>
+          <t>第9期計画は認知症の語を114回用いているが、認知症の人の数の推計値を掲載していない。北海道は令和22年に道内で約35.5〜42.1万人と推計している（北海道計画 図表3-1）。見える化のJ系列（J1〜J18）は大雪についてデータ登録がなく提供不可であることが確定した（令和8年7月29日）ため、3町への直接照会に切り替える。交付金評価では支援Ⅱ（認知症総合支援）が全国の66.6％、認知症地域支援推進員の業務の状況が全国の33.9％、認知症サポーター数が41.7％である（23シート）。また認知症対応型通所介護は平成27年度に消滅、認知症GHも令和4年度に1事業所減となっており（21シート）、認知症の受け皿は10年間で減少方向にある。</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9240,7 @@
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="44" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>対応済み</t>
@@ -9214,86 +9256,86 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>図表集及び本報告書で対応済み。人口メッシュのみ再出力を依頼する。</t>
+          <t>図表集及び本報告書で対応済み。人口メッシュのみ見える化の改修待ち。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr"/>
     </row>
-    <row r="20" ht="44" customHeight="1">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>五 介護サービス等の利用状況、七 介護保険施設・事業所の状況</t>
+          <t>五 介護サービス等の利用状況、七 介護保険施設・事業所の状況、九 地域支援事業の状況、十 医療介護連携の状況</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>既存指標は対応済み。新規指標（自給率、介護SCR、入所率、稼働率、職員数推移）の再出力を依頼する。</t>
+          <t>K・M・W・F・O系列の受領により、七・九・十が前進した。残る未取得は、五の自給率（提供不可→国保連の給付実績情報で代替）と介護SCR（改修待ち）、七の入所率・稼働率（改修待ち）、九のF15〜F25・F28〜F40（再出力）、十の診療報酬側L系列（提供不可）である。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
     </row>
-    <row r="21" ht="44" customHeight="1">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>重大な課題</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>六 介護サービス見込量、九 地域支援事業の状況</t>
+          <t>六 介護サービス見込量</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>六は在宅介護実態調査が業務範囲外（A-9）、九は通いの場の定義不一致（A-16）。いずれも基本指針が求める把握手段が確保できていない。</t>
+          <t>国が把握方法として明示する在宅介護実態調査が業務仕様書４（３）の対象4調査に含まれておらず、H07・H08のデータ源もない（修正指示書A-9）。業務範囲の決定を要する。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="44" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>一 地勢と交通、三 人口動態、八 高齢者向け住まい、十 医療介護連携、十一 認知症</t>
+          <t>一 地勢と交通、三 人口動態、八 高齢者向け住まい、十一 認知症</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>いずれもデータの入手が前提。八と十一は第10期の基本的記載事項・任意記載事項に直結する。</t>
+          <t>いずれも見える化以外からの入手が前提。三はL27・L28が提供不可のため人口動態統計又は3町の集計、十一はJ系列が提供不可のため3町への直接照会となる。八と十一は第10期の基本的記載事項・任意記載事項に直結する。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>注1）本別表は第10期基本指針に新設される案であり、告示前である。告示後に最終確認を要する。注2）11事項のうち、現時点で確認できているのは2事項にとどまる。うち5事項（五の一部、七の一部、三、十、二の人口メッシュ）は見える化システムの再出力で対応でき、3事項（一、八、十一）は発注者・3町からの資料提供で対応できる。残る2事項（六、九）は業務範囲又は指標定義の決定を要する。注3）特に「七 入所率・稼働率」と「五 自市町村内の事業所によるサービス提供割合（介護サービス自給率）」は、本検証で明らかになった未利用認定者504人（A-12）と重度在宅化（A-13）の要因分析に直結する。見える化システムの再出力を最優先で依頼することを推奨する。</t>
+          <t>注1）本別表は第10期基本指針に新設される案であり、告示前である。告示後に最終確認を要する。注2）令和8年7月29日の追加受領（K系列28件・M系列13件・W系列20件）により、対応状況は「対応済み2・一部対応2・重大な課題2・未対応5」から「対応済み2・一部対応4・重大な課題1・未対応4」へ改善した。注3）見える化から取得できないことが確定した指標と、その代替は次のとおり。①五 自給率（δ2・δ3）→ 国保連の給付実績情報から算定。K系列により事業所ゼロの11種別は自給率0％と特定済み。②三 死亡場所別の死亡数（L27・L28）→ 人口動態統計の市区町村別集計又は3町の集計。③十 診療報酬側の連携指標（L20〜L26）→ 上川中部圏域の医療機関への照会。④十一 認知症（J1〜J18）→ 3町への直接照会。注4）残る「七 入所率・稼働率」「五 介護SCR」「二 人口メッシュ」は令和8年度以降の見える化システムの改修により取得可能となる予定である。第10期計画の策定時期との関係で間に合わない可能性があるため、入所率については3町の指定台帳又は施設への照会で補うことを想定しておく必要がある。</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9868,7 +9910,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証の総括　主要所見16件</t>
+          <t>検証の総括　主要所見20件</t>
         </is>
       </c>
     </row>
@@ -10423,8 +10465,136 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応の3サービスは制度創設以来13年間、域内に1事業所も存在しない</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>見える化K3m（定期巡回・随時対応型訪問介護看護）・K3n（夜間対応型訪問介護）・K3q（看護小規模多機能型居宅介護）は平成24年度から令和6年度まで全年度で事業所数0。全28サービス種別のうち11種別（39.3％）で域内事業所がゼロである。一方、要介護5の54.6％・要介護4の49.1％が在宅・居住系にいる（D38）。上川中部圏域では定期巡回が令和8年に68.0人/月、看多機が101.0人/月の見込みがあり、圏域内の他保険者では機能している。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画 第6章第4節は全サービスで定員を据置きとしており、域内に存在しないサービスがあることも、それが重度在宅化と矛盾することも記載していない。所見3（重度在宅化と供給縮小の同時進行）の供給側の内実がここにある。</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>第2章の現状分析に「域内に事業所が存在しないサービス11種別」の一覧を新設する。第6章の整備方針で、定期巡回又は看多機の確保方策（3町単独整備・広域整備・旭川市の事業所の活用のいずれか）を第1回委員会の決定事項とする。介護サービス自給率（δ2・δ3）は提供不可が確定したが、これら11種別については自給率が構造的に0％であることが特定できた（21シート）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の総合得点が全国平均を21.4％下回る</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>見える化W126：令和5年調査（令和6年度分指標）の総合得点は大雪332.0点、全国平均422.4点、北海道平均413.6点。全国平均を90.4点下回る。推進交付金164.7点（全国205.6点の80.1％）、支援交付金167.3点（全国216.7点の77.2％）。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>第2章又は第7章に交付金評価の結果を掲載し、第10期の施策の重点化の根拠とする。特に給付適正化（推進Ⅱ・全国の39.0％）と在宅医療介護連携（支援Ⅲ・同38.2％）は北海道の第9期評価指標④⑧にも対応する領域であり、道計画との整合上も対応が必要である（23シート）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>成果は全国トップ級だが、活動の記録・報告が全国の23.2％にとどまる</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>見える化W128・W130：推進交付金の指標群別得点は、取組・体制96.7点（全国122.5点の78.9％）、活動8.0点（全国34.5点の23.2％）、成果60.0点（全国48.6点の123.5％）。支援交付金も活動25.0点（全国45.0点の55.6％）、成果60.0点（同123.5％）。0点の項目は10項目あり、「評価結果を関係者間で共有し、自立支援等に資する取組を検討」「今年度の評価得点」「ケアプラン点検の実施割合」「医療情報との突合の実施割合」「入退院支援の実施状況」「人生の最終段階における支援の実施状況」を含む。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>第5章を北海道と同じ5層構成（現状と課題／関連データ／施策の方向性／主な事業〈インプット・アウトプット〉／達成目標〈アウトカム〉）とし、アウトプット指標を交付金の活動指標群と対応させる。これにより計画の実効性と交付金得点の双方が改善する。第7章に年次の進行管理（毎年度のKPI実績の算定・委員会への報告・3町との共有）を明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>性・年齢調整済みの要介護2以上認定率は全国を上回り、しかも上昇している</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>見える化W144：令和5年調査の性・年齢調整済み要介護2以上認定率は大雪9.25％、全国8.99％、北海道8.59％。W145の変化率は大雪＋1.76に対し全国▲0.37・北海道▲1.71で、大雪のみ上昇している。一方、所見7のとおり75歳以上の粗認定率は35.3％（平成30年3月末）→33.5％（令和8年3月末）、85歳以上は63.7％（令和2年3月末）→61.6％へ低下している。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>両者は矛盾しない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、合わせると「軽度は改善したが中重度は悪化している」という構造が読み取れる。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。第9期計画の代表KPI①（認定率）は粗率であり、この構造を捉えられていなかった。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>H01のデータ源をW144に確定する。国が全保険者を共通の方法で毎年算定しており、全国・北海道と直接比較でき、見える化B5-aの2系列の選択問題も解消する（修正指示書A-10）。基準値9.25％、目標は「全国平均以下」とする。現に全国を上回りかつ上昇しているため、「維持」ではなく「低下」を目標とすべきである。所見7の「年齢層をそろえると低下している」という評価は、軽度を含む全体についてのものであり、中重度については当てはまらない旨を第2章に明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率に由来し（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
         </is>
@@ -10432,8 +10602,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10446,7 +10616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10475,7 +10645,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　最優先で依頼する指標</t>
+          <t>1　最優先指標の状況（令和8年7月29日時点で確定）</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10699,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（時系列）　全体・訪問系・通所系・短期入所系・多機能系・施設居住系</t>
+          <t>介護サービス自給率（時系列）　全体・訪問系・通所系・短期入所系・多機能系・施設居住系　【提供不可】</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -10549,7 +10719,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>3町がどれだけ旭川市の事業所を利用しているかが数値になる。定期巡回が給付月額15円でほぼゼロなのに圏域では59.1人/月ある理由（旭川市の事業所を使えているのか、そもそも届いていないのか）が判別できる。自給率が低ければ町内整備は不要、高ければ域外に頼れない。第6章の整備方針が逆になる（修正指示書A-13・B-22）。</t>
+          <t>3町がどれだけ旭川市の事業所を利用しているかが数値になる。定期巡回が給付月額15円でほぼゼロなのに圏域では59.1人/月ある理由（旭川市の事業所を使えているのか、そもそも届いていないのか）が判別できる。自給率が低ければ町内整備は不要、高ければ域外に頼れない。第6章の整備方針が逆になる（修正指示書A-13・B-22）。【確定】大雪についてはデータ登録がなく出力できないことを発注者に確認済み。国保連の給付実績情報からの算定（本シート5）に切り替える。ただしK系列の受領により、域内事業所がゼロの11種別（定期巡回・夜間対応・看多機・訪問入浴・福祉用具貸与・認知症対応型通所介護・介護医療院ほか）については自給率が構造的に0％であることが特定できた（21シート2）。</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10736,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（地域比較）　同6区分</t>
+          <t>介護サービス自給率（地域比較）　同6区分　【提供不可】</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -10586,7 +10756,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>旭川市・上川中部圏域内の他保険者との自給率の比較ができる。</t>
+          <t>旭川市・上川中部圏域内の他保険者との自給率の比較ができる。【確定】δ2と同じくデータ登録がない。</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10773,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>月1回以上の通いの場の参加率／参加者数／箇所数</t>
+          <t>月1回以上の通いの場の参加率／参加者数／箇所数　【受領済み・令和2年度まで】</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -10623,7 +10793,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>第9期の代表KPI④は国の目標8％を参考にしながら、実績はニーズ調査の自己申告割合（R4 7.3％・R7 8.8％）で測っており統計が一致していなかった（修正指示書A-16）。F4を出力すれば、この不一致は見える化の再出力だけで解消できる。</t>
+          <t>第9期の代表KPI④は国の目標8％を参考にしながら、実績はニーズ調査の自己申告割合（R4 7.3％・R7 8.8％）で測っており統計が一致していなかった（修正指示書A-16）。F4を出力すれば、この不一致は見える化の再出力だけで解消できる。【確定】F4・F5を受領。令和2年度1.6％で北海道3.9％・全国5.2％を大きく下回る（20シート）。F6（月1回以上の箇所数）は収録がない。令和3年度以降の登録もない。</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10810,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>週1回以上の通いの場の参加率／参加者数／箇所数</t>
+          <t>週1回以上の通いの場の参加率／参加者数／箇所数　【受領済み・令和2年度まで】</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -10660,7 +10830,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>月1回以上と週1回以上の双方を押さえ、第10期の目標をどちらで設定するかの判断材料とする。</t>
+          <t>月1回以上と週1回以上の双方を押さえ、第10期の目標をどちらで設定するかの判断材料とする。【確定】受領済み。令和2年度は0.7％・箇所数3箇所（20シート）。</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10867,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>H13（職種別欠員率）の代替として最有力であったが使用できない。代替は、①北海道と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）を第9期の介護人材実態調査の採用者数・退職者数から算定する、②M2-a〜m（従事者数・サービス別・認定者1万対）で従事者数の推移を代替とする、の2案となる（修正指示書C-16）。</t>
+          <t>H13（職種別欠員率）の代替として最有力であったが使用できない。代替は、①北海道と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）を第9期の介護人材実態調査の採用者数・退職者数から算定する、②M2-a〜m（従事者数・サービス別・認定者1万対）で従事者数の推移を代替とする、の2案となる（修正指示書C-16）。【確定】M2-a〜m（13サービス、平成29年度〜令和6年度）を受領し、②が採用可能となった（22シート）。</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10879,12 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>K1-a〜e／K2-a〜c／K3-a〜s</t>
+          <t>K1-a〜e／K2-a〜c／K3-a〜t</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>サービス提供事業所数（全27サービス種別）</t>
+          <t>サービス提供事業所数（全28サービス種別）　【受領済み・令和6年度まで】</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -10724,88 +10894,93 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>34件</t>
+          <t>28件</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>施設サービス5種、居住系3種、在宅サービス19種の事業所数。</t>
+          <t>施設サービス5種、居住系3種、在宅サービス20種の事業所数。</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>第10期基本指針の新別表 七「介護保険施設・事業所数」に対応。定員（D25〜D30・受領済）と組み合わせると、1事業所あたり定員や事業所数の推移が把握できる。地域密着型通所介護の給付月額が27.0％低下した要因（休廃止の有無）の確認に直結する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+          <t>第10期基本指針の新別表 七「介護保険施設・事業所数」に対応。定員（D25〜D30・受領済）と組み合わせると、1事業所あたり定員や事業所数の推移が把握できる。地域密着型通所介護の給付月額が27.0％低下した要因（休廃止の有無）の確認に直結する。【確定】全28種別を受領（21シート）。地域密着型通所介護は事業所数4で不変であり、給付減は休廃止ではなく稼働率の低下による。また11種別で域内事業所がゼロであること、定期巡回・夜間対応・看多機は制度創設以来13年間ゼロであることを確定した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>W126〜W145</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価得点　【受領済み・令和5年調査】</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>20件</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>総合得点、目標別（推進Ⅰ〜Ⅲ・支援Ⅰ〜Ⅲ・共通Ⅳ）、指標群別（取組体制・活動・成果）、及び目標Ⅰ〜Ⅳの内訳。国が全保険者を共通様式で採点した結果。</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>第10期基本指針の新別表 九「インセンティブ交付金における評価」に対応。【確定】総合得点332.0点で全国422.4点の78.6％（23シート）。活動指標群が全国の23.2％である一方、成果指標群は123.5％という構造を特定した。またW144（性・年齢調整済み要介護2以上認定率）はH01のデータ源として最適である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　新別表11事項への対応のために依頼する指標</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>別表の事項</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>指標ID</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>指標名</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>定義・内容</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>三 人口動態</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>L27-a／b／c</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>在宅死亡者数（介護老人保健施設／老人ホーム／自宅）　【提供不可】</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>3件</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>別表三は「死亡場所別の死亡数等について過年度の推移等を確認すること」としている。見える化のL27系列がこれに対応するが、大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>代替として、①人口動態統計の市区町村別集計（死亡数・死亡場所別）を北海道又は上川保健所経由で入手する、②3町の死亡診断書・死体検案書の集計を用いる、③O11（看取り介護加算算定者数）・O12（ターミナルケア加算）・O13（ターミナルケアマネジメント加算）で介護側の看取りの実施状況を代替する、の3案が考えられる。③は介護報酬側のため出力できる見込み。</t>
         </is>
       </c>
     </row>
@@ -10817,91 +10992,91 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>L28-a／b</t>
+          <t>L27-a／b／c</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>看取り数（死亡診断書のみの場合も含む）　【提供不可】</t>
+          <t>在宅死亡者数（介護老人保健施設／老人ホーム／自宅）　【提供不可】</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>算定回数とレセプト件数の2系列。診療報酬側のためL系列に属する。</t>
+          <t>別表三は「死亡場所別の死亡数等について過年度の推移等を確認すること」としている。見える化のL27系列がこれに対応するが、大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>代替として、①人口動態統計の市区町村別集計（死亡数・死亡場所別）を北海道又は上川保健所経由で入手する、②3町の死亡診断書・死体検案書の集計を用いる、③O11（看取り介護加算算定者数）・O12（ターミナルケア加算）・O13（ターミナルケアマネジメント加算）で介護側の看取りの実施状況を代替する、の3案が考えられる。③は介護報酬側のため出力できる見込み。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>七 施設・事業所</t>
+          <t>三 人口動態</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>M2-a〜m</t>
+          <t>L28-a／b</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>従事者数（サービス別）［認定者1万対］</t>
+          <t>看取り数（死亡診断書のみの場合も含む）　【提供不可】</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>13件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>介護老人福祉施設、老健、療養型、医療院、訪問介護、通所介護、通所リハ3種、訪問看護、地域密着型介護老人福祉施設、居宅介護支援、地域密着型通所介護の13サービス。</t>
+          <t>算定回数とレセプト件数の2系列。診療報酬側のためL系列に属する。</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>別表七の「従事者数」に対応。認定者1万対で標準化されているため全国・北海道と比較できる。H13（職種別欠員率）の代替の一部となる。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>九 地域支援事業</t>
+          <t>七 施設・事業所</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>F15〜F25</t>
+          <t>M2-a〜m</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>地域包括支援センターの設置数・人員体制（3職種別）・地域ケア会議開催回数</t>
+          <t>従事者数（サービス別）［認定者1万対］</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>11件</t>
+          <t>13件</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>設置数、ブランチ・サブセンターを含む設置数、3職種の人員体制（保健師・社会福祉士・主任介護支援専門員別）、地域ケア会議開催回数。いずれも65歳以上人口1万対の標準化値がある。</t>
+          <t>介護老人福祉施設、老健、療養型、医療院、訪問介護、通所介護、通所リハ3種、訪問看護、地域密着型介護老人福祉施設、居宅介護支援、地域密着型通所介護の13サービス。</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>別表九の「地域包括支援センターにおける相談体制の状況」に対応。3町の体制差（東川町は重層的支援推進室に内包）を定量的に示せる。</t>
+          <t>別表七の「従事者数」に対応。認定者1万対で標準化されているため全国・北海道と比較できる。H13（職種別欠員率）の代替の一部となる。</t>
         </is>
       </c>
     </row>
@@ -10913,27 +11088,27 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>F28〜F40</t>
+          <t>F15〜F25</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>訪問型サービスA〜D・通所型サービスA〜C・見守り・配食・介護予防ケアマネジメントの実施延べ件数</t>
+          <t>地域包括支援センターの設置数・人員体制（3職種別）・地域ケア会議開催回数</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>13件</t>
+          <t>11件</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>いずれも65歳以上人口1万対。</t>
+          <t>設置数、ブランチ・サブセンターを含む設置数、3職種の人員体制（保健師・社会福祉士・主任介護支援専門員別）、地域ケア会議開催回数。いずれも65歳以上人口1万対の標準化値がある。</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>北海道のKPI「多様な主体による生活支援、通いの場を実施する市町村（訪問型サービスA・B・D、通所型サービスA・Bのいずれかに取り組む市町村）数」に対応。大雪の総合事業の類型別実施状況が分かる。</t>
+          <t>別表九の「地域包括支援センターにおける相談体制の状況」に対応。3町の体制差（東川町は重層的支援推進室に内包）を定量的に示せる。</t>
         </is>
       </c>
     </row>
@@ -10945,59 +11120,59 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>W系列</t>
+          <t>F28〜F40</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金・介護保険保険者努力支援交付金に係る評価指標</t>
+          <t>訪問型サービスA〜D・通所型サービスA〜C・見守り・配食・介護予防ケアマネジメントの実施延べ件数</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>139件</t>
+          <t>13件</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>市町村評価指標（令和4・5年度66件、令和6年度12件）、都道府県評価指標43件、アウトプット指標10件、アウトカム指標8件。</t>
+          <t>いずれも65歳以上人口1万対。</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>別表九の「インセンティブ交付金における評価」に対応。交付金の評価指標は保険者の取組状況を国の共通様式で点数化したものであり、第10期のKPIの補完指標としてそのまま使える。</t>
+          <t>北海道のKPI「多様な主体による生活支援、通いの場を実施する市町村（訪問型サービスA・B・D、通所型サービスA・Bのいずれかに取り組む市町村）数」に対応。大雪の総合事業の類型別実施状況が分かる。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>十 医療介護連携</t>
+          <t>九 地域支援事業</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>O1〜O13</t>
+          <t>W系列</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>医療介護連携に関する加算等の算定状況（介護報酬側）　【出力可・令和5年度まで】</t>
+          <t>保険者機能強化推進交付金・介護保険保険者努力支援交付金に係る評価指標</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>13件</t>
+          <t>139件</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>退院・退所時連携加算（O5）、緊急時等居宅カンファレンス加算（O4）、緊急時訪問看護加算（O2）・緊急時訪問介護加算（O3）、看護体制強化加算（O1）、特定事業所加算（O6）、医療連携強化加算（O7）・医療連携体制加算（O8）、看護・介護職員連携強化加算（O9）、配置医師緊急時対応加算（O10）、看取り介護加算（O11）、ターミナルケア加算（O12）、ターミナルケアマネジメント加算（O13）。いずれも認定者1万対。</t>
+          <t>市町村評価指標（令和4・5年度66件、令和6年度12件）、都道府県評価指標43件、アウトプット指標10件、アウトカム指標8件。</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>別表十に対応。O4・O5は受領済み（20シート参照）。H09（退院時支援調整実施率）を3町の業務記録で測る前に、O5で代替できる可能性がある（修正指示書B-19）。ただし出力は令和5年度までで、第10期の基準値としては令和5年度が最新となる。</t>
+          <t>別表九の「インセンティブ交付金における評価」に対応。交付金の評価指標は保険者の取組状況を国の共通様式で点数化したものであり、第10期のKPIの補完指標としてそのまま使える。</t>
         </is>
       </c>
     </row>
@@ -11009,27 +11184,27 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>L20〜L26</t>
+          <t>O1〜O13</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>医療介護連携に関する加算等の算定状況（診療報酬側）　【提供不可】</t>
+          <t>医療介護連携に関する加算等の算定状況（介護報酬側）　【出力可・令和5年度まで】</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>13件</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>介護支援連携指導（L20）、退院時共同指導（L21）、在宅ターミナルケア（L24）、退院退所加算（L25）、入院時情報連携加算（L26）ほか。</t>
+          <t>退院・退所時連携加算（O5）、緊急時等居宅カンファレンス加算（O4）、緊急時訪問看護加算（O2）・緊急時訪問介護加算（O3）、看護体制強化加算（O1）、特定事業所加算（O6）、医療連携強化加算（O7）・医療連携体制加算（O8）、看護・介護職員連携強化加算（O9）、配置医師緊急時対応加算（O10）、看取り介護加算（O11）、ターミナルケア加算（O12）、ターミナルケアマネジメント加算（O13）。いずれも認定者1万対。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。医療側からの連携の実施状況は、上川中部圏域の医療機関への照会又は北海道の医療計画・地域医療構想の資料で補う必要がある。</t>
+          <t>別表十に対応。O4・O5は受領済み（20シート参照）。H09（退院時支援調整実施率）を3町の業務記録で測る前に、O5で代替できる可能性がある（修正指示書B-19）。ただし出力は令和5年度までで、第10期の基準値としては令和5年度が最新となる。</t>
         </is>
       </c>
     </row>
@@ -11041,44 +11216,44 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>δ1-a／b／c</t>
+          <t>L20〜L26</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>レーダーチャート（地域の概況（需要）／サービス提供体制（供給）／医療介護連携）</t>
+          <t>医療介護連携に関する加算等の算定状況（診療報酬側）　【提供不可】</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>地域分析のレーダーチャート。</t>
+          <t>介護支援連携指導（L20）、退院時共同指導（L21）、在宅ターミナルケア（L24）、退院退所加算（L25）、入院時情報連携加算（L26）ほか。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>第10期基本指針案が別表十の把握方法に「見える化システム（新）レーダーチャート」を挙げており、既存のδ1-cがこれに相当すると考えられる。3つの視点を1枚で示せるため委員会資料に適する。</t>
+          <t>大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。医療側からの連携の実施状況は、上川中部圏域の医療機関への照会又は北海道の医療計画・地域医療構想の資料で補う必要がある。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>十一 認知症</t>
+          <t>十 医療介護連携</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>J16／J17／J18</t>
+          <t>δ1-a／b／c</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援チームの訪問実績／認知症地域支援推進員の配置人数／認知症カフェの設置主体別箇所数</t>
+          <t>レーダーチャート（地域の概況（需要）／サービス提供体制（供給）／医療介護連携）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -11088,12 +11263,12 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>いずれも実施状況の実数。</t>
+          <t>地域分析のレーダーチャート。</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>別表十一の「ピアサポート活動や就労等の社会参加の機会、場の数・利用者数」の一部に対応。3町の認知症施策の実施状況を定量的に比較できる。</t>
+          <t>第10期基本指針案が別表十の把握方法に「見える化システム（新）レーダーチャート」を挙げており、既存のδ1-cがこれに相当すると考えられる。3つの視点を1枚で示せるため委員会資料に適する。</t>
         </is>
       </c>
     </row>
@@ -11105,401 +11280,405 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>J16／J17／J18</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>認知症初期集中支援チームの訪問実績／認知症地域支援推進員の配置人数／認知症カフェの設置主体別箇所数</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>いずれも実施状況の実数。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>別表十一の「ピアサポート活動や就労等の社会参加の機会、場の数・利用者数」の一部に対応。3町の認知症施策の実施状況を定量的に比較できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>十一 認知症</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>J1〜J15</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>認知症関連研修の修了者数（サポート医、かかりつけ医、病院勤務者、歯科医師、薬剤師、看護職員、介護実践者等）</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>15件</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>研修種別ごとの修了者数。</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>北海道のKPI「専門医療機関との連携により早期診断・早期対応につなげる体制を構築している市町村数」の裏付けとなる。第5章の認知症施策のアウトプット指標に使える。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>3　発注者に確認した提供可否（令和8年7月29日時点）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>系列</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>提供可否</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>収録年度</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>サービス提供事業所数（K1-a〜e／K2-a〜c／K3-a〜t）</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>受領済み</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜令和6年度</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>全28サービス種別を受領。21シートで分析。受領済みの見える化データの中で最も新しい。28種別中11種別（39.3％）で域内の事業所数がゼロであることを確定した。</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価指標（W126〜W145）</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>受領済み</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>令和5年調査（令和6年度分指標）</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>総合得点・目標別・指標群別と目標Ⅰ〜Ⅳの内訳20件を受領。23シートで分析。指標リスト上は139件あり、個別の評価項目66件の全件は未受領。</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>従事者数（M2-a〜m）</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>受領済み</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度〜令和6年度（一部H29のみ）</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>13サービスを受領。22シートで分析。令和2年度は調査中止のため全国的に欠測。訪問介護・通所介護・居宅介護支援は平成29年度のみの収録。</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>通いの場（F1〜F9）</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>受領済み</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>平成25年度〜令和2年度</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>F1・F2・F3（週1回以上の参加率・参加者数・箇所数）、F4・F5（月1回以上の参加率・参加者数）、F7・F8・F9（週1回以上の箇所数の運営主体別・活動場所別・活動内容別）を受領。20シートで分析。令和3年度以降の収録の有無は要確認。</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>F1・F2・F3（週1回以上の参加率・参加者数・箇所数）、F4・F5（月1回以上の参加率・参加者数）、F7・F8・F9（週1回以上の箇所数の運営主体別・活動場所別・活動内容別）を受領。20シートで分析。令和3年度以降は見える化に登録がないことを確認済み（令和8年7月29日）。第10期の基準値としては令和2年度が最新となる。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>医療介護連携に関する加算（介護報酬側）</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>出力可</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>令和5年度まで</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>O4（緊急時等居宅カンファレンス加算）・O5（退院・退所時連携加算）を受領。残るO1・O2・O3・O6〜O13も出力できる見込み。第10期の基準値は令和5年度が最新となる。</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>δ</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>介護サービス自給率（δ2・δ3）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>提供不可</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>大雪についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。第10期基本指針の新別表 五「自市町村内の事業所によるサービス提供割合」に直接対応する指標であるため、代替の確保が必要（本シート5）。ただしK系列により、域内事業所がゼロの11種別については自給率0％と特定できた（21シート）。</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>認知症施策（J1〜J18）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>提供不可</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>大雪についてはデータ登録がない。別表十一（認知症）への対応は3町への直接照会に切り替える。交付金評価の支援Ⅱ（認知症総合支援）は全国の66.6％、認知症地域支援推進員の業務の状況は全国の33.9％である（23シート）。</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>介護人材の必要数（H1・H2）</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>提供不可</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>指標リストには掲載されているが大雪についてはデータ登録がない。H13（職種別欠員率）の代替として最有力であったが使用できない。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>指標リストには掲載されているが大雪についてはデータ登録がない。H13（職種別欠員率）の代替として最有力であったが使用できない。M系列の受領により、職種別従事者数の推移での代替が可能となった（22シート4）。</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>医療機関・看取り・診療報酬側の連携指標（L1〜L28）</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>提供不可</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>大雪についてはデータ登録がない。別表三（死亡場所別の死亡数）と別表十の診療報酬側の指標が取得できない。</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>δ</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>介護サービス自給率（δ2・δ3）</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>出力可否の確認を依頼中。</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>サービス提供事業所数（K1〜K3）</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>同上。</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>従事者数（M2-a〜m）</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>H1・H2が提供不可となったため、H13の代替としての重要度が上がっている。</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>認知症施策（J1〜J18）</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>同上。</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金等の評価指標</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>同上。</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>注）提供不可となったH系列・L系列に依存していた代替案は組み替えを要する。H13（職種別欠員率）はH1・H2が使えないため、北海道と同じ「採用率と離職率の差」（第9期の介護人材実態調査の採用者数・退職者数から算定）又はM2系列（従事者数）での代替となる。別表三（死亡場所別の死亡数）はL27が使えないため、人口動態統計の市区町村別集計、3町の死亡診断書の集計、又はO11〜O13（看取り介護加算・ターミナルケア加算）での代替となる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="70" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>注1）令和8年7月29日に発注者から提供可否の確定を受け、K・W・M系列を受領した。これにより見える化の受領件数は182件から約240件（26.5％）となった。注2）提供不可となったδ・J・H・L系列に依存していた代替案は次のとおり組み替える。①自給率（δ2・δ3）→ 国保連の給付実績情報からの算定（本シート5）とK系列による事業所ゼロ種別の特定。②認知症（J系列）→ 3町への直接照会（認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数、認知症サポーター数）。③H13（職種別欠員率）→ M2系列による職種別従事者数（認定者1万対）の推移。第9期の介護人材実態調査を併用して北海道と同じ「採用率と離職率の差」も算定する。④別表三（死亡場所別の死亡数）→ 人口動態統計の市区町村別集計、3町の死亡診断書の集計、又はO11〜O13（看取り介護加算・ターミナルケア加算）。注3）W144（性・年齢調整済み要介護2以上認定率）の受領により、H01のデータ源が確定した（23シート7）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>4　指標リストに存在しない指標（令和8年度以降の改修待ち）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>別表の事項</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>指針案の記載</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>現状</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>代替</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43" ht="76" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>入所率・稼働率</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>七 介護保険施設・事業所の状況</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>把握方法に「見える化システム（新）入所率、職員数推移」と記載（下線＝令和8年度以降に新たに把握が可能となる指標）</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>指標リストに該当なし。改修待ち。</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>N8-a／N8-b（通所リハビリテーション定員あたり利用延人員数）が稼働率に近い。入所率は定員（D25〜D27・受領済）と受給者数（D1・受領済）から概算できるが、受給者は域外施設の利用者を含むため厳密な入所率にはならない。事業所別の入所率は自治体の指定台帳又は施設への照会が必要。</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44" ht="76" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>介護SCR（性・年齢調整済みレセプト出現比）</t>
+          <t>入所率・稼働率</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>五 介護サービス等の利用状況</t>
+          <t>七 介護保険施設・事業所の状況</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>「介護サービスの提供状況の地域差を示す指標（介護SCR）」を新たに提示</t>
+          <t>把握方法に「見える化システム（新）入所率、職員数推移」と記載（下線＝令和8年度以降に新たに把握が可能となる指標）</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -11509,7 +11688,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>D49（地域差指数）が受領済みで、調整済み給付月額1.08・調整済み認定率1.02・受給率1.08・受給者単価1.06の4指標が得られている。サービス種類別の調整済み値は改修後に取得する。</t>
+          <t>N8-a／N8-b（通所リハビリテーション定員あたり利用延人員数）が稼働率に近い。入所率は定員（D25〜D27・受領済）と受給者数（D1・受領済）から概算できるが、受給者は域外施設の利用者を含むため厳密な入所率にはならない。事業所別の入所率は自治体の指定台帳又は施設への照会が必要。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -11517,27 +11696,27 @@
     <row r="45" ht="76" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>類似保険者比較</t>
+          <t>介護SCR（性・年齢調整済みレセプト出現比）</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>―（業務仕様書４（４）が要求）</t>
+          <t>五 介護サービス等の利用状況</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>指針案の別表には記載なし。仕様書が「類似保険者との比較分析」を明示。</t>
+          <t>「介護サービスの提供状況の地域差を示す指標（介護SCR）」を新たに提示</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>指標リストに「類似」の語なし。δ3系列の「地域比較」で比較対象を選択する機能と考えられるが、選定条件は受領資料から確認できない。</t>
+          <t>指標リストに該当なし。改修待ち。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>出力時に比較対象の選定条件（人口規模、高齢化率、都市規模等）を併せて記録していただく。北海道計画 第7章第12節の上川中部圏域の分布図は圏域内比較であり、旭川市（325,162人）を含むため人口規模が近い保険者との比較にはならない。</t>
+          <t>D49（地域差指数）が受領済みで、調整済み給付月額1.08・調整済み認定率1.02・受給率1.08・受給者単価1.06の4指標が得られている。サービス種類別の調整済み値は改修後に取得する。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -11545,103 +11724,103 @@
     <row r="46" ht="76" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
+          <t>類似保険者比較</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>―（業務仕様書４（４）が要求）</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>指針案の別表には記載なし。仕様書が「類似保険者との比較分析」を明示。</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>指標リストに「類似」の語なし。δ3系列の「地域比較」で比較対象を選択する機能と考えられるが、選定条件は受領資料から確認できない。</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>出力時に比較対象の選定条件（人口規模、高齢化率、都市規模等）を併せて記録していただく。北海道計画 第7章第12節の上川中部圏域の分布図は圏域内比較であり、旭川市（325,162人）を含むため人口規模が近い保険者との比較にはならない。</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="76" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
           <t>人口メッシュ</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>二 人口構造</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>把握方法に「見える化システム（新）人口メッシュ」と記載</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>指標リストに該当なし。改修待ち。</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の特定（別表一）に有用。改修後に取得する。当面は美瑛町の4圏域（旭・北西、美馬牛、朗根内、市街地・周辺）の区分で代替する。</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>5　介護サービス自給率を見える化以外で把握する場合の代替</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>自給率の算定可否</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50" ht="68" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>介護保険事業状況報告（月報・年報）</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>算定できない</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>様式が保険者単位の集計であり、サービスを提供した事業所の所在地の情報を持たない。大雪の被保険者が旭川市の事業所を利用した給付も、大雪の給付として計上される。したがって自給率の分子（自市町村内の事業所による給付月額）が取り出せない。</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>受給者数・給付費の総額（分母に相当）は取得できる。</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="68" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>介護給付費等実態統計（旧・介護給付費実態調査）</t>
+          <t>介護保険事業状況報告（月報・年報）</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -11651,12 +11830,12 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>保険者所在地別と事業所所在地別の集計はあるが、公表は都道府県単位が基本であり、市町村レベルで両者を突合した表は公表されていない。</t>
+          <t>様式が保険者単位の集計であり、サービスを提供した事業所の所在地の情報を持たない。大雪の被保険者が旭川市の事業所を利用した給付も、大雪の給付として計上される。したがって自給率の分子（自市町村内の事業所による給付月額）が取り出せない。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>受給者数・給付費の総額（分母に相当）は取得できる。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -11664,27 +11843,27 @@
     <row r="52" ht="68" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>国保連合会から保険者に提供される給付実績情報</t>
+          <t>介護給付費等実態統計（旧・介護給付費実態調査）</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>算定できる（推奨）</t>
+          <t>算定できない</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>介護給付費明細書（レセプト）の内容が事業所番号付きで提供される。事業所番号と指定事業所台帳（所在地）を突合すれば、自市町村内か域外かを判定できる。見える化のδ2と同じデータソースであるため、値も一致するはず。</t>
+          <t>保険者所在地別と事業所所在地別の集計はあるが、公表は都道府県単位が基本であり、市町村レベルで両者を突合した表は公表されていない。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>毎月提供されているため時系列も作成できる。見える化の定義に合わせるには「毎年9月サービス提供分」で集計する。</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -11692,27 +11871,27 @@
     <row r="53" ht="68" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>保険者の介護保険基幹システムの給付実績照会</t>
+          <t>国保連合会から保険者に提供される給付実績情報</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>算定できる</t>
+          <t>算定できる（推奨）</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>多くのシステムで事業所別の給付費・受給者数を集計できる。</t>
+          <t>介護給付費明細書（レセプト）の内容が事業所番号付きで提供される。事業所番号と指定事業所台帳（所在地）を突合すれば、自市町村内か域外かを判定できる。見える化のδ2と同じデータソースであるため、値も一致するはず。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>システムの仕様により出力可否が異なる。</t>
+          <t>毎月提供されているため時系列も作成できる。見える化の定義に合わせるには「毎年9月サービス提供分」で集計する。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -11720,33 +11899,61 @@
     <row r="54" ht="68" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>保険者の介護保険基幹システムの給付実績照会</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>算定できる</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>多くのシステムで事業所別の給付費・受給者数を集計できる。</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>システムの仕様により出力可否が異なる。</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="68" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>地域密着型サービスの指定台帳</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>地域密着型サービスは保険者が指定するため、原則として自市町村の被保険者のみが利用する。したがって地域密着型の自給率はほぼ100％と見なせる。</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>市町村間の同意による他保険者被保険者の利用がある場合は例外となる。</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="70" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="70" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>注1）本シートは受領した「指標リスト（目的別）」（見える化システムの指標一覧・994行）に基づく。指標IDが付されているものは906件で、うち受領済みはA系列13件・B系列27件・C系列4件・D系列199件・P系列ほかを含む182件（20.1％）である。注2）1の最優先6項目（計54件）は、いずれも本検証で明らかになった論点に直接対応する。特にF4は修正指示書A-16（通いの場の統計の不一致）を、H1・H2は同C-16（H13・H14の設問がない）を、δ2・δ3は同A-13・B-22（重度在宅化と24時間対応サービスの空白）を解決する。注3）2の依頼により、新別表11事項のうち三・七・九・十・十一の5事項が対応可能となる。残る一（地勢と交通）・八（高齢者向け住まい）は自治体からの資料提供、五の一部（介護SCR）・七の一部（入所率・稼働率）・二の一部（人口メッシュ）は改修待ちとなる。注4）依頼にあたっては、①出力年度（可能な限り時系列）、②比較対象（全国・北海道・類似保険者・圏域内保険者）、③類似保険者を選ぶ場合はその選定条件、の3点を併せてご指定いただきたい。</t>
         </is>
@@ -11754,10 +11961,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A56:G56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13368,6 +13575,6610 @@
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A64:J64"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>サービス種別ごとの事業所数と、域内に存在しないサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見える化K1-a〜e／K2-a〜c／K3-a〜t（全28サービス種別、平成24年度〜令和6年度）を受領した。第10期基本指針の新別表 七「介護保険施設・事業所数」に対応する。厚生労働省「介護保険総合データベース」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　域内の事業所数の推移（実数・箇所）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>H24</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>H24→R6</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>【施設】介護老人福祉施設（K1a）</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>定員はD25のとおり234人（H29）→160人（R2以降）と31.6％減少しており、事業所数は変わらないまま定員のみが縮小した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>【施設】地域密着型介護老人福祉施設（K1b）</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>＋2</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度2箇所、平成27年度3箇所と段階的に整備。平成29年度の4箇所は一時的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>【施設】介護老人保健施設（K1c）</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>13年間一貫して3施設。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>【施設】介護療養型医療施設（K1d）</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。全国も令和6年度に0.0となり制度上廃止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>【施設】介護医療院（K1e）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>制度創設（平成30年度）以来ゼロ。北海道1.0／全国0.8（人口10万対、令和6年度）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>【居住系】特定施設入居者生活介護（K2a）</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>13年間一貫して3事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>【居住系】地域密着型特定施設（K2b）</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>【居住系】認知症対応型共同生活介護（K2c）</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>▲1</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>令和4年度に1事業所減。D26の定員117人（R3）→99人（R4以降）、D13の給付月額▲10.5％と整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>【訪問】訪問介護（K3a）</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>＋5</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度に3事業所増（＋30％）。D13の給付月額＋52.8％、利用回数55.4回（全国29.7の1.87倍）と整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>【訪問】訪問入浴介護（K3b）</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。北海道1.1／全国1.3（人口10万対）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>【訪問】訪問看護（K3c）</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>＋5</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度2→令和6年度7で3.5倍。D13の給付月額＋69.2％と整合する。本計画期間で最も伸びた供給基盤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>【訪問】訪問リハビリテーション（K3d）</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>＋2</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>令和3年度に3事業所へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>【訪問】居宅療養管理指導（K3e）</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>＋10</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度に初めて1事業所。令和3年度以降に急増（4→10）。医科・歯科・薬局の在宅対応の広がりを示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>【通所】通所介護（K3f）</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>▲2</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度に5→2。地域密着型通所介護（K3g）への移行と休廃止の双方を含むとみられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>【通所】地域密着型通所介護（K3g）</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>＋4</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>平成28年度の制度創設時から4事業所で不変。D13の給付月額は▲27.0％で、事業所数は減っていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>【通所】通所リハビリテーション（K3h）</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>13年間一貫して3事業所。D13の給付月額＋38.6％は既存事業所の稼働増による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>【通所】認知症対応型通所介護（K3o）</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>▲2</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度まで2事業所。平成27年度以降ゼロで、消滅した唯一のサービス。北海道2.8／全国2.3（人口10万対）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>【短期】短期入所生活介護（K3i）</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>13年間一貫して5事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>【短期】短期入所療養介護（老健）（K3j）</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>老健3施設に併設。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>【短期】短期入所療養介護（病院等）（K3k）</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。全国も0.1と少ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>【短期】短期入所療養介護（介護医療院）（K3t）</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院がないため当然ゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>【その他】福祉用具貸与（K3l）</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。D13の給付月額は＋36.4％と伸びているが、供給はすべて域外の事業所による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>【24時間】定期巡回・随時対応型訪問介護看護（K3m）</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度の制度創設以来ゼロ。北海道2.6／全国1.2（人口10万対）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>【24時間】夜間対応型訪問介護（K3n）</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>【24時間】看護小規模多機能型居宅介護（K3q）</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>13年間ゼロ。北海道1.6／全国0.9（人口10万対）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>【多機能】小規模多機能型居宅介護（K3p）</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>＋1</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度に5事業所。人口10万対18.0は全国4.5の4.00倍で、全サービス中最も全国比が高い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>【支援】介護予防支援（K3r）</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター3箇所に対応。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>【支援】居宅介護支援（K3s）</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>▲1</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>平成27・28年度の12をピークに令和4年度以降10。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>注）「―」は当該年度に制度が存在しないか収録がないことを示す。平成29年度の介護老人福祉施設4・地域密着型介護老人福祉施設4は前後の年度と整合しないため、集計時点の差によるものとみられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2　域内に事業所が存在しないサービス（令和6年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>空白の期間</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>重度者の在宅化を支える中核サービス。要介護5の54.6％が在宅・居住系にいる（D38）にもかかわらず、給付月額は15円で実質ゼロ。上川中部圏域では令和8年に68.0人/月の見込みがあり、圏域内の他保険者では機能している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>給付月額0円。全国的にも少ないサービスだが、定期巡回と併せて夜間の空白を意味する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>医療ニーズの高い在宅者を支えるサービス。上川中部圏域では令和4年1.0人/月→令和8年101.0人/月と急増しており、大雪だけが取り残されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>重度在宅者の清潔保持の手段。域外事業者に依存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>給付月額は平成30年度から36.4％増加しており需要はあるが、供給はすべて域外の事業所による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>平成27年度〜（10年）</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>平成26年度まで2事業所あったが消滅。認知症GHも令和4年度に1事業所減っており、認知症の通所・居住の受け皿は減少方向にある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度〜（7年）</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>介護療養型医療施設もゼロのため、医療必要度の高い入所の受け皿が域内にない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>介護療養型医療施設</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>全国も令和6年度に0.0となったため、現時点では差はない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>全国的にも少ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（病院等）</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度〜（13年）</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>全国的にも少ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（介護医療院）</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度〜（7年）</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院がないため。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>注）単位は人口10万対。全28サービス種別のうち11種別（39.3％）で域内の事業所数がゼロである。うち定期巡回・夜間対応・看多機の3種別は、重度者の在宅生活を24時間支える機能を担うもので、第9期計画が掲げる「住み慣れた地域での生活の継続」の前提を欠く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>3　人口10万対の事業所数（令和6年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>大雪／全国</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>全サービス中最も全国比が高い。5事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>老健3施設に併設。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>3施設。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr"/>
+      <c r="I56" s="6" t="inlineStr"/>
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>3事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>3事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>5事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター3箇所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>7事業所。平成24年度は全国比0.29であり、13年で逆転した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>3事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>3施設。定員は31.6％減少している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>13事業所。令和6年度に3増。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>5事業所。北海道は全国の1.7倍で、道内では相対的に低い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護支援</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>10事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>4事業所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="E67" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>10事業所。令和3年度以降に急増したが、なお全国を下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E68" s="26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr"/>
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>2事業所。地域密着型と合わせても21.6で全国35.8の0.60。通所の供給が薄い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>注）大雪の人口は約2.78万人であり、1事業所が人口10万対3.6に相当する。人口が小さいほど1事業所あたりの寄与が大きくなるため、人口10万対の比較は大雪の値が高く出やすい。事業所数の絶対水準ではなく、①存在するかどうか、②実数の推移、の2点で評価すべきである。通所介護（0.35）・居宅療養管理指導（0.75）は、その補正を加えてもなお低い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>4　定員との突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>事業所数（K）</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>定員（D25・D26）</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>1事業所あたり定員</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73" ht="62" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>H29 4→R6 3（▲1）</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>H29 234人→R2以降160人（▲31.6％）</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>H29 58.5人→R6 53.3人</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>事業所数の減（▲25％）を上回る定員減（▲31.6％）であり、残った施設でも定員を縮小している。要支援・要介護者1人あたり定員は0.126（H30）→0.082（R7）で34.9％減（D28）。</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="62" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>R3 6→R4 5（▲1）</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>R3 117人→R4以降99人（▲15.4％）</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>R3 19.5人→R4 19.8人</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>1事業所の閉鎖がそのまま定員減となっている（1ユニット18人相当）。給付月額の▲10.5％（D13）と整合する。</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr"/>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75" ht="62" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>H28以降4で不変</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>―（定員の収録なし）</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E75" s="35" t="inlineStr">
+        <is>
+          <t>事業所数が変わらないのに給付月額が27.0％減少している（D13）。利用者数の減少か、事業所の規模縮小・稼働率低下による。第10期基本指針の新別表 七が求める「稼働率」の把握が必要となる典型例である。</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76" ht="62" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>H24 2→R6 7（3.5倍）</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>―（定員の概念なし）</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>給付月額＋69.2％（D13）、従事者数15人（H29）→37人（R6）（M2j）と、事業所数・従事者数・給付がそろって増加している唯一のサービス。第9期の供給基盤の変化として最も明確である。</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr"/>
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>5　第10期への反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>本検証で確認した事実</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>第10期での対応</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80" ht="72" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの空白の明記</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・夜間対応・看多機の3サービスは制度創設以来13年間、域内に1事業所も存在しない。一方で要介護5の54.6％、要介護4の49.1％が在宅・居住系にいる（D38）。</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>第2章の現状分析に「域内に事業所が存在しないサービス11種別」の一覧を新設する。第6章の整備方針では、定期巡回又は看多機の圏域内での確保方策（3町単独整備・広域整備・旭川市の事業所の活用のいずれか）を明示する（修正指示書A-13）。</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81" ht="72" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>自給率に代わる供給構造の把握</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス自給率（δ2・δ3）は見える化にデータ登録がなく提供できないことが確定した。ただしK系列により、11種別で域内事業所がゼロであること、すなわちこれらのサービスの自給率が構造的に0％であることが特定できた。</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>自給率そのものは国保連の給付実績情報から算定する（19シート5）が、「事業所ゼロ＝自給率0％」の11種別については、K系列で代替できる。第2章にこの整理を記載する。</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr"/>
+      <c r="I81" s="6" t="inlineStr"/>
+      <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82" ht="72" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>通所サービスの供給の薄さ</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>通所介護は人口10万対7.2で全国20.3の0.35。地域密着型と合わせても全国の0.60。受給者単価も通所介護62,688円で全国84,875円の0.74（D13系列）。</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護の利用回数が全国の1.87倍である一方、通所の供給が薄いという構造を第2章に明記する。通所の代替として訪問が使われている可能性を検討する。</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr"/>
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83" ht="72" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>認知症の受け皿の減少</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護は平成27年度に消滅（2→0）、認知症対応型共同生活介護は令和4年度に1事業所減（6→5）。認知症施策の見える化データ（J系列）は登録がなく提供できない。</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>認知症の通所・居住の受け皿が10年間で減少していることを第5章の認知症施策に明記する。別表十一への対応はJ系列が使えないため、3町への直接照会に切り替える（確認依頼書）。</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="72" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導の急増の評価</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度0→令和6年度10事業所。特に令和3年度以降に4→10と急増している。</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>医科・歯科・薬局の在宅対応が広がったことを示す。在宅医療・介護連携の数少ない前進として第5章に記載する。ただし交付金評価では在宅医療・介護連携が全国の38.2％と最低水準であり（23シート）、事業所の増加が連携の実効に結びついているかは別に確認を要する。</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr"/>
+      <c r="I84" s="6" t="inlineStr"/>
+      <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートは見える化K1-a〜e（施設サービス5種）・K2-a〜c（居住系3種）・K3-a〜t（在宅サービス20種）の計28ファイルによる。出典は厚生労働省「介護保険総合データベース」及び総務省「住民基本台帳に基づく人口、人口動態及び世帯数調査」。注2）事業所数は各年度の値であり、年度途中の開設・休廃止は反映されない場合がある。注3）K系列は令和6年度まで収録されており、受領済みの見える化データの中では最も新しい。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A86:K86"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>サービス別の従事者数と、介護人材指標（H13）の代替可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見える化M2-a〜m（13サービス、平成29年度〜令和6年度）を受領した。第10期基本指針の新別表 七「従事者数」に対応する。介護人材の必要数（H1・H2）はデータ登録がなく提供できないことが確定したため、本系列がH13（職種別欠員率）の主たる代替候補となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　サービス別の従事者数（実数・人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>H29→R6</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設（M2a）</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>▲11</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>▲9.5％</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>定員が234人（H29）→160人（R2以降）と31.6％減少したのに対し、従事者は9.5％減にとどまる。利用者あたりの手厚さは増している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち介護職員</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>▲10</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>▲12.5％</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>介護職員は12.5％減。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設（M2b）</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>158</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>165</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>162</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>＋34</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>＋37.8％</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度に大きく増加。令和5年度に113へ減少したのち令和6年度124。認定者1万対632.01は全国312.22の2.02倍で、全サービス中最も全国比が高い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち介護職員</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>81</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>＋9</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>＋18.0％</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>令和5年度の減少幅が大きい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設（M2k）</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>＋26</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>＋108.3％</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>令和3年度84人をピークに令和6年度50人へ40.5％減少している。事業所数は3で不変（K1b）のため、1事業所あたりの人員が減っている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション（老健）（M2g）</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>▲1</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>▲4.3％</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度41人をピークに令和5年度20人へ半減。事業所数は3で不変（K3h）。給付月額は＋38.6％（D13）と増えており、人員は減って給付は増えている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護（M2j）</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>＋22</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>＋146.7％</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>事業所数2→7（K3c）、給付月額＋69.2％（D13）と整合する明確な拡大。認定者1万対188.58は全国207.04の91.1％、北海道157.15の120.0％。平成29年度は全国の75.8％であり、全国水準に近づいた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護（M2m）</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>＋4</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>＋19.0％</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>事業所数は4で不変（K3g）だが給付月額は▲27.0％（D13）。従事者数は増えており、利用者の減少による稼働率低下が示唆される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護（M2e）</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度のみの収録。認定者1万対313.5は全国346.47の90.5％。事業所は令和6年度に13へ増えており（K3a）、現時点の人員は把握できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>通所介護（M2f）</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度のみ。認定者1万対69.08は全国366.17の18.9％。平成30年度の地域密着型への移行前の値である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護支援（M2l）</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>平成29年度のみ。認定者1万対170.03は全国160.7の105.8％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>介護療養型医療施設（M2c）</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>施設が存在しないためゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院（M2d）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション（医療施設）（M2h）</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>医療施設の通所リハは域内にない。北海道27.48／全国53.20（認定者1万対）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション（介護医療院）（M2i）</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が新型コロナウイルス感染症の影響で実施されなかったため、全国・北海道を含め欠測である。注2）訪問介護（M2e）・通所介護（M2f）・居宅介護支援（M2l）は平成29年度のみの収録で、平成30年度以降の値がない。これは発注者から事前に「一部H29までの実績しかない」と示されていた点に該当する。注3）「―」は収録がないことを、0は事業所が存在しないことを示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2　認定者1万対でみた全国・北海道との比較（令和6年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>大雪／全国</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>632.01</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>281.41</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>312.22</v>
+      </c>
+      <c r="E25" s="36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>全国の2.02倍。老健3施設が域内の入所機能の中心であることを示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>254.84</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>77.94</v>
+      </c>
+      <c r="E26" s="36" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>全国の3.27倍。ただし令和3年度441.41から4割減しており、方向は下向き。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション（老健）</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>全国の1.71倍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>535.17</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>485.72</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>540.03</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>全国とほぼ同水準。平成29年度は616.37で全国520.67の1.18倍であり、8年間で全国並みまで低下した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>188.58</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>157.15</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>207.04</v>
+      </c>
+      <c r="E29" s="36" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>全国の91.1％まで接近。北海道は上回る。第9期で最も改善した供給基盤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>127.42</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>139.23</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>160.27</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>全国の80.0％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>注）分母は要介護（要支援）認定者数。認定者1万対で標準化されているため全国・北海道と直接比較できる。大雪の認定者は約1,960人であり、1人が認定者1万対5.1に相当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>3　職種別の状況（介護老人福祉施設・実数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>R元</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>H29→R6</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>施設長</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>▲1</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>配置医師は嘱託によるとみられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>生活相談員</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>▲2</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>令和6年度に3人へ減少。相談支援体制の縮小を示す可能性がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>看護師</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>＋2</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>准看護師</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>▲4</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>8年間で7人→3人へ57.1％減。看護師の増加（5→7）では補いきれていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>▲10</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>▲12.5％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>管理栄養士</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>栄養士</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>機能訓練指導員</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>▲1</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>令和6年度に1人。自立支援・重度化防止の実施体制に関わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>介護支援専門員</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>その他の職員</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>＋5</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>▲11</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>▲9.5％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>注）歯科医師・歯科衛生士・障害者生活支援員・調理員は全年度で収録がない。介護老人保健施設（M2b）についても同様の職種別内訳が得られる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>4　H13（職種別欠員率）の代替としての評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>欠員の把握</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>代替できない</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>M2系列は在籍している従事者数であり、必要数（H1・H2）が提供不可となった以上、欠員（必要数－在籍数）は算定できない。欠員率そのものの代替とはならない。</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="54" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>人員の増減の把握</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>代替できる</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>サービス別・職種別の実数が平成29年度から令和6年度まで得られる（令和2年度を除く）。特に准看護師7→3、生活相談員5→3、機能訓練指導員2→1といった特定職種の減少は、欠員率よりも直接的に体制の変化を示す。</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="54" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>全国比較</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>代替できる</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>認定者1万対で標準化されているため、全国・北海道との比較ができる。介護老人福祉施設が全国比1.18（H29）→0.99（R6）へ低下していることは、相対的な人員確保力の低下を示す。</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="54" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>直近性</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>課題あり</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>収録は令和6年度までで、訪問介護・通所介護・居宅介護支援は平成29年度のみ。第10期の基準値としては使えるが、訪問系・通所系の現況は把握できない。</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="54" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>結論</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>H13は「職種別欠員率」から「職種別従事者数（認定者1万対）の推移」へ定義を改めることを推奨する。測定手段はM2系列で確保でき、第9期の介護人材実態調査を併用すれば北海道と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）も算定できる。北海道の第9期評価指標⑥と接続できるため、道計画との整合も確保される（修正指示書C-16）。</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートは見える化M2-a〜m（13ファイル）による。出典は厚生労働省「介護サービス施設・事業所調査」。注2）介護人材の必要数（H1）及び需要見込みに対する供給見込みの割合（H2）は、大雪地区広域連合についてはデータ登録がなく出力できないことを発注者に確認済み（令和8年7月29日）。注3）従事者数は各年10月1日現在の値であり、非常勤を含む実人数である。常勤換算値ではないため、勤務時間の変化は反映されない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A31:K31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金・介護保険保険者努力支援交付金の評価得点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見える化W126〜W145（令和5年調査＝令和6年度分指標）を受領した。第10期基本指針の新別表 九「インセンティブ交付金における評価」に対応する。国が全保険者に共通の様式で採点した結果であり、大雪の取組状況を全国・北海道と同一の物差しで比較できる唯一のデータである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　総合得点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>対全国</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>対北海道</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>210.4</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を40.9点下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>介護保険保険者努力支援交付金</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を49.4点下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="n">
+        <v>332</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>413.6</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>422.4</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>全国平均422.4点に対し332.0点で、90.4点（21.4％）低い。北海道平均も81.6点下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>注）交付金の交付額は得点に応じて配分されるため、この差はそのまま財源の差となる。第9期計画は交付金の評価結果に言及していない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2　指標群別の得点（本検証で最も重要な発見）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>交付金・指標群</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>対全国</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>推進　取組・体制指標群</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>計画・体制の整備に関する指標。全国の78.9％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>推進　活動指標群</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>実際の活動量を測る指標。全国の23.2％で、全4分類中で最も低い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>推進　成果指標群</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="n">
+        <v>60</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E15" s="38" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>要介護度の変化等のアウトカム。全国の123.5％で満点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>支援　取組・体制指標群</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="D16" s="27" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="E16" s="37" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>全国の66.9％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>支援　活動指標群</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>全国の55.6％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>支援　成果指標群</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="n">
+        <v>60</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>推進と共通の目標Ⅳ。満点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>【解釈】成果（アウトカム）は全国トップ級である一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。これは「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態を示す。第9期計画のロジックモデルが不完全であること（18シート）、代表KPIの検証が令和8年3月末実績の1回のみで年次の中間評価がないこと（02シート）と同じ構造である。第10期でロジックモデルのアウトプット指標を整備すれば、施策の実効性と交付金得点の双方が改善する余地が大きい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>3　目標別の得点</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>交付金・目標</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>対全国</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅰ　持続可能な地域のあるべき姿をかたちにする</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="C23" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>計画の進捗管理・評価に関する目標。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅱ　公正・公平な給付を行う体制を構築する</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C24" s="27" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E24" s="37" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化。全8目標中で最も低い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅲ　介護人材の確保その他のサービス提供基盤の整備</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="C25" s="27" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>全国平均とちょうど同点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>推進・支援Ⅳ　高齢者が可能な限り自立した日常生活を営む</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="n">
+        <v>60</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D26" s="27" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E26" s="38" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>成果指標。満点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅰ　介護予防／日常生活支援を推進する</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="C27" s="27" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="D27" s="27" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>全国の91.8％で、大雪の弱点の中では相対的に良い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅱ　認知症総合支援を推進する</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D28" s="27" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E28" s="37" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>全国の66.6％。J系列（認知症）のデータが提供不可であることと併せ、認知症施策の実態把握そのものが手薄である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅲ　在宅医療・在宅介護連携の体制を構築する</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="C29" s="27" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D29" s="27" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="E29" s="37" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>全国の38.2％。O4・O5の算定実数が年0〜1人であること（20シート）、L系列（診療報酬側）のデータがないことと整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>4　0点の項目（10項目）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>交付金・目標</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>評価項目</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>本検証での位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅰ</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>評価結果を関係者間で共有し、自立支援等に資する取組を検討</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIの検証結果が委員会・3町・関係者間で共有されていないことを示す。02シートの「年次の中間評価がない」という所見と一致する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅰ</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>今年度の評価得点</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>同上。計画の自己評価そのものが未実施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅰ</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>PFS（成果連動型民間委託契約方式）の活用</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>全国的にも取組は少ない。優先度は低い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅱ</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>ケアプラン点検の実施割合</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化の主要3事業の一つ。北海道の第9期評価指標⑧は「給付適正化主要3事業の実施率100％」であり、大雪はこの指標に反する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅱ</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>医療情報との突合の実施割合</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>同上。給付適正化主要3事業の一つ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅲ</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>介護の仕事の魅力を伝達するための取組</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標⑥（介護従事者数・採用率と離職率の差）に関連する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅲ</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>介護人材の定着・資質向上に関する取組</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅱ</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>認知症サポーターステップアップ講座の開催</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標⑤に関連する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅲ</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>入退院支援の実施状況</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>第10期のH09（退院時支援調整実施率）が対象とする領域そのものである。O5（退院・退所時連携加算）の実数が年0〜1人であること（20シート）と整合する。H09を新設する根拠が国の評価でも裏付けられた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅲ</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>人生の最終段階における支援の実施状況</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>看取りに関する取組。L27・L28（死亡場所別の死亡数・看取り数）が提供不可であることと併せ、看取りの体制・実績とも把握できていない。別表三への対応と一体で整理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>5　全国平均を上回る項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>交付金・目標</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>評価項目</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>対全国</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>本検証での位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>生活支援コーディネーター数</t>
+        </is>
+      </c>
+      <c r="C46" s="36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標②（生活支援コーディネーター配置市町村数127→142）と整合する強み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア会議における個別事例の検討</t>
+        </is>
+      </c>
+      <c r="C47" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標①（地域ケア会議の運営状況）と整合する強み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅳ</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化（要介護3〜5）</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>満点。D2/D4でみた施設受給率の低下（要介護5が1.2％→0.7％）と整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅳ</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化（要介護1・2）</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>満点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>通いの場等における心身・認知機能の把握</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>通いの場は3箇所しかないが（20シート）、その運営の質は評価されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>総合事業における多様なサービスの実施</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標②（多様な主体による生活支援85→98市町村）と整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅰ</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>後期高齢者数と給付費の伸び率の比較</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>給付費の分析そのものは行われている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター3職種の配置状況</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>全国は上回るが北海道は下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅲ</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>庁内・庁外における連携体制</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>広域連合と3町の連携体制が評価されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅰ</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>地域の介護保険事業の特徴を把握し、課題を抽出</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>課題の抽出はできているが、その先の「評価結果の共有・取組の検討」が0点である点に本質がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>6　全国平均を大きく下回る項目（0点を除く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>交付金・目標</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>評価項目</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>対全国</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>本検証での位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅲ</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>介護支援専門員に対する研修</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>高齢者のポイント事業への参加率</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅱ</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>認知症地域支援推進員の業務の状況</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F61" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策の中核となる職。J系列が提供不可であるため、3町への直接照会で実態を把握する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅲ</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携の具体的取組状況</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携推進事業の8項目の実施状況。第5章の該当節の記述の裏付けを要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅱ</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費の適正化に向けた方策</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標⑧に反する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>アウトリーチ等の取組状況</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>認定者504人が未利用（D42）という所見2と関連する。未利用者へのアウトリーチが不足している可能性を示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅱ</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>認知症サポーター数</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅲ</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>医療・介護関係者間の情報共有</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標④（情報共有ツール導入134→158市町村）に対応する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅳ</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>健康寿命延伸の状況（要介護2以上認定率）</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>目標Ⅳの5項目中、唯一低い項目。詳細は7による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>支援Ⅰ</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター事業評価の達成状況</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F68" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr"/>
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期評価指標①（地域包括支援センター運営状況調査 71.6％→全国平均値以上）に対応する。大雪は北海道の目標に対しても下回っている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>推進Ⅰ</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業計画の進捗状況（計画評価）</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F69" s="19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr"/>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の進行管理が国の評価でも低く採点されている。02シートの所見（代表KPIの検証が期末1回のみ）を国の評価が裏付けている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>7　成果指標の詳細（目標Ⅳ）と年齢調整済認定率</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>大雪</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>評価の方向</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-1　短期的な要介護度の伸び（軽度・単年度変化率）</t>
+        </is>
+      </c>
+      <c r="B73" s="36" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>全国の65.1％で良好。得点15.0（全国10.7）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-1　同（前年度の変化率との差）</t>
+        </is>
+      </c>
+      <c r="B74" s="26" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="C74" s="19" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="D74" s="19" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr"/>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>全国・北海道が低下する中で大雪のみ＋9.34と上昇。水準は良いが方向は悪化している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-2　長期的な要介護度の変化（要介護1・2）</t>
+        </is>
+      </c>
+      <c r="B75" s="36" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="C75" s="19" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="D75" s="19" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>全国の86.1％で良好。得点15.0（全国8.1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-3　短期的な要介護度の伸び（中重度・単年度変化率）</t>
+        </is>
+      </c>
+      <c r="B76" s="36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C76" s="19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="D76" s="19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr"/>
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>全国の21.1％で極めて良好。得点10.0（全国10.2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-3　同（前年度の変化率との差）</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="D77" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr"/>
+      <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-1と同じく、大雪のみ上昇方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-4　長期的な要介護度の変化（要介護3〜5）</t>
+        </is>
+      </c>
+      <c r="B78" s="36" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="C78" s="19" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="D78" s="19" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>全国の50.9％で良好。得点15.0（全国8.0）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-5　性・年齢調整済み要介護2以上認定率（当年度）</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="D79" s="19" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr"/>
+      <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>全国の102.9％、北海道の107.7％。得点5.0（全国11.7）で、目標Ⅳの中で唯一低い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-5　同（変化率）</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C80" s="19" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="D80" s="19" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>低いほど良い</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>全国▲0.37・北海道▲1.71が低下する中で、大雪のみ＋1.76と上昇している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="56" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>【重要】W144は「性・年齢調整済み要介護2以上の認定率」であり、第10期のH01（年齢調整済要介護認定率）が求めていた指標そのものである。国が全保険者について毎年算定・公表しているため、データ源として最も確実である。その値は大雪9.25％で全国8.99％を2.9％上回り、しかも全国・北海道が低下する中で大雪のみ上昇している（W145）。本検証の別の所見（75歳以上の認定率が35.3％→33.5％へ低下、85歳以上が63.7％→61.6％へ低下）と矛盾するものではない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、両者を合わせると「軽度は改善したが中重度は悪化している」という構造が読み取れる。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>8　第10期への反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85" ht="76" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>H01のデータ源をW144に確定</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>H01（年齢調整済要介護認定率）は、見える化B5-aに2系列あり【注目する地域のみ】18.4％と【他地域と比較】16.7％のどちらを採るかが未決定であった（修正指示書A-10）。W144は国が全保険者共通の方法で算定した性・年齢調整済み要介護2以上の認定率であり、全国・北海道と直接比較でき、毎年更新される。</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>H01の定義を「性・年齢調整済み要介護2以上認定率（保険者機能強化推進交付金 評価指標Ⅳ-5）」とし、基準値9.25％（令和5年調査）、目標は「全国平均以下」とする案を委員会に諮る。現に全国を上回りかつ上昇しているため、「維持」ではなく「低下」を目標とすべきである。B5-aは補完指標として資料編に残す。</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
+      <c r="I85" s="6" t="inlineStr"/>
+      <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="76" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>アウトプット指標の整備を第10期の骨格に</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>活動指標群が全国の23.2％（推進）・55.6％（支援）である一方、成果指標群は123.5％。結果は出ているが活動が記録・報告されていない。</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>第5章の全節を北海道計画と同じ5層構成（現状と課題／関連データ／施策の方向性／主な事業〈インプット・アウトプット〉／達成目標〈アウトカム〉）とし、アウトプット指標を交付金の活動指標群と対応させる（18シート）。これにより計画の実効性と交付金得点の双方が改善する。</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87" ht="76" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化の位置づけの引上げ</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅱが全国の39.0％で全8目標中最低。ケアプラン点検・医療情報との突合はいずれも0点。北海道の第9期評価指標⑧は「給付適正化主要3事業の実施率100％」である。</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>第7章（計画の推進体制）又は第5章に給付適正化の節を設け、ケアプラン点検と医療情報との突合の実施を第10期のKPI（アウトプット指標）に位置づける。北海道計画との整合上も必須である。</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="76" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携の実態の明示</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅲが全国の38.2％。入退院支援・人生の最終段階の支援はいずれも0点。O5の算定実数は年0〜1人、L系列はデータ登録なし。</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>第5章の在宅医療・介護連携の節に、現状として「入退院支援・看取りの取組が国の評価で0点である」ことを明記し、H09（退院時支援調整実施率）の新設をその対応として位置づける。第10期基本指針の別表十への対応と一体で整理する。</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+      <c r="I88" s="6" t="inlineStr"/>
+      <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89" ht="76" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>計画の進行管理の是正</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅰの「評価結果を関係者間で共有し、自立支援等に資する取組を検討」及び「今年度の評価得点」がいずれも0点。「介護保険事業計画の進捗状況」も全国の64.5％。</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>第7章に年次の進行管理の仕組み（毎年度のKPI実績の算定・委員会への報告・3町との共有）を明記する。これは第9期計画に欠けていた点であり（02シート）、国の評価でも同じ指摘が出ている。</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="76" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>強みの明文化</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>生活支援コーディネーター数（全国の2.06倍）、地域ケア会議の個別事例検討（1.88倍）、庁内・庁外の連携体制（1.27倍）、要介護度の長期的変化（1.85〜1.88倍）は全国上位。</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>第9期の成果として第1章又は第2章に明記する。特に要介護度の長期的変化が良好であることは、重度者の在宅化（D38）が結果として自立支援に寄与している可能性を示す。</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr"/>
+      <c r="J90" s="6" t="inlineStr"/>
+      <c r="K90" s="6" t="inlineStr"/>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートは見える化W126〜W145（20ファイル）による。出典は厚生労働省「保険者機能強化推進交付金・介護保険保険者努力支援交付金に係る評価指標（市町村分）」。調査実施年は令和5年（2023年）で、令和6年度分の指標として用いられる。注2）全国・北海道の値は全保険者の平均値である。注3）受領したのは総合得点・目標別・指標群別と、目標Ⅰ〜Ⅳの内訳20件である。指標リスト上のW系列は139件あり、個別の評価項目（66件）の全件は受領していない。0点の項目・全国平均を大きく下回る項目については、実際の評価調書（3町又は広域連合が国へ提出したもの）と突合して、取組が行われていないのか、取組はあるが要件を満たさないのかを確認する必要がある。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>設定なし（広域の目標値への言及2件）</t>
+          <t>6事業10項目以上（令和6〜8年度を対象）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>重大な不整合。「数値目標」の出現は広域4件に対し3町とも0件。広域がKPIを設定しても、達成手段を担う町の計画に目標がないため、PDCAが町段階で機能しない。</t>
+          <t>【令和8年7月29日訂正】各章を目視で再点検した結果、東川町は令和6〜8年度を対象とする事業の数値目標を設定していることが判明した（訪問型サービス200人／年、通所型サービス150人／年、介護予防ケアマネジメント720件／年、介護予防把握200件／年、いきいきセンター開所200日・登録80名、地域まるごと元気アップ48回・25人）。美瑛町・東神楽町は事業の数値目標を設定していない。「数値目標」の出現は広域4件に対し3町とも0件であるが、東川町は語を用いずに数値で目標を設定している。広域がKPIを設定しても、達成手段を担う町の計画に目標がないため、PDCAが町段階で機能しない。</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2の15領域の役割分担と共通指標について、3町の担当課と合意し、3町の第10期高齢者福祉計画に共通指標を掲載してもらう。</t>
+          <t>素案 資料2の15領域の役割分担と共通指標について、3町の担当課と合意し、3町の第10期高齢者福祉計画に共通指標を掲載してもらう。東川町は第9期に事業の数値目標を年度別に設定し実績と対比する仕組みを既に有しているため、同町の様式を美瑛町・東神楽町にも参考として示す。</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>3町の計画に数値目標がない。第10期の最大の課題。</t>
+          <t>語の出現数では3町とも0件だが、東川町は語を用いずに令和6〜8年度の事業の数値目標を設定している（09シート・訂正）。美瑛町・東神楽町は設定していない。</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者福祉計画に数値目標が1件も設定されていない。「数値目標」の出現は広域4件に対し3町とも0件。広域のKPI検証への参画を明記しているのは東川町のみ。</t>
+          <t>美瑛町・東神楽町の高齢者福祉計画に事業の数値目標が設定されていない（東川町は6事業10項目以上を設定。令和8年7月29日訂正）。広域のKPI検証への参画を明記しているのは東川町のみ。</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -9910,14 +9910,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証の総括　主要所見20件</t>
+          <t>検証の総括　主要所見20件（中間・記載事項の検証）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>重要度A＝第1回委員会での決定を要する／B＝第10期計画の記述に反映する／C＝データ確認のうえ判断する</t>
+          <t>重要度A＝第1回委員会での決定を要する／B＝第10期計画の記述に反映する／C＝データ確認のうえ判断する。本検証は、①代表KPIの達成度、②計画の記載事項（指標設計・施策体系・推計・保険料）の妥当性、③交付金による外部評価の分析からなる。令和6〜8年度の事業実績が未受領のため、事業が計画どおり実施されたかというプロセス評価は行っていない（レッドチームレビュー No.13）。また第9期の最終年度（令和8年度）の実績は令和9年3月末に確定するため、現時点の評価は中間評価である。他団体との比較は、入手可能な比較対象（上川管内21保険者、全国・北海道、健康とくらしの調査の同規模保険者40）によるものであり、介護保険上の類似保険者の選定条件は未決定である（同 No.14）。交付金の得点比較は人口規模を揃えていないため、小規模保険者に構造的に不利な評価項目が含まれる点に留意する（同 No.16）。判定の閾値は、比率の差が1.0ポイント未満を「同等」とし、それ以外は定性的に判断している（同 No.17）。</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>給付水準の高さは施設・居住系サービスの受給率に集約される</t>
+          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価に由来する</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。</t>
+          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（レッドチームレビュー No.7）。また介護老人福祉施設の定員が234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>未利用の要因（供給制約・申請先行・軽度者の自立）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。</t>
+          <t>未利用の要因（供給制約・申請先行・軽度者の自立・家族介護・経済的理由）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。【留意】認定者が増え受給者が減ったという事実だけでは供給制約は導けない（レッドチームレビュー No.8）。第9期に認定申請の勧奨を行った結果であれば、供給制約ではなく認定行政の変化であり、施策の方向は逆になる。要因を特定するまで供給制約と断定しない。</t>
         </is>
       </c>
     </row>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>重度在宅者の増加と供給縮小の同時進行を第2章の主要論点として明記し、第6章の整備方針に接続する。家族介護者支援（H07・H08）の優先度を上げる。</t>
+          <t>重度在宅者の増加と供給縮小の同時進行を第2章の主要論点として明記し、第6章の整備方針に接続する。家族介護者支援（H07・H08）の優先度を上げる。【留意】この「在宅化」は施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない（レッドチームレビュー No.10）。24時間対応の3サービスが区域内に存在しないことを踏まえると、家族介護への転嫁である可能性が高い。政策の成果と誤読されないよう記述する。</t>
         </is>
       </c>
     </row>
@@ -10094,22 +10094,22 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者福祉計画に数値目標が1件も設定されていない</t>
+          <t>数値目標を設定しているのは東川町のみで、美瑛町・東神楽町は設定していない【令和8年7月29日訂正】</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>空白除去後の全文検索で「数値目標」の出現回数は広域4件に対し3町とも0件。「目標値」は東川町2件のみで、いずれも広域の目標値への言及。「日常生活圏域」は広域12件に対し3町とも0件。</t>
+          <t>各章を目視で再点検した結果、東川町は第9期計画期間（令和6〜8年度）を対象とする事業の数値目標を6事業10項目以上設定している。訪問型サービス利用者数200人／年、通所型サービス利用者数150人／年、介護予防ケアマネジメント件数720件／年、介護予防把握事業の把握件数200件／年、いきいきセンター事業の開所日数200日・年度末登録者数80名、地域まるごと元気アップ事業の開催回数48回（午前・午後各）・参加者数25人（同）。美瑛町は令和6〜8年度を対象とする数値目標の表が確認できない。東神楽町の令和6〜8年度の数表は人口推計及び認定者数推計であり、目標値ではない。なお「数値目標」という用語の出現は広域4件に対し3町とも0件、「日常生活圏域」は広域12件に対し3町とも0件である。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>広域が代表KPI4項目を設定した一方、その達成主体である3町の計画には目標も進行管理の指標もない。「一般介護予防事業評価事業」で広域のKPI検証への参画を明記しているのは東川町のみ。</t>
+          <t>当初は「3町とも数値目標が1件もない」と判定していたが、これは「数値目標」「目標値」という語の全文検索によるものであり、語を用いずに数値で目標を設定している東川町の事例を見落としていた（レッドチームレビュー No.5）。広域が代表KPI4項目を設定した一方、美瑛町・東神楽町の計画には事業の目標がない。「一般介護予防事業評価事業」で広域のKPI検証への参画を明記しているのは東川町のみである。</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2「構成3町との役割分担・共通指標」の実効性が第10期の成否を左右する。3町の第10期計画に共通指標を掲載してもらう合意を、第1回委員会で取り付ける。</t>
+          <t>東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は東川町では実現可能性が高い。美瑛町・東神楽町については、東川町の様式を参考に共通指標の設定を協議する。素案 資料2「構成3町との役割分担・共通指標」の実効性が第10期の成否を左右する。</t>
         </is>
       </c>
     </row>
@@ -10163,12 +10163,12 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>見える化B4-a・B4-d・B4-eの合計認定率（各年3月末）は、全体が平成30年20.8％→令和8年21.8％で＋1.0ポイントである一方、75歳以上は35.3％→33.5％で▲1.8ポイント、85歳以上は令和2年63.7％→令和8年61.6％で▲2.1ポイント。</t>
+          <t>見える化B4-a・B4-d・B4-eの合計認定率（各年3月末）は、全体が平成30年3月末20.8％→令和8年3月末（令和7年度末）21.8％で＋1.0ポイントである一方、75歳以上は35.3％→33.5％で▲1.8ポイント、85歳以上は令和2年3月末63.7％→令和8年3月末61.6％で▲2.1ポイント。第9期の最終年度（令和8年度）の実績は令和9年3月末に確定する。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
+          <t>【留意】本所見の根拠は合計・75歳以上・85歳以上の3系列であり、65〜74歳の認定率及び5歳階級別の直接法による年齢調整は行っていない（レッドチームレビュー No.1）。また性・年齢調整済み要介護2以上認定率（W144）は全国を上回り変化率も＋1.76と悪化しており、本所見と方向が異なる。両者は指標の範囲（全要介護度の粗率か要介護2以上の調整済みか）が異なるが、整合を要介護度別の推移で実証していない。確認事項No.37の資料により再検証する。全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>第8期は必要額と基準額がほぼ均衡しており設定は良好。第9期は令和6年度に337円/月の余裕が生じ、取崩を前提とした設計に対し実績は剰余方向。令和8年度の実績を待って確定する。</t>
+          <t>第8期は必要額と基準額がほぼ均衡しており設定は良好。第9期は令和6年度に337円/月の余裕が生じ、取崩を前提とした設計に対し実績は剰余方向。令和8年度の実績を待って確定する。【留意】剰余の額（2年で約42百万円）は概算である（レッドチームレビュー No.3）。令和6年度の必要保険料月額は令和8年1月時点の実績を年度換算した値であり、決算及び基金の積立実績で確認していない。決算により確定値に置き換える。</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の総合得点が全国平均を21.4％下回る</t>
+          <t>保険者機能強化推進交付金等の総合得点が全国平均を21.4％下回る（令和5年調査＝第8期の取組を反映）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。</t>
+          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施され、評価対象は主に令和4年度の実施状況である。第9期は令和6年度からであるため、この得点は第9期ではなく第8期の取組を反映している（レッドチームレビュー No.2）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>成果は全国トップ級だが、活動の記録・報告が全国の23.2％にとどまる</t>
+          <t>令和6年度分指標では成果が全国を上回る一方、活動の記録・報告が全国の23.2％にとどまる</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
+          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、「全国トップ級」等の表現は用いない（レッドチームレビュー No.9）。また本得点は第8期の取組を反映したものである（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>両者は矛盾しない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、合わせると「軽度は改善したが中重度は悪化している」という構造が読み取れる。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。第9期計画の代表KPI①（認定率）は粗率であり、この構造を捉えられていなかった。</t>
+          <t>両者は矛盾しない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、【令和8年7月29日訂正】当初は「軽度は改善したが中重度は悪化している」と説明していたが、見える化B5a・B6a・B6bの調整済み認定率により、これは誤りであることが判明した。年齢構成を調整すると、中重度（要介護3〜5）は平成30年5.4％から令和7年4.7％へ低下が続いている一方、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じている。W144とB5aは基準人口・調整方法・時点・単位が異なるため直接比較できない（認定率の年齢調整分析 04・05シート）。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。第9期計画の代表KPI①（認定率）は粗率であり、この構造を捉えられていなかった。</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -19947,10 +19947,10 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="56" customHeight="1">
+    <row r="81" ht="70" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>【重要】W144は「性・年齢調整済み要介護2以上の認定率」であり、第10期のH01（年齢調整済要介護認定率）が求めていた指標そのものである。国が全保険者について毎年算定・公表しているため、データ源として最も確実である。その値は大雪9.25％で全国8.99％を2.9％上回り、しかも全国・北海道が低下する中で大雪のみ上昇している（W145）。本検証の別の所見（75歳以上の認定率が35.3％→33.5％へ低下、85歳以上が63.7％→61.6％へ低下）と矛盾するものではない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、両者を合わせると「軽度は改善したが中重度は悪化している」という構造が読み取れる。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。</t>
+          <t>【重要】W144は「性・年齢調整済み要介護2以上の認定率」であり、第10期のH01（年齢調整済要介護認定率）が求めていた指標そのものである。国が全保険者について毎年算定・公表しているため、データ源として最も確実である。その値は大雪9.25％で全国8.99％を2.9％上回り、しかも全国・北海道が低下する中で大雪のみ上昇している（W145）。本検証の別の所見（75歳以上の認定率が35.3％→33.5％へ低下、85歳以上が63.7％→61.6％へ低下）と矛盾するものではない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、【訂正】両者は基準人口・調整方法・時点・単位が異なるため直接比較できない。見える化B6a・B6bによれば、中重度は低下が続き軽度が直近で上昇に転じている（認定率の年齢調整分析 04・05シート）。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -6009,7 +6009,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>平成26年度4.3％から令和7年度3.7％へ0.6ポイント低下。低下分のほぼ全てが要介護5に由来する。</t>
+          <t>平成26年度4.3％から令和7年度3.7％へ0.6ポイント低下。低下分の大半は要介護5の受給率の低下による。要介護5の受給者が減った理由（死亡・施設入所・認定の変化）は特定していない。</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価に由来する</t>
+          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価がともに高いことによる</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（レッドチームレビュー No.7）。また介護老人福祉施設の定員が234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
+          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（レッドチームレビュー No.7）。また介護老人福祉施設の定員が公表値の上で234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は住民基本台帳によるコーホート変化率法を用い、東川町については本文で「下方修正した」と注記しているが、修正後もなお社人研と大きく乖離している。</t>
+          <t>第9期計画は住民基本台帳によるコーホート変化率法を用い、東川町については本文で「下方修正した」と注記しているが、修正後もなお社人研と大きく乖離している。ただし住民基本台帳と国勢調査は基準が異なるため、乖離のうち基準の差による分と社会増の見込みによる分は分離できていない。令和6年・令和7年の住民基本台帳実績を両推計に当てはめて検証する。</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の総合得点が全国平均を21.4％下回る（令和5年調査＝第8期の取組を反映）</t>
+          <t>保険者機能強化推進交付金等の総合得点が全国平均を21.4％下回る（令和5年度に実施された調査による）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施され、評価対象は主に令和4年度の実施状況である。第9期は令和6年度からであるため、この得点は第9期ではなく第8期の取組を反映している（レッドチームレビュー No.2）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
+          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施されたものであり、第9期（令和6年度〜）の取組は反映されていない（レッドチームレビュー No.2）。なお評価項目ごとの対象期間（調査時点の体制か前年度の実績か）は調査要領で確認していないため、「第8期の評価である」とは記述しない（レッドチームレビュー No.20）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、「全国トップ級」等の表現は用いない（レッドチームレビュー No.9）。また本得点は第8期の取組を反映したものである（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
+          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、「全国トップ級」等の表現は用いない（レッドチームレビュー No.9）。また本得点は令和5年度に実施された調査によるものであり、第9期の取組は反映されていない（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10596,7 +10596,7 @@
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率に由来し（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
+          <t>注1）重要度Aは第1回介護保険事業計画策定委員会での決定又は資料入手を要する事項、Bは第10期計画本文の記述に反映する事項、Cは追加のデータ確認のうえ判断する事項。注2）所見1・2・3は相互に関連する。給付水準の高さは認定率ではなく施設・居住系サービスの受給率と受給者単価がともに高いことによるものであり（所見1）、その施設・居住系受給率の全国との差は平成26年度1.98ポイントから令和7年度0.95ポイントへ半減し（13シート）、同時に認定者の利用率が低下し（所見2）、重度者の在宅化と供給縮小が進んでいる（所見3）。この4点が第10期の需給分析の中心論点になる。</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21452,7 @@
       <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>計画は一貫して0.8〜2.2ポイント低い。分母（総人口）の過大が原因。第10期は見える化に統一する。</t>
+          <t>計画は一貫して0.8〜2.2ポイント低い。65歳以上人口はほぼ一致する一方、分母（総人口）が大きいため。差が生じた理由は町別人口の実績により検証する。第10期は見える化に統一する。</t>
         </is>
       </c>
     </row>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>大雪は全国を8％上回る。分母はD41との突合により第1号被保険者数と確定した（大雪：在宅11.2％＋施設居住系5.3％＝16.5％、全国：11.0％＋4.3％＝15.3％、比1.078）。内訳は在宅が全国比1.02、施設および居住系が同1.23で、超過分はほぼ全て施設・居住系に由来する。</t>
+          <t>大雪は全国を8％上回る。分母はD41との突合により第1号被保険者数と確定した（大雪：在宅11.2％＋施設居住系5.3％＝16.5％、全国：11.0％＋4.3％＝15.3％、比1.078）。内訳は在宅が全国比1.02、施設および居住系が同1.23で、超過分の大半は施設・居住系の受給率の差による。</t>
         </is>
       </c>
     </row>
@@ -23077,7 +23077,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>平成29年度234人から令和2年度160人へ74人（31.6％）減少。第9期計画に減少の経緯の記述がない。</t>
+          <t>平成29年度234人から令和2年度160人へ74人（31.6％）減少。第9期計画に減少の経緯の記述がなく、休廃止・転換・休止床の整理のいずれによるものかを確認していない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -21452,7 +21452,7 @@
       <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>計画は一貫して0.8〜2.2ポイント低い。65歳以上人口はほぼ一致する一方、分母（総人口）が大きいため。差が生じた理由は町別人口の実績により検証する。第10期は見える化に統一する。</t>
+          <t>計画は一貫して0.8〜2.2ポイント低い。令和5年の差1.10ポイントは、高齢者数が178人少ないこと（寄与＋0.64pt）と総人口が382人多いこと（寄与＋0.46pt）が重なるため。分子の寄与が分母を上回る。住基と国勢調査は基準が異なる。第10期は見える化に統一する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>素案第9稿の施策・KPIが、上記1〜9の検証結果に対応しているかを評価する。</t>
+          <t>計画素案の施策・KPIが、上記1〜9の検証結果に対応しているかを評価する。</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>第10稿作成時</t>
+          <t>計画素案の改訂時</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -3217,7 +3217,7 @@
     <row r="28" ht="56" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>注1）本文の文字数（空白除去後）は、広域9期109,819字、美瑛22,514字、東神楽20,620字、東川22,793字、素案10期28,832字。素案第9稿は骨子段階であり、資料受領後に増補される前提のため、出現回数の単純比較ではなく密度で評価している。注2）密度が高いことは必ずしも記述が充実していることを意味しない。方針の1文で語が繰り返される場合もある。本表は記載漏れの検出を目的とする。注3）「処遇改善」「人生会議・ACP」が4計画とも0回である点は、国の方針との関係で確認を要する。処遇改善は事業者の取組であり保険者計画に必須の記載事項ではないが、第10期指針案が人材確保を都道府県計画の基本記載事項に追加する方向であることを踏まえ、北海道との連携の文脈で言及することを検討する。</t>
+          <t>注1）本文の文字数（空白除去後）は、広域9期109,819字、美瑛22,514字、東神楽20,620字、東川22,793字、素案10期28,832字。計画素案は骨子段階であり、資料受領後に増補される前提のため、出現回数の単純比較ではなく密度で評価している。注2）密度が高いことは必ずしも記述が充実していることを意味しない。方針の1文で語が繰り返される場合もある。本表は記載漏れの検出を目的とする。注3）「処遇改善」「人生会議・ACP」が4計画とも0回である点は、国の方針との関係で確認を要する。処遇改善は事業者の取組であり保険者計画に必須の記載事項ではないが、第10期指針案が人材確保を都道府県計画の基本記載事項に追加する方向であることを踏まえ、北海道との連携の文脈で言及することを検討する。</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>修正指示書（第9稿→第10稿）に追加済みの項目21件。追加後の総数は51件（区分A 15件／区分B 20件／区分C 16件、うち要照会35件）。</t>
+          <t>修正指示書に追加済みの項目21件。追加後の総数は51件（区分A 15件／区分B 20件／区分C 16件、うち要照会35件）。</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>平成27年度6.10％をピークに0.85ポイント低下。定員の縮小と整合する。</t>
+          <t>平成27年度6.10％をピークに0.85ポイント低下。定員の縮小と符合する。</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>注1）受給率は受給者数を第1号被保険者数で除した値。介護サービス利用率（06シート）は受給者数を認定者数で除した値であり、分母が異なる別の比率である。注2）D41-aは月次データであり、本シートでは年度（4月〜翌年3月）で平均した。令和7年度は令和8年1月までの10か月平均である。注3）要支援・要介護者1人あたり定員は介護サービス情報公表システム及び月報による。定員そのものは変わらなくても認定者が増えれば低下するため、供給の実数の変化（06シート1）と併せて読む。注4）第9期計画・素案第9稿とも本シートの指標を掲載していない。第2章に新設することを推奨する（修正指示書A-11・A-13）。</t>
+          <t>注1）受給率は受給者数を第1号被保険者数で除した値。介護サービス利用率（06シート）は受給者数を認定者数で除した値であり、分母が異なる別の比率である。注2）D41-aは月次データであり、本シートでは年度（4月〜翌年3月）で平均した。令和7年度は令和8年1月までの10か月平均である。注3）要支援・要介護者1人あたり定員は介護サービス情報公表システム及び月報による。定員そのものは変わらなくても認定者が増えれば低下するため、供給の実数の変化（06シート1）と併せて読む。注4）第9期計画・計画素案とも本シートの指標を掲載していない。第2章に新設することを推奨する（修正指示書A-11・A-13）。</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>素案第9稿 資料編 資料1の定義に対し、データ源の確保状況、基準値の算定可否、本検証の結果との整合、実行可能性を評価した。</t>
+          <t>計画素案 資料編 資料1の定義に対し、データ源の確保状況、基準値の算定可否、本検証の結果との整合、実行可能性を評価した。</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>素案第9稿の精査、修正指示書45件、施策体系新旧対照表、図表番号一覧（本文への差し込み位置）。</t>
+          <t>計画素案の精査、修正指示書45件、施策体系新旧対照表、図表番号一覧（本文への差し込み位置）。</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>地域課題は妥当性検証報告書で整理済み。骨子は素案第9稿が先行している。</t>
+          <t>地域課題は妥当性検証報告書で整理済み。骨子は計画素案が先行している。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>素案は第9稿まで作成済み。修正指示書45件で第10稿の方向を整理。</t>
+          <t>計画素案を作成済み。修正指示書45件で次の版の方向を整理。</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -9876,7 +9876,7 @@
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>注1）北海道第9期計画 第5章は8節・52頁で構成され、8節は第4章第2節の8基本目標と1対1で対応している。本シートは第3節（自立支援、介護予防・重度化防止の推進）、第6節（介護人材の養成・確保）、第8節（介護保険制度の適切な運営）の頁を目視で確認したうえで、全節に共通する構成として整理した。注2）大雪の素案第9稿は「本文12項目＋補完4項目＋施策管理指標」の3層構造を掲げており方向は妥当である。本シートの提案は、その3層を北海道と同じ「インプット→アウトプット→アウトカム」の記述構成に落とし込むことで、施策と指標の対応を計画本文の上で見えるようにするものである。注3）北海道の指標には市町村数を単位とするものが多く、1保険者である大雪にはそのまま適用できない。日常生活圏域数又は実数・率への置き換えが必要であり、その際の圏域の扱いは修正指示書C-9と連動する。</t>
+          <t>注1）北海道第9期計画 第5章は8節・52頁で構成され、8節は第4章第2節の8基本目標と1対1で対応している。本シートは第3節（自立支援、介護予防・重度化防止の推進）、第6節（介護人材の養成・確保）、第8節（介護保険制度の適切な運営）の頁を目視で確認したうえで、全節に共通する構成として整理した。注2）大雪の計画素案は「本文12項目＋補完4項目＋施策管理指標」の3層構造を掲げており方向は妥当である。本シートの提案は、その3層を北海道と同じ「インプット→アウトプット→アウトカム」の記述構成に落とし込むことで、施策と指標の対応を計画本文の上で見えるようにするものである。注3）北海道の指標には市町村数を単位とするものが多く、1保険者である大雪にはそのまま適用できない。日常生活圏域数又は実数・率への置き換えが必要であり、その際の圏域の扱いは修正指示書C-9と連動する。</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>重要度A＝第1回委員会での決定を要する／B＝第10期計画の記述に反映する／C＝データ確認のうえ判断する。本検証は、①代表KPIの達成度、②計画の記載事項（指標設計・施策体系・推計・保険料）の妥当性、③交付金による外部評価の分析からなる。令和6〜8年度の事業実績が未受領のため、事業が計画どおり実施されたかというプロセス評価は行っていない（レッドチームレビュー No.13）。また第9期の最終年度（令和8年度）の実績は令和9年3月末に確定するため、現時点の評価は中間評価である。他団体との比較は、入手可能な比較対象（上川管内21保険者、全国・北海道、健康とくらしの調査の同規模保険者40）によるものであり、介護保険上の類似保険者の選定条件は未決定である（同 No.14）。交付金の得点比較は人口規模を揃えていないため、小規模保険者に構造的に不利な評価項目が含まれる点に留意する（同 No.16）。判定の閾値は、比率の差が1.0ポイント未満を「同等」とし、それ以外は定性的に判断している（同 No.17）。</t>
+          <t>重要度A＝第1回委員会での決定を要する／B＝第10期計画の記述に反映する／C＝データ確認のうえ判断する。本検証は、①代表KPIの達成度、②計画の記載事項（指標設計・施策体系・推計・保険料）の妥当性、③交付金による外部評価の分析からなる。令和6〜8年度の事業実績が未受領のため、事業が計画どおり実施されたかというプロセス評価は行っていない（自己点検記録 No.13）。また第9期の最終年度（令和8年度）の実績は令和9年3月末に確定するため、現時点の評価は中間評価である。他団体との比較は、入手可能な比較対象（上川管内21保険者、全国・北海道、健康とくらしの調査の同規模保険者40）によるものであり、介護保険上の類似保険者の選定条件は未決定である（同 No.14）。交付金の得点比較は人口規模を揃えていないため、小規模保険者に構造的に不利な評価項目が含まれる点に留意する（同 No.16）。判定の閾値は、比率の差が1.0ポイント未満を「同等」とし、それ以外は定性的に判断している（同 No.17）。</t>
         </is>
       </c>
     </row>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（レッドチームレビュー No.7）。また介護老人福祉施設の定員が公表値の上で234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
+          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（自己点検記録 No.7）。また介護老人福祉施設の定員が公表値の上で234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>未利用の要因（供給制約・申請先行・軽度者の自立・家族介護・経済的理由）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。【留意】認定者が増え受給者が減ったという事実だけでは供給制約は導けない（レッドチームレビュー No.8）。第9期に認定申請の勧奨を行った結果であれば、供給制約ではなく認定行政の変化であり、施策の方向は逆になる。要因を特定するまで供給制約と断定しない。</t>
+          <t>未利用の要因（供給制約・申請先行・軽度者の自立・家族介護・経済的理由）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。【留意】認定者が増え受給者が減ったという事実だけでは供給制約は導けない（自己点検記録 No.8）。第9期に認定申請の勧奨を行った結果であれば、供給制約ではなく認定行政の変化であり、施策の方向は逆になる。要因を特定するまで供給制約と断定しない。</t>
         </is>
       </c>
     </row>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>重度在宅者の増加と供給縮小の同時進行を第2章の主要論点として明記し、第6章の整備方針に接続する。家族介護者支援（H07・H08）の優先度を上げる。【留意】この「在宅化」は施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない（レッドチームレビュー No.10）。24時間対応の3サービスが区域内に存在しないことを踏まえると、家族介護への転嫁である可能性が高い。政策の成果と誤読されないよう記述する。</t>
+          <t>重度在宅者の増加と供給縮小の同時進行を第2章の主要論点として明記し、第6章の整備方針に接続する。家族介護者支援（H07・H08）の優先度を上げる。【留意】この「在宅化」は施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない（自己点検記録 No.10）。24時間対応の3サービスが区域内に存在しないことを踏まえると、家族介護への転嫁である可能性が高い。政策の成果と誤読されないよう記述する。</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>当初は「3町とも数値目標が1件もない」と判定していたが、これは「数値目標」「目標値」という語の全文検索によるものであり、語を用いずに数値で目標を設定している東川町の事例を見落としていた（レッドチームレビュー No.5）。広域が代表KPI4項目を設定した一方、美瑛町・東神楽町の計画には事業の目標がない。「一般介護予防事業評価事業」で広域のKPI検証への参画を明記しているのは東川町のみである。</t>
+          <t>当初は「3町とも数値目標が1件もない」と判定していたが、これは「数値目標」「目標値」という語の全文検索によるものであり、語を用いずに数値で目標を設定している東川町の事例を見落としていた（自己点検記録 No.5）。広域が代表KPI4項目を設定した一方、美瑛町・東神楽町の計画には事業の目標がない。「一般介護予防事業評価事業」で広域のKPI検証への参画を明記しているのは東川町のみである。</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>【留意】本所見の根拠は合計・75歳以上・85歳以上の3系列であり、65〜74歳の認定率及び5歳階級別の直接法による年齢調整は行っていない（レッドチームレビュー No.1）。また性・年齢調整済み要介護2以上認定率（W144）は全国を上回り変化率も＋1.76と悪化しており、本所見と方向が異なる。両者は指標の範囲（全要介護度の粗率か要介護2以上の調整済みか）が異なるが、整合を要介護度別の推移で実証していない。確認事項No.37の資料により再検証する。全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
+          <t>【留意】本所見の根拠は合計・75歳以上・85歳以上の3系列であり、65〜74歳の認定率及び5歳階級別の直接法による年齢調整は行っていない（自己点検記録 No.1）。また性・年齢調整済み要介護2以上認定率（W144）は全国を上回り変化率も＋1.76と悪化しており、本所見と方向が異なる。両者は指標の範囲（全要介護度の粗率か要介護2以上の調整済みか）が異なるが、整合を要介護度別の推移で実証していない。確認事項No.37の資料により再検証する。全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>第8期は必要額と基準額がほぼ均衡しており設定は良好。第9期は令和6年度に337円/月の余裕が生じ、取崩を前提とした設計に対し実績は剰余方向。令和8年度の実績を待って確定する。【留意】剰余の額（2年で約42百万円）は概算である（レッドチームレビュー No.3）。令和6年度の必要保険料月額は令和8年1月時点の実績を年度換算した値であり、決算及び基金の積立実績で確認していない。決算により確定値に置き換える。</t>
+          <t>第8期は必要額と基準額がほぼ均衡しており設定は良好。第9期は令和6年度に337円/月の余裕が生じ、取崩を前提とした設計に対し実績は剰余方向。令和8年度の実績を待って確定する。【留意】剰余の額（2年で約42百万円）は概算である（自己点検記録 No.3）。令和6年度の必要保険料月額は令和8年1月時点の実績を年度換算した値であり、決算及び基金の積立実績で確認していない。決算により確定値に置き換える。</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施されたものであり、第9期（令和6年度〜）の取組は反映されていない（レッドチームレビュー No.2）。なお評価項目ごとの対象期間（調査時点の体制か前年度の実績か）は調査要領で確認していないため、「第8期の評価である」とは記述しない（レッドチームレビュー No.20）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
+          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施されたものであり、第9期（令和6年度〜）の取組は反映されていない（自己点検記録 No.2）。なお評価項目ごとの対象期間（調査時点の体制か前年度の実績か）は調査要領で確認していないため、「第8期の評価である」とは記述しない（自己点検記録 No.20）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、「全国トップ級」等の表現は用いない（レッドチームレビュー No.9）。また本得点は令和5年度に実施された調査によるものであり、第9期の取組は反映されていない（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
+          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、水準を断定する表現は用いず、「令和6年度分の指標では全国平均を上回る」と記述する。また本得点は令和5年度に実施された調査によるものであり、第9期の取組は反映されていない（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>両者は矛盾しない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、【令和8年7月29日訂正】当初は「軽度は改善したが中重度は悪化している」と説明していたが、見える化B5a・B6a・B6bの調整済み認定率により、これは誤りであることが判明した。年齢構成を調整すると、中重度（要介護3〜5）は平成30年5.4％から令和7年4.7％へ低下が続いている一方、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じている。W144とB5aは基準人口・調整方法・時点・単位が異なるため直接比較できない（認定率の年齢調整分析 04・05シート）。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。第9期計画の代表KPI①（認定率）は粗率であり、この構造を捉えられていなかった。</t>
+          <t>両者は矛盾しない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、【令和8年7月29日訂正】当初は「軽度は改善したが中重度は悪化している」と説明していたが、見える化B5a・B6a・B6bの調整済み認定率により、これは誤りであることが判明した。年齢構成を調整すると、中重度（要介護3〜5）は平成30年5.4％から令和7年4.7％へ低下が続いている一方、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じている。W144とB5aは基準人口・調整方法・時点・単位が異なるため直接比較できない（認定率の年齢調整分析 04・05シート）。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と符合する。第9期計画の代表KPI①（認定率）は粗率であり、この構造を捉えられていなかった。</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11955,7 +11955,7 @@
     <row r="57" ht="70" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>注1）本シートは受領した「指標リスト（目的別）」（見える化システムの指標一覧・994行）に基づく。指標IDが付されているものは906件で、うち受領済みはA系列13件・B系列27件・C系列4件・D系列199件・P系列ほかを含む182件（20.1％）である。注2）1の最優先6項目（計54件）は、いずれも本検証で明らかになった論点に直接対応する。特にF4は修正指示書A-16（通いの場の統計の不一致）を、H1・H2は同C-16（H13・H14の設問がない）を、δ2・δ3は同A-13・B-22（重度在宅化と24時間対応サービスの空白）を解決する。注3）2の依頼により、新別表11事項のうち三・七・九・十・十一の5事項が対応可能となる。残る一（地勢と交通）・八（高齢者向け住まい）は自治体からの資料提供、五の一部（介護SCR）・七の一部（入所率・稼働率）・二の一部（人口メッシュ）は改修待ちとなる。注4）依頼にあたっては、①出力年度（可能な限り時系列）、②比較対象（全国・北海道・類似保険者・圏域内保険者）、③類似保険者を選ぶ場合はその選定条件、の3点を併せてご指定いただきたい。</t>
+          <t>注1）本シートは受領した「指標リスト（目的別）」（見える化システムの指標一覧・994行）に基づく。指標IDが付されているものは906件で、うち受領済みはA系列13件・B系列27件・C系列4件・D系列199件・P系列ほかを含む182件（20.1％）である。注2）1の最優先6項目（計54件）は、いずれも本検証で扱った論点に直接対応する。特にF4は修正指示書A-16（通いの場の統計の不一致）を、H1・H2は同C-16（H13・H14の設問がない）を、δ2・δ3は同A-13・B-22（重度在宅化と24時間対応サービスの空白）を解決する。注3）2の依頼により、新別表11事項のうち三・七・九・十・十一の5事項が対応可能となる。残る一（地勢と交通）・八（高齢者向け住まい）は自治体からの資料提供、五の一部（介護SCR）・七の一部（入所率・稼働率）・二の一部（人口メッシュ）は改修待ちとなる。注4）依頼にあたっては、①出力年度（可能な限り時系列）、②比較対象（全国・北海道・類似保険者・圏域内保険者）、③類似保険者を選ぶ場合はその選定条件、の3点を併せてご指定いただきたい。</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>令和4年度に1事業所減。D26の定員117人（R3）→99人（R4以降）、D13の給付月額▲10.5％と整合する。</t>
+          <t>令和4年度に1事業所減。D26の定員117人（R3）→99人（R4以降）、D13の給付月額▲10.5％と符合する。</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>令和6年度に3事業所増（＋30％）。D13の給付月額＋52.8％、利用回数55.4回（全国29.7の1.87倍）と整合する。</t>
+          <t>令和6年度に3事業所増（＋30％）。D13の給付月額＋52.8％、利用回数55.4回（全国29.7の1.87倍）と符合する。</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>平成24年度2→令和6年度7で3.5倍。D13の給付月額＋69.2％と整合する。本計画期間で最も伸びた供給基盤。</t>
+          <t>平成24年度2→令和6年度7で3.5倍。D13の給付月額＋69.2％と符合する。本計画期間で最も伸びた供給基盤。</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>1事業所の閉鎖がそのまま定員減となっている（1ユニット18人相当）。給付月額の▲10.5％（D13）と整合する。</t>
+          <t>1事業所の閉鎖がそのまま定員減となっている（1ユニット18人相当）。給付月額の▲10.5％（D13）と符合する。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>事業所数2→7（K3c）、給付月額＋69.2％（D13）と整合する明確な拡大。認定者1万対188.58は全国207.04の91.1％、北海道157.15の120.0％。平成29年度は全国の75.8％であり、全国水準に近づいた。</t>
+          <t>事業所数2→7（K3c）、給付月額＋69.2％（D13）と符合する明確な拡大。認定者1万対188.58は全国207.04の91.1％、北海道157.15の120.0％。平成29年度は全国の75.8％であり、全国水準に近づいた。</t>
         </is>
       </c>
     </row>
@@ -18261,7 +18261,7 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>【解釈】成果（アウトカム）は全国トップ級である一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。これは「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態を示す。第9期計画のロジックモデルが不完全であること（18シート）、代表KPIの検証が令和8年3月末実績の1回のみで年次の中間評価がないこと（02シート）と同じ構造である。第10期でロジックモデルのアウトプット指標を整備すれば、施策の実効性と交付金得点の双方が改善する余地が大きい。</t>
+          <t>【解釈】成果（アウトカム）は令和6年度分の指標では全国平均を上回る一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。これは「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態を示す。第9期計画のロジックモデルが不完全であること（18シート）、代表KPIの検証が令和8年3月末実績の1回のみで年次の中間評価がないこと（02シート）と同じ構造である。第10期でロジックモデルのアウトプット指標を整備すれば、施策の実効性と交付金得点の双方が改善する余地が大きい。</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>全国の38.2％。O4・O5の算定実数が年0〜1人であること（20シート）、L系列（診療報酬側）のデータがないことと整合する。</t>
+          <t>全国の38.2％。O4・O5の算定実数が年0〜1人であること（20シート）、L系列（診療報酬側）のデータがないことと符合する。</t>
         </is>
       </c>
     </row>
@@ -18831,7 +18831,7 @@
       <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>第10期のH09（退院時支援調整実施率）が対象とする領域そのものである。O5（退院・退所時連携加算）の実数が年0〜1人であること（20シート）と整合する。H09を新設する根拠が国の評価でも裏付けられた。</t>
+          <t>第10期のH09（退院時支援調整実施率）が対象とする領域そのものである。O5（退院・退所時連携加算）の実数が年0〜1人であること（20シート）と符合する。H09を新設する根拠が国の評価でも裏付けられた。</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       <c r="J46" s="6" t="inlineStr"/>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>北海道の第9期評価指標②（生活支援コーディネーター配置市町村数127→142）と整合する強み。</t>
+          <t>北海道の第9期評価指標②（生活支援コーディネーター配置市町村数127→142）と符合する強み。</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>北海道の第9期評価指標①（地域ケア会議の運営状況）と整合する強み。</t>
+          <t>北海道の第9期評価指標①（地域ケア会議の運営状況）と符合する強み。</t>
         </is>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
       <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>満点。D2/D4でみた施設受給率の低下（要介護5が1.2％→0.7％）と整合する。</t>
+          <t>満点。D2/D4でみた施設受給率の低下（要介護5が1.2％→0.7％）と符合する。</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19108,7 @@
       <c r="J51" s="6" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>北海道の第9期評価指標②（多様な主体による生活支援85→98市町村）と整合する。</t>
+          <t>北海道の第9期評価指標②（多様な主体による生活支援85→98市町村）と符合する。</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
     <row r="81" ht="70" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>【重要】W144は「性・年齢調整済み要介護2以上の認定率」であり、第10期のH01（年齢調整済要介護認定率）が求めていた指標そのものである。国が全保険者について毎年算定・公表しているため、データ源として最も確実である。その値は大雪9.25％で全国8.99％を2.9％上回り、しかも全国・北海道が低下する中で大雪のみ上昇している（W145）。本検証の別の所見（75歳以上の認定率が35.3％→33.5％へ低下、85歳以上が63.7％→61.6％へ低下）と矛盾するものではない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、【訂正】両者は基準人口・調整方法・時点・単位が異なるため直接比較できない。見える化B6a・B6bによれば、中重度は低下が続き軽度が直近で上昇に転じている（認定率の年齢調整分析 04・05シート）。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と整合する。</t>
+          <t>【重要】W144は「性・年齢調整済み要介護2以上の認定率」であり、第10期のH01（年齢調整済要介護認定率）が求めていた指標そのものである。国が全保険者について毎年算定・公表しているため、データ源として最も確実である。その値は大雪9.25％で全国8.99％を2.9％上回り、しかも全国・北海道が低下する中で大雪のみ上昇している（W145）。本検証の別の所見（75歳以上の認定率が35.3％→33.5％へ低下、85歳以上が63.7％→61.6％へ低下）と矛盾するものではない。前者は要介護2以上に限った性年齢調整済みの値、後者は全要介護度を含む年齢層別の粗率であり、【訂正】両者は基準人口・調整方法・時点・単位が異なるため直接比較できない。見える化B6a・B6bによれば、中重度は低下が続き軽度が直近で上昇に転じている（認定率の年齢調整分析 04・05シート）。この構造は、要介護4・5の在宅受給率が上昇し（13シート）、施設定員が縮小している（03シート）という供給側の変化と符合する。</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>4.2ポイント上昇。国の地域包括ケアの方向と整合するが、重度者の在宅化が主因である点に留意を要する。</t>
+          <t>4.2ポイント上昇。国の地域包括ケアの方向と符合するが、重度者の在宅化が主因である点に留意を要する。</t>
         </is>
       </c>
     </row>
@@ -23810,7 +23810,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第9期基本指針への第9期計画の対応と、第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1 令和8年3月9日、第135回 資料2-1 令和8年6月29日）への素案第9稿の対応状況。両資料を受領し原典で確認した。</t>
+          <t>第9期基本指針への第9期計画の対応と、第10期基本指針案（社会保障審議会介護保険部会 第134回 資料1-1 令和8年3月9日、第135回 資料2-1 令和8年6月29日）への計画素案の対応状況。両資料を受領し原典で確認した。</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23945,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は対応済み。ただし素案第9稿の同語の出現は3回で、記載量が第9期を下回る。第10期指針案は生産性向上を都道府県計画の基本記載事項に追加する方向であり、素案の記述強化を要する。</t>
+          <t>第9期計画は対応済み。ただし計画素案の同語の出現は3回で、記載量が第9期を下回る。第10期指針案は生産性向上を都道府県計画の基本記載事項に追加する方向であり、素案の記述強化を要する。</t>
         </is>
       </c>
     </row>
@@ -24016,7 +24016,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2　第10期基本指針案の主な方向への素案第9稿の対応</t>
+          <t>2　第10期基本指針案の主な方向への計画素案の対応</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24043,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>素案第9稿の記載</t>
+          <t>計画素案の記載</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -24370,7 +24370,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>素案第9稿への影響</t>
+          <t>計画素案への影響</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -9917,7 +9917,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>重要度A＝第1回委員会での決定を要する／B＝第10期計画の記述に反映する／C＝データ確認のうえ判断する。本検証は、①代表KPIの達成度、②計画の記載事項（指標設計・施策体系・推計・保険料）の妥当性、③交付金による外部評価の分析からなる。令和6〜8年度の事業実績が未受領のため、事業が計画どおり実施されたかというプロセス評価は行っていない（自己点検記録 No.13）。また第9期の最終年度（令和8年度）の実績は令和9年3月末に確定するため、現時点の評価は中間評価である。他団体との比較は、入手可能な比較対象（上川管内21保険者、全国・北海道、健康とくらしの調査の同規模保険者40）によるものであり、介護保険上の類似保険者の選定条件は未決定である（同 No.14）。交付金の得点比較は人口規模を揃えていないため、小規模保険者に構造的に不利な評価項目が含まれる点に留意する（同 No.16）。判定の閾値は、比率の差が1.0ポイント未満を「同等」とし、それ以外は定性的に判断している（同 No.17）。</t>
+          <t>重要度A＝第1回委員会での決定を要する／B＝第10期計画の記述に反映する／C＝データ確認のうえ判断する。本検証は、①代表KPIの達成度、②計画の記載事項（指標設計・施策体系・推計・保険料）の妥当性、③交付金による外部評価の分析からなる。令和6〜8年度の事業実績が未受領のため、事業が計画どおり実施されたかというプロセス評価は行っていない（受託者の自己点検による）。また第9期の最終年度（令和8年度）の実績は令和9年3月末に確定するため、現時点の評価は中間評価である。他団体との比較は、入手可能な比較対象（上川管内21保険者、全国・北海道、健康とくらしの調査の同規模保険者40）によるものであり、介護保険上の類似保険者の選定条件は未決定である（同 No.14）。交付金の得点比較は人口規模を揃えていないため、小規模保険者に構造的に不利な評価項目が含まれる点に留意する（同 No.16）。判定の閾値は、比率の差が1.0ポイント未満を「同等」とし、それ以外は定性的に判断している（同 No.17）。</t>
         </is>
       </c>
     </row>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（自己点検記録 No.7）。また介護老人福祉施設の定員が公表値の上で234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
+          <t>H01を年齢調整済認定率へ改める方向は妥当。加えて施設および居住系サービス受給率をモニタリング指標に加える。D49の受給率の分母はD41との突合により第1号被保険者数と確定し、当初の定義上の疑義は解消した。【留意】認定率・受給率・受給者単価は独立ではなく、施設が多ければ受給率と単価が同時に上がるため、要因の特定にはなっていない（受託者の自己点検による）。また介護老人福祉施設の定員が公表値の上で234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いことから、区域外施設の利用による可能性がある。自給率の算定（第5章 基本目標3）により検証する。</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>未利用の要因（供給制約・申請先行・軽度者の自立・家族介護・経済的理由）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。【留意】認定者が増え受給者が減ったという事実だけでは供給制約は導けない（自己点検記録 No.8）。第9期に認定申請の勧奨を行った結果であれば、供給制約ではなく認定行政の変化であり、施策の方向は逆になる。要因を特定するまで供給制約と断定しない。</t>
+          <t>未利用の要因（供給制約・申請先行・軽度者の自立・家族介護・経済的理由）を分解し、供給制約分をH12（未充足）で管理する。第2章に利用率と受給率の双方の推移を新設し、分母の違いを注記する。【留意】認定者が増え受給者が減ったという事実だけでは供給制約は導けない（受託者の自己点検による）。第9期に認定申請の勧奨を行った結果であれば、供給制約ではなく認定行政の変化であり、施策の方向は逆になる。要因を特定するまで供給制約と断定しない。</t>
         </is>
       </c>
     </row>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>重度在宅者の増加と供給縮小の同時進行を第2章の主要論点として明記し、第6章の整備方針に接続する。家族介護者支援（H07・H08）の優先度を上げる。【留意】この「在宅化」は施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない（自己点検記録 No.10）。24時間対応の3サービスが区域内に存在しないことを踏まえると、家族介護への転嫁である可能性が高い。政策の成果と誤読されないよう記述する。</t>
+          <t>重度在宅者の増加と供給縮小の同時進行を第2章の主要論点として明記し、第6章の整備方針に接続する。家族介護者支援（H07・H08）の優先度を上げる。【留意】この「在宅化」は施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない（受託者の自己点検による）。24時間対応の3サービスが区域内に存在しないことを踏まえると、家族介護への転嫁である可能性が高い。政策の成果と誤読されないよう記述する。</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>当初は「3町とも数値目標が1件もない」と判定していたが、これは「数値目標」「目標値」という語の全文検索によるものであり、語を用いずに数値で目標を設定している東川町の事例を見落としていた（自己点検記録 No.5）。広域が代表KPI4項目を設定した一方、美瑛町・東神楽町の計画には事業の目標がない。「一般介護予防事業評価事業」で広域のKPI検証への参画を明記しているのは東川町のみである。</t>
+          <t>当初は「3町とも数値目標が1件もない」と判定していたが、これは「数値目標」「目標値」という語の全文検索によるものであり、語を用いずに数値で目標を設定している東川町の事例を見落としていた（受託者の自己点検による）。広域が代表KPI4項目を設定した一方、美瑛町・東神楽町の計画には事業の目標がない。「一般介護予防事業評価事業」で広域のKPI検証への参画を明記しているのは東川町のみである。</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>【留意】本所見の根拠は合計・75歳以上・85歳以上の3系列であり、65〜74歳の認定率及び5歳階級別の直接法による年齢調整は行っていない（自己点検記録 No.1）。また性・年齢調整済み要介護2以上認定率（W144）は全国を上回り変化率も＋1.76と悪化しており、本所見と方向が異なる。両者は指標の範囲（全要介護度の粗率か要介護2以上の調整済みか）が異なるが、整合を要介護度別の推移で実証していない。確認事項No.37の資料により再検証する。全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
+          <t>【留意】本所見の根拠は合計・75歳以上・85歳以上の3系列であり、65〜74歳の認定率及び5歳階級別の直接法による年齢調整は行っていない（受託者の自己点検による）。また性・年齢調整済み要介護2以上認定率（W144）は全国を上回り変化率も＋1.76と悪化しており、本所見と方向が異なる。両者は指標の範囲（全要介護度の粗率か要介護2以上の調整済みか）が異なるが、整合を要介護度別の推移で実証していない。確認事項No.37の資料により再検証する。全体の認定率の上昇は、75歳以上・85歳以上の構成比が高まったことによるもので、同一年齢層でみれば認定率は低下している。第9期の介護予防の取組は、年齢構成の影響を除けば成果が出ている。未調整の認定率を目標に据えたために「未達」と評価される構造になっていた。</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>第8期は必要額と基準額がほぼ均衡しており設定は良好。第9期は令和6年度に337円/月の余裕が生じ、取崩を前提とした設計に対し実績は剰余方向。令和8年度の実績を待って確定する。【留意】剰余の額（2年で約42百万円）は概算である（自己点検記録 No.3）。令和6年度の必要保険料月額は令和8年1月時点の実績を年度換算した値であり、決算及び基金の積立実績で確認していない。決算により確定値に置き換える。</t>
+          <t>第8期は必要額と基準額がほぼ均衡しており設定は良好。第9期は令和6年度に337円/月の余裕が生じ、取崩を前提とした設計に対し実績は剰余方向。令和8年度の実績を待って確定する。【留意】剰余の額（2年で約42百万円）は概算である（受託者の自己点検による）。令和6年度の必要保険料月額は令和8年1月時点の実績を年度換算した値であり、決算及び基金の積立実績で確認していない。決算により確定値に置き換える。</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施されたものであり、第9期（令和6年度〜）の取組は反映されていない（自己点検記録 No.2）。なお評価項目ごとの対象期間（調査時点の体制か前年度の実績か）は調査要領で確認していないため、「第8期の評価である」とは記述しない（自己点検記録 No.20）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
+          <t>第9期計画は交付金の評価結果に一切言及していない。交付金額は得点に応じて配分されるため、この差はそのまま財源の差となる。【留意】令和5年調査は令和5年度に実施されたものであり、第9期（令和6年度〜）の取組は反映されていない（受託者の自己点検による）。なお評価項目ごとの対象期間（調査時点の体制か前年度の実績か）は調査要領で確認していないため、「第8期の評価である」とは記述しない（受託者の自己点検による）。第9期の評価とするには令和6年・令和7年調査の得点を要する（確認事項No.38）。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、水準を断定する表現は用いず、「令和6年度分の指標では全国平均を上回る」と記述する。また本得点は令和5年度に実施された調査によるものであり、第9期の取組は反映されていない（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
+          <t>成果と活動の得点に差がある状態（原因は評価調書の受領後に確認）である。原因は未確認である。【留意】成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。分子・分母の実数による安定性の検証を行っていないため、水準を断定する表現は用いず、「令和6年度分の指標では全国平均を上回る」と記述する。また本得点は令和5年度に実施された調査によるものであり、第9期の取組は反映されていない（所見18の留意）。第9期計画の第5章が3列の表のみでアウトプット指標を持たないこと（所見15）、代表KPIの検証が期末1回のみで年次の中間評価がないこと（02シート）と同じ構造であり、国の評価がこれを独立に裏付けている。「介護保険事業計画の進捗状況（計画評価）」も全国の64.5％である。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -18261,7 +18261,7 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>【解釈】成果（アウトカム）は令和6年度分の指標では全国平均を上回る一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。これは「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態を示す。第9期計画のロジックモデルが不完全であること（18シート）、代表KPIの検証が令和8年3月末実績の1回のみで年次の中間評価がないこと（02シート）と同じ構造である。第10期でロジックモデルのアウトプット指標を整備すれば、施策の実効性と交付金得点の双方が改善する余地が大きい。</t>
+          <t>【解釈】成果（アウトカム）は令和6年度分の指標では全国平均を上回る一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。これは成果と活動の得点に差がある状態（原因は評価調書の受領後に確認）である。原因は未確認である。第9期計画のロジックモデルが不完全であること（18シート）、代表KPIの検証が令和8年3月末実績の1回のみで年次の中間評価がないこと（02シート）と同じ構造である。第10期でロジックモデルのアウトプット指標を整備すれば、施策の実効性と交付金得点の双方が改善する余地が大きい。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_妥当性検証報告書.xlsx
+++ b/output/第10期計画_妥当性検証報告書.xlsx
@@ -13161,7 +13161,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>第3章第4節から当該記述を外し、ニーズ調査ベースの系列であることを明記する。総合事業ベースでは令和2年度1.6％で、北海道の第9期目標5.37％を2.34ポイント下回る。</t>
+          <t>第3章第4節から当該記述を外し、ニーズ調査ベースの系列であることを明記する。総合事業ベースでは令和6年度3.53％で、北海道の第9期目標5.37％を1.84ポイント下回る（令和2年度は1.6％）。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>総合事業ベースで全国の31％、箇所数の密度で全国の25％という水準は、第9期計画が代表KPIに掲げた領域としては低い。しかも平成29年度をピークに低下している。</t>
+          <t>総合事業ベースの参加率は令和2年度1.6％から令和6年度3.53％へ回復し、箇所数も3箇所から25箇所（うち週1回以上11箇所）へ増えた。ただし全国の令和2年度5.2％、北海道3.9％という水準にはなお届いていない。</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>農作業を主な活動内容とする通いの場は全国0.1％・北海道0.1％と稀だが、大雪は3箇所中1箇所を占める。</t>
+          <t>農作業を主な活動内容とする通いの場は全国0.1％・北海道0.1％と稀だが、大雪は令和2年度の3箇所中1箇所を占めていた。令和6年度の25箇所の活動内容の内訳は本調査からは分からない。</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
